--- a/listas/ImportarPreciosPOSCarnaveDF PUBLICO.xlsx
+++ b/listas/ImportarPreciosPOSCarnaveDF PUBLICO.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/35cfd8ec92face1f/Desktop/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{51524EB0-82B5-42CD-81EF-AA031FAE3FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="20730" windowHeight="11760"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PRECIOS_DE_VENTA" sheetId="1" r:id="rId1"/>
@@ -14,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">PRECIOS_DE_VENTA!$A$1:$L$1000</definedName>
     <definedName name="Excel_BuiltIn__FilterDatabase" localSheetId="0">PRECIOS_DE_VENTA!$A$2:$N$2</definedName>
   </definedNames>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1668" uniqueCount="645">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1707" uniqueCount="684">
   <si>
     <t>#PLANILLA DE FORMACIÓN DE PRECIOS PARA SISTEMA POS CARNAVE</t>
   </si>
@@ -1970,12 +1976,129 @@
   </si>
   <si>
     <t>PAPAS PRINGLES</t>
+  </si>
+  <si>
+    <t>MILANESA DE CERDO</t>
+  </si>
+  <si>
+    <t>MIX ENERGETICO</t>
+  </si>
+  <si>
+    <t>SALSA DE SOJA</t>
+  </si>
+  <si>
+    <t>PASTA DE MANI</t>
+  </si>
+  <si>
+    <t>ARROZ GALLO</t>
+  </si>
+  <si>
+    <t>ATUN AL NATURAL</t>
+  </si>
+  <si>
+    <t>ATUN EN ACEITE</t>
+  </si>
+  <si>
+    <t>MANI SALADO,SABOR,PELADO</t>
+  </si>
+  <si>
+    <t>MANI C/CASCARA</t>
+  </si>
+  <si>
+    <t>ESENCIA DE VAINILLA</t>
+  </si>
+  <si>
+    <t>ACEITE DE COCO</t>
+  </si>
+  <si>
+    <t>SALSA DE HUMO</t>
+  </si>
+  <si>
+    <t>PALITOS ZYMA</t>
+  </si>
+  <si>
+    <t>FRUTOS SECOS S/PASAS</t>
+  </si>
+  <si>
+    <t>TOSTADAS LIGTH</t>
+  </si>
+  <si>
+    <t>ALMOHADITAS RELLENAS</t>
+  </si>
+  <si>
+    <t>PASTA MULTICEREAL MAIZ</t>
+  </si>
+  <si>
+    <t>PASTA MULTICEREAL QUINOA</t>
+  </si>
+  <si>
+    <t>PASTA MULTICEREAL CHIA</t>
+  </si>
+  <si>
+    <t>PECHUGA REVENTA</t>
+  </si>
+  <si>
+    <t>ALAS REVENTA</t>
+  </si>
+  <si>
+    <t>PATA Y MUSLO REVENTA</t>
+  </si>
+  <si>
+    <t>MEDIA TARDE</t>
+  </si>
+  <si>
+    <t>LEVADURA LEVEX</t>
+  </si>
+  <si>
+    <t>PULPA DURAZNO</t>
+  </si>
+  <si>
+    <t>PULPA MELON</t>
+  </si>
+  <si>
+    <t>PULPA FRUTILLA</t>
+  </si>
+  <si>
+    <t>ACEITUNAS NEGRAS</t>
+  </si>
+  <si>
+    <t>FAJITAS DE PECHUGA</t>
+  </si>
+  <si>
+    <t>COPOZ MAIZ AZUCARADO</t>
+  </si>
+  <si>
+    <t>COPOZ MAIZ S/AZUCAR</t>
+  </si>
+  <si>
+    <t>BOLITA CHOCO</t>
+  </si>
+  <si>
+    <t>ARITOS FRUTALES</t>
+  </si>
+  <si>
+    <t>ARITOS CEREALES Y MIEL</t>
+  </si>
+  <si>
+    <t>NINA CRANBERRY</t>
+  </si>
+  <si>
+    <t>NINA BLONDIES</t>
+  </si>
+  <si>
+    <t>NINA LEMON</t>
+  </si>
+  <si>
+    <t>ETCHAR PRIVADO</t>
+  </si>
+  <si>
+    <t>POLVO DE HORNEAR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.00&quot; &quot;%"/>
     <numFmt numFmtId="165" formatCode="0&quot; &quot;%"/>
@@ -2848,7 +2971,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3170,37 +3293,38 @@
     <xf numFmtId="4" fontId="17" fillId="12" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="16" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="26">
-    <cellStyle name="Accent" xfId="1"/>
-    <cellStyle name="Accent 1" xfId="2"/>
-    <cellStyle name="Accent 2" xfId="3"/>
-    <cellStyle name="Accent 3" xfId="4"/>
-    <cellStyle name="Bad" xfId="5"/>
-    <cellStyle name="Error" xfId="6"/>
-    <cellStyle name="Excel_BuiltIn_Percent" xfId="7"/>
-    <cellStyle name="Footnote" xfId="8"/>
-    <cellStyle name="Good" xfId="9"/>
-    <cellStyle name="Heading" xfId="10"/>
-    <cellStyle name="Heading 1" xfId="11"/>
-    <cellStyle name="Heading 2" xfId="12"/>
+    <cellStyle name="Accent" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Accent 1" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Accent 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Accent 3" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Bad" xfId="5" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Error" xfId="6" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Excel_BuiltIn_Percent" xfId="7" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Footnote" xfId="8" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Good" xfId="9" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Heading" xfId="10" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="Heading 1" xfId="11" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Heading 2" xfId="12" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
     <cellStyle name="Neutral" xfId="13" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
-    <cellStyle name="Normal 2" xfId="14"/>
-    <cellStyle name="Normal 3" xfId="15"/>
-    <cellStyle name="Normal 4" xfId="16"/>
-    <cellStyle name="Note" xfId="17"/>
+    <cellStyle name="Normal 2" xfId="14" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="Normal 3" xfId="15" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="Normal 4" xfId="16" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="Note" xfId="17" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
     <cellStyle name="Porcentaje" xfId="25" builtinId="5"/>
-    <cellStyle name="Porcentaje 2" xfId="18"/>
-    <cellStyle name="Porcentaje 3" xfId="19"/>
-    <cellStyle name="Result" xfId="20"/>
-    <cellStyle name="Status" xfId="21"/>
-    <cellStyle name="Text" xfId="22"/>
-    <cellStyle name="Texto explicativo 2" xfId="23"/>
-    <cellStyle name="Warning" xfId="24"/>
+    <cellStyle name="Porcentaje 2" xfId="18" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="Porcentaje 3" xfId="19" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="Result" xfId="20" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="Status" xfId="21" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
+    <cellStyle name="Text" xfId="22" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
+    <cellStyle name="Texto explicativo 2" xfId="23" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
+    <cellStyle name="Warning" xfId="24" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3504,14 +3628,14 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.28515625" defaultRowHeight="15.75"/>
   <cols>
@@ -3530,17 +3654,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="1" customFormat="1" ht="20.25">
-      <c r="A1" s="125" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="125"/>
-      <c r="E1" s="125"/>
-      <c r="F1" s="125"/>
-      <c r="G1" s="125"/>
-      <c r="H1" s="125"/>
-      <c r="I1" s="125"/>
+      <c r="A1" s="126" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="126"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
+      <c r="E1" s="126"/>
+      <c r="F1" s="126"/>
+      <c r="G1" s="126"/>
+      <c r="H1" s="126"/>
+      <c r="I1" s="126"/>
       <c r="J1" s="121" t="s">
         <v>549</v>
       </c>
@@ -5505,11 +5629,11 @@
         <v>4500</v>
       </c>
       <c r="H49" s="22">
-        <v>0.33300000000000002</v>
+        <v>0.66659999999999997</v>
       </c>
       <c r="I49" s="23">
         <f t="shared" ref="I49:I60" si="6">+ROUND((G49*H49)+G49,0)</f>
-        <v>5999</v>
+        <v>7500</v>
       </c>
       <c r="J49">
         <f t="shared" si="1"/>
@@ -5521,7 +5645,7 @@
       </c>
       <c r="L49">
         <f t="shared" si="3"/>
-        <v>5999</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="50" spans="1:12">
@@ -6216,11 +6340,11 @@
         <v>7305.75</v>
       </c>
       <c r="H66" s="36">
-        <v>0.36859999999999998</v>
+        <v>0.27160000000000001</v>
       </c>
       <c r="I66" s="37">
         <f t="shared" si="7"/>
-        <v>9999</v>
+        <v>9290</v>
       </c>
       <c r="J66">
         <f t="shared" si="1"/>
@@ -6232,7 +6356,7 @@
       </c>
       <c r="L66">
         <f t="shared" si="3"/>
-        <v>9999</v>
+        <v>9290</v>
       </c>
     </row>
     <row r="67" spans="1:12">
@@ -6590,7 +6714,7 @@
         <v>15</v>
       </c>
       <c r="E76" s="45">
-        <v>35000</v>
+        <v>35760</v>
       </c>
       <c r="F76" s="20">
         <v>0</v>
@@ -6631,7 +6755,7 @@
         <v>15</v>
       </c>
       <c r="E77" s="46">
-        <v>63000</v>
+        <v>29810</v>
       </c>
       <c r="F77" s="20">
         <v>0</v>
@@ -6826,21 +6950,21 @@
         <v>15</v>
       </c>
       <c r="E82" s="19">
-        <v>40620</v>
+        <v>35760</v>
       </c>
       <c r="F82" s="20">
         <v>0</v>
       </c>
       <c r="G82" s="21">
         <f>E82*(1-F82)/20</f>
-        <v>2031</v>
+        <v>1788</v>
       </c>
       <c r="H82" s="22">
         <v>0.3</v>
       </c>
       <c r="I82" s="23">
         <f t="shared" ref="I82:I104" si="15">+ROUND((G82*H82)+G82,0)</f>
-        <v>2640</v>
+        <v>2324</v>
       </c>
       <c r="J82" t="str">
         <f t="shared" si="8"/>
@@ -6852,7 +6976,7 @@
       </c>
       <c r="L82">
         <f t="shared" si="10"/>
-        <v>2640</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="83" spans="1:12">
@@ -6869,21 +6993,21 @@
         <v>15</v>
       </c>
       <c r="E83" s="19">
-        <v>3930</v>
+        <v>3454</v>
       </c>
       <c r="F83" s="20">
         <v>0</v>
       </c>
       <c r="G83" s="21">
         <f t="shared" ref="G83:G97" si="16">E83*(1-F83)</f>
-        <v>3930</v>
+        <v>3454</v>
       </c>
       <c r="H83" s="22">
         <v>0.3</v>
       </c>
       <c r="I83" s="23">
         <f t="shared" si="15"/>
-        <v>5109</v>
+        <v>4490</v>
       </c>
       <c r="J83" t="str">
         <f t="shared" si="8"/>
@@ -6895,7 +7019,7 @@
       </c>
       <c r="L83">
         <f t="shared" si="10"/>
-        <v>5109</v>
+        <v>4490</v>
       </c>
     </row>
     <row r="84" spans="1:12">
@@ -6998,21 +7122,21 @@
         <v>15</v>
       </c>
       <c r="E86" s="19">
-        <v>25280</v>
+        <v>25700</v>
       </c>
       <c r="F86" s="20">
         <v>0</v>
       </c>
       <c r="G86" s="21">
         <f>E86*(1-F86)/20</f>
-        <v>1264</v>
+        <v>1285</v>
       </c>
       <c r="H86" s="22">
         <v>0.3</v>
       </c>
       <c r="I86" s="23">
         <f t="shared" si="15"/>
-        <v>1643</v>
+        <v>1671</v>
       </c>
       <c r="J86" t="str">
         <f t="shared" si="8"/>
@@ -7024,7 +7148,7 @@
       </c>
       <c r="L86">
         <f t="shared" si="10"/>
-        <v>1643</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="87" spans="1:12">
@@ -7041,21 +7165,21 @@
         <v>15</v>
       </c>
       <c r="E87" s="19">
-        <v>3870</v>
+        <v>3624</v>
       </c>
       <c r="F87" s="20">
         <v>0</v>
       </c>
       <c r="G87" s="21">
         <f t="shared" si="16"/>
-        <v>3870</v>
+        <v>3624</v>
       </c>
       <c r="H87" s="22">
         <v>0.3</v>
       </c>
       <c r="I87" s="23">
         <f t="shared" si="15"/>
-        <v>5031</v>
+        <v>4711</v>
       </c>
       <c r="J87" t="str">
         <f t="shared" si="8"/>
@@ -7067,7 +7191,7 @@
       </c>
       <c r="L87">
         <f t="shared" si="10"/>
-        <v>5031</v>
+        <v>4711</v>
       </c>
     </row>
     <row r="88" spans="1:12">
@@ -7342,21 +7466,21 @@
         <v>15</v>
       </c>
       <c r="E94" s="19">
-        <v>33132</v>
+        <v>33792</v>
       </c>
       <c r="F94" s="20">
         <v>0</v>
       </c>
       <c r="G94" s="21">
         <f>E94*(1-F94)/12</f>
-        <v>2761</v>
+        <v>2816</v>
       </c>
       <c r="H94" s="22">
-        <v>0.32919999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="15"/>
-        <v>3670</v>
+        <v>3661</v>
       </c>
       <c r="J94" t="str">
         <f t="shared" si="8"/>
@@ -7368,7 +7492,7 @@
       </c>
       <c r="L94">
         <f t="shared" si="10"/>
-        <v>3670</v>
+        <v>3661</v>
       </c>
     </row>
     <row r="95" spans="1:12">
@@ -7385,21 +7509,21 @@
         <v>15</v>
       </c>
       <c r="E95" s="19">
-        <v>33132</v>
+        <v>33792</v>
       </c>
       <c r="F95" s="20">
         <v>0</v>
       </c>
       <c r="G95" s="21">
         <f>E95*(1-F95)/12</f>
-        <v>2761</v>
+        <v>2816</v>
       </c>
       <c r="H95" s="22">
-        <v>0.32919999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="I95" s="23">
         <f t="shared" si="15"/>
-        <v>3670</v>
+        <v>3661</v>
       </c>
       <c r="J95" t="str">
         <f t="shared" si="8"/>
@@ -7411,7 +7535,7 @@
       </c>
       <c r="L95">
         <f t="shared" si="10"/>
-        <v>3670</v>
+        <v>3661</v>
       </c>
     </row>
     <row r="96" spans="1:12">
@@ -7729,21 +7853,21 @@
         <v>15</v>
       </c>
       <c r="E103" s="19">
-        <v>2740</v>
+        <v>2795</v>
       </c>
       <c r="F103" s="20">
         <v>0</v>
       </c>
       <c r="G103" s="21">
         <f>E103*(1-F103)</f>
-        <v>2740</v>
+        <v>2795</v>
       </c>
       <c r="H103" s="22">
         <v>0.3</v>
       </c>
       <c r="I103" s="23">
         <f t="shared" si="15"/>
-        <v>3562</v>
+        <v>3634</v>
       </c>
       <c r="J103" t="str">
         <f t="shared" si="8"/>
@@ -7755,7 +7879,7 @@
       </c>
       <c r="L103">
         <f t="shared" si="10"/>
-        <v>3562</v>
+        <v>3634</v>
       </c>
     </row>
     <row r="104" spans="1:12">
@@ -7772,21 +7896,21 @@
         <v>15</v>
       </c>
       <c r="E104" s="19">
-        <v>32880</v>
+        <v>33540</v>
       </c>
       <c r="F104" s="20">
         <v>0</v>
       </c>
       <c r="G104" s="21">
         <f>E104*(1-F104)/12</f>
-        <v>2740</v>
+        <v>2795</v>
       </c>
       <c r="H104" s="22">
         <v>0.3</v>
       </c>
       <c r="I104" s="23">
         <f t="shared" si="15"/>
-        <v>3562</v>
+        <v>3634</v>
       </c>
       <c r="J104" t="str">
         <f t="shared" si="8"/>
@@ -7798,7 +7922,7 @@
       </c>
       <c r="L104">
         <f t="shared" si="10"/>
-        <v>3562</v>
+        <v>3634</v>
       </c>
     </row>
     <row r="105" spans="1:12">
@@ -11234,21 +11358,21 @@
         <v>15</v>
       </c>
       <c r="E189" s="19">
-        <v>14508</v>
+        <v>15996</v>
       </c>
       <c r="F189" s="20">
         <v>0</v>
       </c>
       <c r="G189" s="21">
         <f>E189*(1-F189)/12</f>
-        <v>1209</v>
+        <v>1333</v>
       </c>
       <c r="H189" s="22">
         <v>0.45</v>
       </c>
       <c r="I189" s="23">
         <f t="shared" si="26"/>
-        <v>1753</v>
+        <v>1933</v>
       </c>
       <c r="J189" t="str">
         <f t="shared" si="19"/>
@@ -11260,7 +11384,7 @@
       </c>
       <c r="L189">
         <f t="shared" si="21"/>
-        <v>1753</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="190" spans="1:12">
@@ -11320,21 +11444,21 @@
         <v>15</v>
       </c>
       <c r="E191" s="19">
-        <v>14500</v>
+        <v>14925</v>
       </c>
       <c r="F191" s="20">
         <v>0</v>
       </c>
       <c r="G191" s="21">
         <f>E191*(1-F191)/25</f>
-        <v>580</v>
+        <v>597</v>
       </c>
       <c r="H191" s="22">
         <v>0.45</v>
       </c>
       <c r="I191" s="23">
         <f t="shared" si="26"/>
-        <v>841</v>
+        <v>866</v>
       </c>
       <c r="J191" t="str">
         <f t="shared" si="19"/>
@@ -11346,7 +11470,7 @@
       </c>
       <c r="L191">
         <f t="shared" si="21"/>
-        <v>841</v>
+        <v>866</v>
       </c>
     </row>
     <row r="192" spans="1:12">
@@ -11363,21 +11487,21 @@
         <v>15</v>
       </c>
       <c r="E192" s="19">
-        <v>10980</v>
+        <v>12108</v>
       </c>
       <c r="F192" s="20">
         <v>0</v>
       </c>
       <c r="G192" s="21">
         <f>E192*(1-F192)/12</f>
-        <v>915</v>
+        <v>1009</v>
       </c>
       <c r="H192" s="22">
         <v>0.45</v>
       </c>
       <c r="I192" s="23">
         <f t="shared" si="26"/>
-        <v>1327</v>
+        <v>1463</v>
       </c>
       <c r="J192" t="str">
         <f t="shared" si="19"/>
@@ -11389,7 +11513,7 @@
       </c>
       <c r="L192">
         <f t="shared" si="21"/>
-        <v>1327</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="193" spans="1:12">
@@ -11406,21 +11530,21 @@
         <v>15</v>
       </c>
       <c r="E193" s="19">
-        <v>20436</v>
+        <v>22536</v>
       </c>
       <c r="F193" s="20">
         <v>0</v>
       </c>
       <c r="G193" s="21">
         <f>E193*(1-F193)/12</f>
-        <v>1703</v>
+        <v>1878</v>
       </c>
       <c r="H193" s="22">
         <v>0.45</v>
       </c>
       <c r="I193" s="23">
         <f t="shared" si="26"/>
-        <v>2469</v>
+        <v>2723</v>
       </c>
       <c r="J193" t="str">
         <f t="shared" si="19"/>
@@ -11432,7 +11556,7 @@
       </c>
       <c r="L193">
         <f t="shared" si="21"/>
-        <v>2469</v>
+        <v>2723</v>
       </c>
     </row>
     <row r="194" spans="1:12">
@@ -11449,21 +11573,21 @@
         <v>15</v>
       </c>
       <c r="E194" s="19">
-        <v>1184</v>
+        <v>1514</v>
       </c>
       <c r="F194" s="20">
         <v>0</v>
       </c>
       <c r="G194" s="21">
         <f>E194*(1-F194)</f>
-        <v>1184</v>
+        <v>1514</v>
       </c>
       <c r="H194" s="22">
         <v>0.45</v>
       </c>
       <c r="I194" s="23">
         <f t="shared" si="26"/>
-        <v>1717</v>
+        <v>2195</v>
       </c>
       <c r="J194" t="str">
         <f t="shared" si="19"/>
@@ -11475,7 +11599,7 @@
       </c>
       <c r="L194">
         <f t="shared" si="21"/>
-        <v>1717</v>
+        <v>2195</v>
       </c>
     </row>
     <row r="195" spans="1:12">
@@ -11492,21 +11616,21 @@
         <v>15</v>
       </c>
       <c r="E195" s="19">
-        <v>9828</v>
+        <v>10512</v>
       </c>
       <c r="F195" s="20">
         <v>0</v>
       </c>
       <c r="G195" s="21">
         <f t="shared" ref="G195:G205" si="27">E195*(1-F195)/12</f>
-        <v>819</v>
+        <v>876</v>
       </c>
       <c r="H195" s="22">
         <v>0.45</v>
       </c>
       <c r="I195" s="23">
         <f t="shared" si="26"/>
-        <v>1188</v>
+        <v>1270</v>
       </c>
       <c r="J195" t="str">
         <f t="shared" si="19"/>
@@ -11518,7 +11642,7 @@
       </c>
       <c r="L195">
         <f t="shared" si="21"/>
-        <v>1188</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="196" spans="1:12">
@@ -11535,21 +11659,21 @@
         <v>15</v>
       </c>
       <c r="E196" s="19">
-        <v>10992</v>
+        <v>13068</v>
       </c>
       <c r="F196" s="20">
         <v>0</v>
       </c>
       <c r="G196" s="21">
         <f t="shared" si="27"/>
-        <v>916</v>
+        <v>1089</v>
       </c>
       <c r="H196" s="22">
         <v>0.45</v>
       </c>
       <c r="I196" s="23">
         <f t="shared" si="26"/>
-        <v>1328</v>
+        <v>1579</v>
       </c>
       <c r="J196" t="str">
         <f t="shared" si="19"/>
@@ -11561,7 +11685,7 @@
       </c>
       <c r="L196">
         <f t="shared" si="21"/>
-        <v>1328</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="197" spans="1:12">
@@ -11578,21 +11702,21 @@
         <v>15</v>
       </c>
       <c r="E197" s="19">
-        <v>9048</v>
+        <v>10452</v>
       </c>
       <c r="F197" s="20">
         <v>0</v>
       </c>
       <c r="G197" s="21">
         <f t="shared" si="27"/>
-        <v>754</v>
+        <v>871</v>
       </c>
       <c r="H197" s="22">
         <v>0.45</v>
       </c>
       <c r="I197" s="23">
         <f t="shared" si="26"/>
-        <v>1093</v>
+        <v>1263</v>
       </c>
       <c r="J197" t="str">
         <f t="shared" si="19"/>
@@ -11604,7 +11728,7 @@
       </c>
       <c r="L197">
         <f t="shared" si="21"/>
-        <v>1093</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="198" spans="1:12">
@@ -11621,21 +11745,21 @@
         <v>15</v>
       </c>
       <c r="E198" s="19">
-        <v>8340</v>
+        <v>9636</v>
       </c>
       <c r="F198" s="20">
         <v>0</v>
       </c>
       <c r="G198" s="21">
         <f t="shared" si="27"/>
-        <v>695</v>
+        <v>803</v>
       </c>
       <c r="H198" s="22">
         <v>0.45</v>
       </c>
       <c r="I198" s="23">
         <f t="shared" si="26"/>
-        <v>1008</v>
+        <v>1164</v>
       </c>
       <c r="J198" t="str">
         <f t="shared" ref="J198:J261" si="28">IF(ISNUMBER(A198), IF(C198=1032, A198, "00" &amp; A198 &amp; "." &amp; C198), "")</f>
@@ -11647,7 +11771,7 @@
       </c>
       <c r="L198">
         <f t="shared" ref="L198:L261" si="30">IF(J198="","",I198)</f>
-        <v>1008</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="199" spans="1:12">
@@ -11664,21 +11788,21 @@
         <v>15</v>
       </c>
       <c r="E199" s="19">
-        <v>11712</v>
+        <v>12528</v>
       </c>
       <c r="F199" s="20">
         <v>0</v>
       </c>
       <c r="G199" s="21">
         <f t="shared" si="27"/>
-        <v>976</v>
+        <v>1044</v>
       </c>
       <c r="H199" s="22">
         <v>0.45</v>
       </c>
       <c r="I199" s="23">
         <f t="shared" si="26"/>
-        <v>1415</v>
+        <v>1514</v>
       </c>
       <c r="J199" t="str">
         <f t="shared" si="28"/>
@@ -11690,7 +11814,7 @@
       </c>
       <c r="L199">
         <f t="shared" si="30"/>
-        <v>1415</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="200" spans="1:12">
@@ -11707,21 +11831,21 @@
         <v>15</v>
       </c>
       <c r="E200" s="19">
-        <v>10200</v>
+        <v>11220</v>
       </c>
       <c r="F200" s="20">
         <v>0</v>
       </c>
       <c r="G200" s="21">
         <f t="shared" si="27"/>
-        <v>850</v>
+        <v>935</v>
       </c>
       <c r="H200" s="22">
         <v>0.45</v>
       </c>
       <c r="I200" s="23">
         <f t="shared" si="26"/>
-        <v>1233</v>
+        <v>1356</v>
       </c>
       <c r="J200" t="str">
         <f t="shared" si="28"/>
@@ -11733,7 +11857,7 @@
       </c>
       <c r="L200">
         <f t="shared" si="30"/>
-        <v>1233</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="201" spans="1:12">
@@ -11750,21 +11874,21 @@
         <v>15</v>
       </c>
       <c r="E201" s="19">
-        <v>10188</v>
+        <v>11208</v>
       </c>
       <c r="F201" s="20">
         <v>0</v>
       </c>
       <c r="G201" s="21">
         <f t="shared" si="27"/>
-        <v>849</v>
+        <v>934</v>
       </c>
       <c r="H201" s="22">
         <v>0.45</v>
       </c>
       <c r="I201" s="23">
         <f t="shared" si="26"/>
-        <v>1231</v>
+        <v>1354</v>
       </c>
       <c r="J201" t="str">
         <f t="shared" si="28"/>
@@ -11776,7 +11900,7 @@
       </c>
       <c r="L201">
         <f t="shared" si="30"/>
-        <v>1231</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="202" spans="1:12">
@@ -11793,21 +11917,21 @@
         <v>15</v>
       </c>
       <c r="E202" s="19">
-        <v>10992</v>
+        <v>11760</v>
       </c>
       <c r="F202" s="20">
         <v>0</v>
       </c>
       <c r="G202" s="21">
         <f t="shared" si="27"/>
-        <v>916</v>
+        <v>980</v>
       </c>
       <c r="H202" s="22">
         <v>0.45</v>
       </c>
       <c r="I202" s="23">
         <f t="shared" si="26"/>
-        <v>1328</v>
+        <v>1421</v>
       </c>
       <c r="J202" t="str">
         <f t="shared" si="28"/>
@@ -11819,7 +11943,7 @@
       </c>
       <c r="L202">
         <f t="shared" si="30"/>
-        <v>1328</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="203" spans="1:12">
@@ -11836,21 +11960,21 @@
         <v>15</v>
       </c>
       <c r="E203" s="19">
-        <v>11628</v>
+        <v>13944</v>
       </c>
       <c r="F203" s="20">
         <v>0</v>
       </c>
       <c r="G203" s="21">
         <f t="shared" si="27"/>
-        <v>969</v>
+        <v>1162</v>
       </c>
       <c r="H203" s="22">
         <v>0.45</v>
       </c>
       <c r="I203" s="23">
         <f>+ROUND((G203*H203)+G203,0)</f>
-        <v>1405</v>
+        <v>1685</v>
       </c>
       <c r="J203" t="str">
         <f t="shared" si="28"/>
@@ -11862,7 +11986,7 @@
       </c>
       <c r="L203">
         <f t="shared" si="30"/>
-        <v>1405</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="204" spans="1:12">
@@ -11879,21 +12003,21 @@
         <v>15</v>
       </c>
       <c r="E204" s="19">
-        <v>16080</v>
+        <v>18960</v>
       </c>
       <c r="F204" s="20">
         <v>0</v>
       </c>
       <c r="G204" s="21">
         <f t="shared" si="27"/>
-        <v>1340</v>
+        <v>1580</v>
       </c>
       <c r="H204" s="22">
         <v>0.45</v>
       </c>
       <c r="I204" s="23">
         <f t="shared" si="26"/>
-        <v>1943</v>
+        <v>2291</v>
       </c>
       <c r="J204" t="str">
         <f t="shared" si="28"/>
@@ -11905,7 +12029,7 @@
       </c>
       <c r="L204">
         <f t="shared" si="30"/>
-        <v>1943</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="205" spans="1:12">
@@ -11922,21 +12046,21 @@
         <v>15</v>
       </c>
       <c r="E205" s="19">
-        <v>13092</v>
+        <v>14580</v>
       </c>
       <c r="F205" s="20">
         <v>0</v>
       </c>
       <c r="G205" s="21">
         <f t="shared" si="27"/>
-        <v>1091</v>
+        <v>1215</v>
       </c>
       <c r="H205" s="22">
         <v>0.45</v>
       </c>
       <c r="I205" s="23">
         <f t="shared" si="26"/>
-        <v>1582</v>
+        <v>1762</v>
       </c>
       <c r="J205" t="str">
         <f t="shared" si="28"/>
@@ -11948,7 +12072,7 @@
       </c>
       <c r="L205">
         <f t="shared" si="30"/>
-        <v>1582</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="206" spans="1:12">
@@ -11965,21 +12089,21 @@
         <v>15</v>
       </c>
       <c r="E206" s="19">
-        <v>31830</v>
+        <v>34422</v>
       </c>
       <c r="F206" s="20">
         <v>0</v>
       </c>
       <c r="G206" s="21">
         <f>E206*(1-F206)/6</f>
-        <v>5305</v>
+        <v>5737</v>
       </c>
       <c r="H206" s="22">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="I206" s="23">
         <f t="shared" si="26"/>
-        <v>7692</v>
+        <v>7458</v>
       </c>
       <c r="J206" t="str">
         <f t="shared" si="28"/>
@@ -11991,7 +12115,7 @@
       </c>
       <c r="L206">
         <f t="shared" si="30"/>
-        <v>7692</v>
+        <v>7458</v>
       </c>
     </row>
     <row r="207" spans="1:12">
@@ -12008,21 +12132,21 @@
         <v>15</v>
       </c>
       <c r="E207" s="19">
-        <v>30072</v>
+        <v>33474</v>
       </c>
       <c r="F207" s="20">
         <v>0</v>
       </c>
       <c r="G207" s="21">
         <f>E207*(1-F207)/6</f>
-        <v>5012</v>
+        <v>5579</v>
       </c>
       <c r="H207" s="22">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="I207" s="23">
         <f t="shared" si="26"/>
-        <v>7267</v>
+        <v>7253</v>
       </c>
       <c r="J207" t="str">
         <f t="shared" si="28"/>
@@ -12034,7 +12158,7 @@
       </c>
       <c r="L207">
         <f t="shared" si="30"/>
-        <v>7267</v>
+        <v>7253</v>
       </c>
     </row>
     <row r="208" spans="1:12">
@@ -12051,21 +12175,21 @@
         <v>15</v>
       </c>
       <c r="E208" s="19">
-        <v>15624</v>
+        <v>17184</v>
       </c>
       <c r="F208" s="20">
         <v>0</v>
       </c>
       <c r="G208" s="21">
         <f>E208*(1-F208)/24</f>
-        <v>651</v>
+        <v>716</v>
       </c>
       <c r="H208" s="22">
         <v>0.45</v>
       </c>
       <c r="I208" s="23">
         <f t="shared" si="26"/>
-        <v>944</v>
+        <v>1038</v>
       </c>
       <c r="J208" t="str">
         <f t="shared" si="28"/>
@@ -12077,7 +12201,7 @@
       </c>
       <c r="L208">
         <f t="shared" si="30"/>
-        <v>944</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="209" spans="1:12">
@@ -12094,21 +12218,21 @@
         <v>15</v>
       </c>
       <c r="E209" s="19">
-        <v>7308</v>
+        <v>8436</v>
       </c>
       <c r="F209" s="20">
         <v>0</v>
       </c>
       <c r="G209" s="21">
         <f>E209*(1-F209)/12</f>
-        <v>609</v>
+        <v>703</v>
       </c>
       <c r="H209" s="22">
         <v>0.45</v>
       </c>
       <c r="I209" s="23">
         <f t="shared" si="26"/>
-        <v>883</v>
+        <v>1019</v>
       </c>
       <c r="J209" t="str">
         <f t="shared" si="28"/>
@@ -12120,7 +12244,7 @@
       </c>
       <c r="L209">
         <f t="shared" si="30"/>
-        <v>883</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="210" spans="1:12">
@@ -12137,21 +12261,21 @@
         <v>15</v>
       </c>
       <c r="E210" s="19">
-        <v>13560</v>
+        <v>14232</v>
       </c>
       <c r="F210" s="20">
         <v>0</v>
       </c>
       <c r="G210" s="21">
         <f t="shared" ref="G210:G223" si="31">E210*(1-F210)/12</f>
-        <v>1130</v>
+        <v>1186</v>
       </c>
       <c r="H210" s="22">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="I210" s="23">
         <f t="shared" si="26"/>
-        <v>1695</v>
+        <v>1720</v>
       </c>
       <c r="J210" t="str">
         <f t="shared" si="28"/>
@@ -12163,7 +12287,7 @@
       </c>
       <c r="L210">
         <f t="shared" si="30"/>
-        <v>1695</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="211" spans="1:12">
@@ -12180,21 +12304,21 @@
         <v>15</v>
       </c>
       <c r="E211" s="19">
-        <v>19504</v>
+        <v>20480</v>
       </c>
       <c r="F211" s="20">
         <v>0</v>
       </c>
       <c r="G211" s="21">
-        <f t="shared" si="31"/>
-        <v>1625.3333333333333</v>
+        <f>E211*(1-F211)/8</f>
+        <v>2560</v>
       </c>
       <c r="H211" s="22">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="I211" s="23">
         <f t="shared" si="26"/>
-        <v>2438</v>
+        <v>3712</v>
       </c>
       <c r="J211" t="str">
         <f t="shared" si="28"/>
@@ -12206,7 +12330,7 @@
       </c>
       <c r="L211">
         <f t="shared" si="30"/>
-        <v>2438</v>
+        <v>3712</v>
       </c>
     </row>
     <row r="212" spans="1:12">
@@ -12223,21 +12347,21 @@
         <v>15</v>
       </c>
       <c r="E212" s="19">
-        <v>17508</v>
+        <v>18384</v>
       </c>
       <c r="F212" s="20">
         <v>0</v>
       </c>
       <c r="G212" s="21">
         <f t="shared" si="31"/>
-        <v>1459</v>
+        <v>1532</v>
       </c>
       <c r="H212" s="22">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="I212" s="23">
         <f t="shared" si="26"/>
-        <v>2189</v>
+        <v>2221</v>
       </c>
       <c r="J212" t="str">
         <f t="shared" si="28"/>
@@ -12249,7 +12373,7 @@
       </c>
       <c r="L212">
         <f t="shared" si="30"/>
-        <v>2189</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="213" spans="1:12">
@@ -12266,21 +12390,21 @@
         <v>15</v>
       </c>
       <c r="E213" s="19">
-        <v>3876</v>
+        <v>3180</v>
       </c>
       <c r="F213" s="20">
         <v>0</v>
       </c>
       <c r="G213" s="21">
         <f t="shared" si="31"/>
-        <v>323</v>
+        <v>265</v>
       </c>
       <c r="H213" s="22">
         <v>0.45</v>
       </c>
       <c r="I213" s="23">
         <f t="shared" si="26"/>
-        <v>468</v>
+        <v>384</v>
       </c>
       <c r="J213" t="str">
         <f t="shared" si="28"/>
@@ -12292,7 +12416,7 @@
       </c>
       <c r="L213">
         <f t="shared" si="30"/>
-        <v>468</v>
+        <v>384</v>
       </c>
     </row>
     <row r="214" spans="1:12">
@@ -12309,21 +12433,21 @@
         <v>15</v>
       </c>
       <c r="E214" s="19">
-        <v>3876</v>
+        <v>3180</v>
       </c>
       <c r="F214" s="20">
         <v>0</v>
       </c>
       <c r="G214" s="21">
         <f t="shared" si="31"/>
-        <v>323</v>
+        <v>265</v>
       </c>
       <c r="H214" s="22">
         <v>0.45</v>
       </c>
       <c r="I214" s="23">
         <f t="shared" si="26"/>
-        <v>468</v>
+        <v>384</v>
       </c>
       <c r="J214" t="str">
         <f t="shared" si="28"/>
@@ -12335,7 +12459,7 @@
       </c>
       <c r="L214">
         <f t="shared" si="30"/>
-        <v>468</v>
+        <v>384</v>
       </c>
     </row>
     <row r="215" spans="1:12">
@@ -12352,21 +12476,21 @@
         <v>15</v>
       </c>
       <c r="E215" s="19">
-        <v>3876</v>
+        <v>3180</v>
       </c>
       <c r="F215" s="20">
         <v>0</v>
       </c>
       <c r="G215" s="21">
         <f t="shared" si="31"/>
-        <v>323</v>
+        <v>265</v>
       </c>
       <c r="H215" s="22">
         <v>0.45</v>
       </c>
       <c r="I215" s="23">
         <f t="shared" si="26"/>
-        <v>468</v>
+        <v>384</v>
       </c>
       <c r="J215" t="str">
         <f t="shared" si="28"/>
@@ -12378,7 +12502,7 @@
       </c>
       <c r="L215">
         <f t="shared" si="30"/>
-        <v>468</v>
+        <v>384</v>
       </c>
     </row>
     <row r="216" spans="1:12">
@@ -12395,21 +12519,21 @@
         <v>15</v>
       </c>
       <c r="E216" s="19">
-        <v>3876</v>
+        <v>3180</v>
       </c>
       <c r="F216" s="20">
         <v>0</v>
       </c>
       <c r="G216" s="21">
-        <f>E216*(1-F216)/6</f>
-        <v>646</v>
+        <f>E216*(1-F216)/12</f>
+        <v>265</v>
       </c>
       <c r="H216" s="22">
         <v>0.45</v>
       </c>
       <c r="I216" s="23">
         <f t="shared" si="26"/>
-        <v>937</v>
+        <v>384</v>
       </c>
       <c r="J216" t="str">
         <f t="shared" si="28"/>
@@ -12421,7 +12545,7 @@
       </c>
       <c r="L216">
         <f t="shared" si="30"/>
-        <v>937</v>
+        <v>384</v>
       </c>
     </row>
     <row r="217" spans="1:12">
@@ -12438,21 +12562,21 @@
         <v>15</v>
       </c>
       <c r="E217" s="19">
-        <v>3204</v>
+        <v>3636</v>
       </c>
       <c r="F217" s="20">
         <v>0</v>
       </c>
       <c r="G217" s="21">
         <f t="shared" si="31"/>
-        <v>267</v>
+        <v>303</v>
       </c>
       <c r="H217" s="22">
         <v>0.45</v>
       </c>
       <c r="I217" s="23">
         <f t="shared" si="26"/>
-        <v>387</v>
+        <v>439</v>
       </c>
       <c r="J217" t="str">
         <f t="shared" si="28"/>
@@ -12464,7 +12588,7 @@
       </c>
       <c r="L217">
         <f t="shared" si="30"/>
-        <v>387</v>
+        <v>439</v>
       </c>
     </row>
     <row r="218" spans="1:12">
@@ -12481,21 +12605,21 @@
         <v>15</v>
       </c>
       <c r="E218" s="19">
-        <v>3204</v>
+        <v>3636</v>
       </c>
       <c r="F218" s="20">
         <v>0</v>
       </c>
       <c r="G218" s="21">
         <f t="shared" si="31"/>
-        <v>267</v>
+        <v>303</v>
       </c>
       <c r="H218" s="22">
         <v>0.45</v>
       </c>
       <c r="I218" s="23">
         <f t="shared" si="26"/>
-        <v>387</v>
+        <v>439</v>
       </c>
       <c r="J218" t="str">
         <f t="shared" si="28"/>
@@ -12507,7 +12631,7 @@
       </c>
       <c r="L218">
         <f t="shared" si="30"/>
-        <v>387</v>
+        <v>439</v>
       </c>
     </row>
     <row r="219" spans="1:12">
@@ -12524,21 +12648,21 @@
         <v>15</v>
       </c>
       <c r="E219" s="19">
-        <v>3204</v>
+        <v>3636</v>
       </c>
       <c r="F219" s="20">
         <v>0</v>
       </c>
       <c r="G219" s="21">
         <f t="shared" si="31"/>
-        <v>267</v>
+        <v>303</v>
       </c>
       <c r="H219" s="22">
         <v>0.45</v>
       </c>
       <c r="I219" s="23">
         <f t="shared" si="26"/>
-        <v>387</v>
+        <v>439</v>
       </c>
       <c r="J219" t="str">
         <f t="shared" si="28"/>
@@ -12550,7 +12674,7 @@
       </c>
       <c r="L219">
         <f t="shared" si="30"/>
-        <v>387</v>
+        <v>439</v>
       </c>
     </row>
     <row r="220" spans="1:12">
@@ -12567,21 +12691,21 @@
         <v>15</v>
       </c>
       <c r="E220" s="19">
-        <v>3204</v>
+        <v>3636</v>
       </c>
       <c r="F220" s="20">
         <v>0</v>
       </c>
       <c r="G220" s="21">
         <f t="shared" si="31"/>
-        <v>267</v>
+        <v>303</v>
       </c>
       <c r="H220" s="22">
         <v>0.45</v>
       </c>
       <c r="I220" s="23">
         <f t="shared" si="26"/>
-        <v>387</v>
+        <v>439</v>
       </c>
       <c r="J220" t="str">
         <f t="shared" si="28"/>
@@ -12593,7 +12717,7 @@
       </c>
       <c r="L220">
         <f t="shared" si="30"/>
-        <v>387</v>
+        <v>439</v>
       </c>
     </row>
     <row r="221" spans="1:12">
@@ -12610,21 +12734,21 @@
         <v>15</v>
       </c>
       <c r="E221" s="19">
-        <v>3204</v>
+        <v>3636</v>
       </c>
       <c r="F221" s="20">
         <v>0</v>
       </c>
       <c r="G221" s="21">
         <f t="shared" si="31"/>
-        <v>267</v>
+        <v>303</v>
       </c>
       <c r="H221" s="22">
         <v>0.45</v>
       </c>
       <c r="I221" s="23">
         <f t="shared" si="26"/>
-        <v>387</v>
+        <v>439</v>
       </c>
       <c r="J221" t="str">
         <f t="shared" si="28"/>
@@ -12636,7 +12760,7 @@
       </c>
       <c r="L221">
         <f t="shared" si="30"/>
-        <v>387</v>
+        <v>439</v>
       </c>
     </row>
     <row r="222" spans="1:12">
@@ -12653,21 +12777,21 @@
         <v>15</v>
       </c>
       <c r="E222" s="19">
-        <v>3204</v>
+        <v>3636</v>
       </c>
       <c r="F222" s="20">
         <v>0</v>
       </c>
       <c r="G222" s="21">
         <f t="shared" si="31"/>
-        <v>267</v>
+        <v>303</v>
       </c>
       <c r="H222" s="22">
         <v>0.45</v>
       </c>
       <c r="I222" s="23">
         <f t="shared" ref="I222:I250" si="32">+ROUND((G222*H222)+G222,0)</f>
-        <v>387</v>
+        <v>439</v>
       </c>
       <c r="J222" t="str">
         <f t="shared" si="28"/>
@@ -12679,7 +12803,7 @@
       </c>
       <c r="L222">
         <f t="shared" si="30"/>
-        <v>387</v>
+        <v>439</v>
       </c>
     </row>
     <row r="223" spans="1:12">
@@ -12696,21 +12820,21 @@
         <v>15</v>
       </c>
       <c r="E223" s="19">
-        <v>3204</v>
+        <v>3636</v>
       </c>
       <c r="F223" s="20">
         <v>0</v>
       </c>
       <c r="G223" s="21">
         <f t="shared" si="31"/>
-        <v>267</v>
+        <v>303</v>
       </c>
       <c r="H223" s="22">
         <v>0.45</v>
       </c>
       <c r="I223" s="23">
         <f t="shared" si="32"/>
-        <v>387</v>
+        <v>439</v>
       </c>
       <c r="J223" t="str">
         <f t="shared" si="28"/>
@@ -12722,7 +12846,7 @@
       </c>
       <c r="L223">
         <f t="shared" si="30"/>
-        <v>387</v>
+        <v>439</v>
       </c>
     </row>
     <row r="224" spans="1:12">
@@ -12739,21 +12863,21 @@
         <v>15</v>
       </c>
       <c r="E224" s="19">
-        <v>25621</v>
+        <v>30493</v>
       </c>
       <c r="F224" s="20">
         <v>0</v>
       </c>
       <c r="G224" s="21">
         <f>E224*(1-F224)</f>
-        <v>25621</v>
+        <v>30493</v>
       </c>
       <c r="H224" s="22">
         <v>0.45</v>
       </c>
       <c r="I224" s="23">
         <f t="shared" si="32"/>
-        <v>37150</v>
+        <v>44215</v>
       </c>
       <c r="J224" t="str">
         <f t="shared" si="28"/>
@@ -12765,7 +12889,7 @@
       </c>
       <c r="L224">
         <f t="shared" si="30"/>
-        <v>37150</v>
+        <v>44215</v>
       </c>
     </row>
     <row r="225" spans="1:12">
@@ -12782,21 +12906,21 @@
         <v>15</v>
       </c>
       <c r="E225" s="19">
-        <v>17800</v>
+        <v>19440</v>
       </c>
       <c r="F225" s="20">
         <v>0</v>
       </c>
       <c r="G225" s="21">
         <f>E225*(1-F225)/10</f>
-        <v>1780</v>
+        <v>1944</v>
       </c>
       <c r="H225" s="22">
         <v>0.45</v>
       </c>
       <c r="I225" s="23">
         <f t="shared" si="32"/>
-        <v>2581</v>
+        <v>2819</v>
       </c>
       <c r="J225" t="str">
         <f t="shared" si="28"/>
@@ -12808,7 +12932,7 @@
       </c>
       <c r="L225">
         <f t="shared" si="30"/>
-        <v>2581</v>
+        <v>2819</v>
       </c>
     </row>
     <row r="226" spans="1:12">
@@ -12825,21 +12949,21 @@
         <v>15</v>
       </c>
       <c r="E226" s="19">
-        <v>17800</v>
+        <v>19440</v>
       </c>
       <c r="F226" s="20">
         <v>0</v>
       </c>
       <c r="G226" s="21">
         <f t="shared" ref="G226:G231" si="33">E226*(1-F226)/10</f>
-        <v>1780</v>
+        <v>1944</v>
       </c>
       <c r="H226" s="22">
         <v>0.45</v>
       </c>
       <c r="I226" s="23">
         <f t="shared" si="32"/>
-        <v>2581</v>
+        <v>2819</v>
       </c>
       <c r="J226" t="str">
         <f t="shared" si="28"/>
@@ -12851,7 +12975,7 @@
       </c>
       <c r="L226">
         <f t="shared" si="30"/>
-        <v>2581</v>
+        <v>2819</v>
       </c>
     </row>
     <row r="227" spans="1:12">
@@ -12868,21 +12992,21 @@
         <v>15</v>
       </c>
       <c r="E227" s="19">
-        <v>17800</v>
+        <v>19440</v>
       </c>
       <c r="F227" s="20">
         <v>0</v>
       </c>
       <c r="G227" s="21">
         <f t="shared" si="33"/>
-        <v>1780</v>
+        <v>1944</v>
       </c>
       <c r="H227" s="22">
         <v>0.45</v>
       </c>
       <c r="I227" s="23">
         <f t="shared" si="32"/>
-        <v>2581</v>
+        <v>2819</v>
       </c>
       <c r="J227" t="str">
         <f t="shared" si="28"/>
@@ -12894,7 +13018,7 @@
       </c>
       <c r="L227">
         <f t="shared" si="30"/>
-        <v>2581</v>
+        <v>2819</v>
       </c>
     </row>
     <row r="228" spans="1:12">
@@ -12911,21 +13035,21 @@
         <v>15</v>
       </c>
       <c r="E228" s="19">
-        <v>18690</v>
+        <v>19440</v>
       </c>
       <c r="F228" s="20">
         <v>0</v>
       </c>
       <c r="G228" s="21">
         <f t="shared" si="33"/>
-        <v>1869</v>
+        <v>1944</v>
       </c>
       <c r="H228" s="22">
         <v>0.45</v>
       </c>
       <c r="I228" s="23">
         <f t="shared" si="32"/>
-        <v>2710</v>
+        <v>2819</v>
       </c>
       <c r="J228" t="str">
         <f t="shared" si="28"/>
@@ -12937,7 +13061,7 @@
       </c>
       <c r="L228">
         <f t="shared" si="30"/>
-        <v>2710</v>
+        <v>2819</v>
       </c>
     </row>
     <row r="229" spans="1:12">
@@ -12954,21 +13078,21 @@
         <v>15</v>
       </c>
       <c r="E229" s="19">
-        <v>18690</v>
+        <v>19440</v>
       </c>
       <c r="F229" s="20">
         <v>0</v>
       </c>
       <c r="G229" s="21">
         <f t="shared" si="33"/>
-        <v>1869</v>
+        <v>1944</v>
       </c>
       <c r="H229" s="22">
         <v>0.45</v>
       </c>
       <c r="I229" s="23">
         <f t="shared" si="32"/>
-        <v>2710</v>
+        <v>2819</v>
       </c>
       <c r="J229" t="str">
         <f t="shared" si="28"/>
@@ -12980,7 +13104,7 @@
       </c>
       <c r="L229">
         <f t="shared" si="30"/>
-        <v>2710</v>
+        <v>2819</v>
       </c>
     </row>
     <row r="230" spans="1:12">
@@ -12997,21 +13121,21 @@
         <v>15</v>
       </c>
       <c r="E230" s="19">
-        <v>18690</v>
+        <v>19440</v>
       </c>
       <c r="F230" s="20">
         <v>0</v>
       </c>
       <c r="G230" s="21">
         <f t="shared" si="33"/>
-        <v>1869</v>
+        <v>1944</v>
       </c>
       <c r="H230" s="22">
         <v>0.45</v>
       </c>
       <c r="I230" s="23">
         <f t="shared" si="32"/>
-        <v>2710</v>
+        <v>2819</v>
       </c>
       <c r="J230" t="str">
         <f t="shared" si="28"/>
@@ -13023,7 +13147,7 @@
       </c>
       <c r="L230">
         <f t="shared" si="30"/>
-        <v>2710</v>
+        <v>2819</v>
       </c>
     </row>
     <row r="231" spans="1:12">
@@ -13040,21 +13164,21 @@
         <v>15</v>
       </c>
       <c r="E231" s="19">
-        <v>18690</v>
+        <v>19440</v>
       </c>
       <c r="F231" s="20">
         <v>0</v>
       </c>
       <c r="G231" s="21">
         <f t="shared" si="33"/>
-        <v>1869</v>
+        <v>1944</v>
       </c>
       <c r="H231" s="22">
         <v>0.45</v>
       </c>
       <c r="I231" s="23">
         <f t="shared" si="32"/>
-        <v>2710</v>
+        <v>2819</v>
       </c>
       <c r="J231" t="str">
         <f t="shared" si="28"/>
@@ -13066,7 +13190,7 @@
       </c>
       <c r="L231">
         <f t="shared" si="30"/>
-        <v>2710</v>
+        <v>2819</v>
       </c>
     </row>
     <row r="232" spans="1:12">
@@ -13083,21 +13207,21 @@
         <v>15</v>
       </c>
       <c r="E232" s="19">
-        <v>18690</v>
+        <v>20508</v>
       </c>
       <c r="F232" s="20">
         <v>0</v>
       </c>
       <c r="G232" s="21">
         <f>E232*(1-F232)/12</f>
-        <v>1557.5</v>
+        <v>1709</v>
       </c>
       <c r="H232" s="22">
         <v>0.45</v>
       </c>
       <c r="I232" s="23">
         <f t="shared" si="32"/>
-        <v>2258</v>
+        <v>2478</v>
       </c>
       <c r="J232" t="str">
         <f t="shared" si="28"/>
@@ -13109,7 +13233,7 @@
       </c>
       <c r="L232">
         <f t="shared" si="30"/>
-        <v>2258</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="233" spans="1:12">
@@ -13126,21 +13250,21 @@
         <v>15</v>
       </c>
       <c r="E233" s="19">
-        <v>11112</v>
+        <v>12264</v>
       </c>
       <c r="F233" s="20">
         <v>0</v>
       </c>
       <c r="G233" s="21">
         <f>E233*(1-F233)/12</f>
-        <v>926</v>
+        <v>1022</v>
       </c>
       <c r="H233" s="22">
         <v>0.45</v>
       </c>
       <c r="I233" s="23">
         <f t="shared" si="32"/>
-        <v>1343</v>
+        <v>1482</v>
       </c>
       <c r="J233" t="str">
         <f t="shared" si="28"/>
@@ -13152,7 +13276,7 @@
       </c>
       <c r="L233">
         <f t="shared" si="30"/>
-        <v>1343</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="234" spans="1:12">
@@ -13169,21 +13293,21 @@
         <v>15</v>
       </c>
       <c r="E234" s="19">
-        <v>3967</v>
+        <v>3769</v>
       </c>
       <c r="F234" s="20">
         <v>0</v>
       </c>
       <c r="G234" s="21">
         <f>E234*(1-F234)</f>
-        <v>3967</v>
+        <v>3769</v>
       </c>
       <c r="H234" s="22">
         <v>0.45</v>
       </c>
       <c r="I234" s="23">
         <f t="shared" si="32"/>
-        <v>5752</v>
+        <v>5465</v>
       </c>
       <c r="J234" t="str">
         <f t="shared" si="28"/>
@@ -13195,7 +13319,7 @@
       </c>
       <c r="L234">
         <f t="shared" si="30"/>
-        <v>5752</v>
+        <v>5465</v>
       </c>
     </row>
     <row r="235" spans="1:12">
@@ -13212,21 +13336,21 @@
         <v>15</v>
       </c>
       <c r="E235" s="19">
-        <v>21888</v>
+        <v>25452</v>
       </c>
       <c r="F235" s="20">
         <v>0</v>
       </c>
       <c r="G235" s="21">
         <f>E235*(1-F235)/6</f>
-        <v>3648</v>
+        <v>4242</v>
       </c>
       <c r="H235" s="22">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="I235" s="23">
         <f t="shared" si="32"/>
-        <v>5290</v>
+        <v>5727</v>
       </c>
       <c r="J235" t="str">
         <f t="shared" si="28"/>
@@ -13238,7 +13362,7 @@
       </c>
       <c r="L235">
         <f t="shared" si="30"/>
-        <v>5290</v>
+        <v>5727</v>
       </c>
     </row>
     <row r="236" spans="1:12">
@@ -13255,21 +13379,21 @@
         <v>15</v>
       </c>
       <c r="E236" s="19">
-        <v>24930</v>
+        <v>25452</v>
       </c>
       <c r="F236" s="20">
         <v>0</v>
       </c>
       <c r="G236" s="21">
         <f>E236*(1-F236)/6</f>
-        <v>4155</v>
+        <v>4242</v>
       </c>
       <c r="H236" s="22">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="I236" s="23">
         <f t="shared" si="32"/>
-        <v>5402</v>
+        <v>5727</v>
       </c>
       <c r="J236" t="str">
         <f t="shared" si="28"/>
@@ -13281,7 +13405,7 @@
       </c>
       <c r="L236">
         <f t="shared" si="30"/>
-        <v>5402</v>
+        <v>5727</v>
       </c>
     </row>
     <row r="237" spans="1:12">
@@ -13298,21 +13422,21 @@
         <v>15</v>
       </c>
       <c r="E237" s="19">
-        <v>27910</v>
+        <v>29310</v>
       </c>
       <c r="F237" s="20">
         <v>0</v>
       </c>
       <c r="G237" s="21">
         <f>E237*(1-F237)/10</f>
-        <v>2791</v>
+        <v>2931</v>
       </c>
       <c r="H237" s="22">
-        <v>0.46899999999999997</v>
+        <v>0.45</v>
       </c>
       <c r="I237" s="23">
         <f t="shared" si="32"/>
-        <v>4100</v>
+        <v>4250</v>
       </c>
       <c r="J237" t="str">
         <f t="shared" si="28"/>
@@ -13324,7 +13448,7 @@
       </c>
       <c r="L237">
         <f t="shared" si="30"/>
-        <v>4100</v>
+        <v>4250</v>
       </c>
     </row>
     <row r="238" spans="1:12">
@@ -13341,21 +13465,21 @@
         <v>15</v>
       </c>
       <c r="E238" s="19">
-        <v>7800</v>
+        <v>8200</v>
       </c>
       <c r="F238" s="20">
         <v>0</v>
       </c>
       <c r="G238" s="21">
         <f>E238*(1-F238)/10</f>
-        <v>780</v>
+        <v>820</v>
       </c>
       <c r="H238" s="22">
         <v>0.46100000000000002</v>
       </c>
       <c r="I238" s="23">
         <f t="shared" si="32"/>
-        <v>1140</v>
+        <v>1198</v>
       </c>
       <c r="J238" t="str">
         <f t="shared" si="28"/>
@@ -13367,7 +13491,7 @@
       </c>
       <c r="L238">
         <f t="shared" si="30"/>
-        <v>1140</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="239" spans="1:12">
@@ -13384,21 +13508,21 @@
         <v>15</v>
       </c>
       <c r="E239" s="19">
-        <v>14340</v>
+        <v>13040</v>
       </c>
       <c r="F239" s="20">
         <v>0</v>
       </c>
       <c r="G239" s="21">
         <f>E239*(1-F239)/10</f>
-        <v>1434</v>
+        <v>1304</v>
       </c>
       <c r="H239" s="22">
         <v>0.45</v>
       </c>
       <c r="I239" s="23">
         <f t="shared" si="32"/>
-        <v>2079</v>
+        <v>1891</v>
       </c>
       <c r="J239" t="str">
         <f t="shared" si="28"/>
@@ -13410,7 +13534,7 @@
       </c>
       <c r="L239">
         <f t="shared" si="30"/>
-        <v>2079</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="240" spans="1:12">
@@ -13513,21 +13637,21 @@
         <v>15</v>
       </c>
       <c r="E242" s="19">
-        <v>6474</v>
+        <v>7206</v>
       </c>
       <c r="F242" s="20">
         <v>0</v>
       </c>
       <c r="G242" s="21">
         <f>E242*(1-F242)/6</f>
-        <v>1079</v>
+        <v>1201</v>
       </c>
       <c r="H242" s="22">
         <v>0.45</v>
       </c>
       <c r="I242" s="23">
         <f t="shared" si="32"/>
-        <v>1565</v>
+        <v>1741</v>
       </c>
       <c r="J242" t="str">
         <f t="shared" si="28"/>
@@ -13539,7 +13663,7 @@
       </c>
       <c r="L242">
         <f t="shared" si="30"/>
-        <v>1565</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="243" spans="1:12">
@@ -13599,21 +13723,21 @@
         <v>15</v>
       </c>
       <c r="E244" s="19">
-        <v>13320</v>
+        <v>12910</v>
       </c>
       <c r="F244" s="20">
         <v>0</v>
       </c>
       <c r="G244" s="21">
         <f>E244*(1-F244)/10</f>
-        <v>1332</v>
+        <v>1291</v>
       </c>
       <c r="H244" s="22">
         <v>0.45</v>
       </c>
       <c r="I244" s="23">
         <f t="shared" si="32"/>
-        <v>1931</v>
+        <v>1872</v>
       </c>
       <c r="J244" t="str">
         <f t="shared" si="28"/>
@@ -13625,7 +13749,7 @@
       </c>
       <c r="L244">
         <f t="shared" si="30"/>
-        <v>1931</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="245" spans="1:12">
@@ -13642,21 +13766,21 @@
         <v>15</v>
       </c>
       <c r="E245" s="19">
-        <v>26376</v>
+        <v>27696</v>
       </c>
       <c r="F245" s="20">
         <v>0</v>
       </c>
       <c r="G245" s="21">
         <f>E245*(1-F245)/12</f>
-        <v>2198</v>
+        <v>2308</v>
       </c>
       <c r="H245" s="22">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="I245" s="23">
         <f t="shared" si="32"/>
-        <v>3187</v>
+        <v>3000</v>
       </c>
       <c r="J245" t="str">
         <f t="shared" si="28"/>
@@ -13668,7 +13792,7 @@
       </c>
       <c r="L245">
         <f t="shared" si="30"/>
-        <v>3187</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="246" spans="1:12">
@@ -13685,21 +13809,21 @@
         <v>15</v>
       </c>
       <c r="E246" s="19">
-        <v>26376</v>
+        <v>27696</v>
       </c>
       <c r="F246" s="20">
         <v>0</v>
       </c>
       <c r="G246" s="21">
         <f t="shared" ref="G246:G255" si="34">E246*(1-F246)/12</f>
-        <v>2198</v>
+        <v>2308</v>
       </c>
       <c r="H246" s="22">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="I246" s="23">
         <f t="shared" si="32"/>
-        <v>3187</v>
+        <v>3000</v>
       </c>
       <c r="J246" t="str">
         <f t="shared" si="28"/>
@@ -13711,7 +13835,7 @@
       </c>
       <c r="L246">
         <f t="shared" si="30"/>
-        <v>3187</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="247" spans="1:12">
@@ -13728,21 +13852,21 @@
         <v>15</v>
       </c>
       <c r="E247" s="19">
-        <v>26376</v>
+        <v>27696</v>
       </c>
       <c r="F247" s="20">
         <v>0</v>
       </c>
       <c r="G247" s="21">
         <f t="shared" si="34"/>
-        <v>2198</v>
+        <v>2308</v>
       </c>
       <c r="H247" s="22">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="I247" s="23">
         <f t="shared" si="32"/>
-        <v>3187</v>
+        <v>3000</v>
       </c>
       <c r="J247" t="str">
         <f t="shared" si="28"/>
@@ -13754,7 +13878,7 @@
       </c>
       <c r="L247">
         <f t="shared" si="30"/>
-        <v>3187</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="248" spans="1:12">
@@ -13771,21 +13895,21 @@
         <v>15</v>
       </c>
       <c r="E248" s="19">
-        <v>10908</v>
+        <v>12000</v>
       </c>
       <c r="F248" s="20">
         <v>0</v>
       </c>
       <c r="G248" s="21">
         <f t="shared" si="34"/>
-        <v>909</v>
+        <v>1000</v>
       </c>
       <c r="H248" s="22">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="I248" s="23">
         <f t="shared" si="32"/>
-        <v>1318</v>
+        <v>1300</v>
       </c>
       <c r="J248" t="str">
         <f t="shared" si="28"/>
@@ -13797,7 +13921,7 @@
       </c>
       <c r="L248">
         <f t="shared" si="30"/>
-        <v>1318</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="249" spans="1:12">
@@ -13814,21 +13938,21 @@
         <v>15</v>
       </c>
       <c r="E249" s="19">
-        <v>12888</v>
+        <v>14184</v>
       </c>
       <c r="F249" s="20">
         <v>0</v>
       </c>
       <c r="G249" s="21">
         <f t="shared" si="34"/>
-        <v>1074</v>
+        <v>1182</v>
       </c>
       <c r="H249" s="22">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="I249" s="23">
         <f t="shared" si="32"/>
-        <v>1557</v>
+        <v>1537</v>
       </c>
       <c r="J249" t="str">
         <f t="shared" si="28"/>
@@ -13840,7 +13964,7 @@
       </c>
       <c r="L249">
         <f t="shared" si="30"/>
-        <v>1557</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="250" spans="1:12">
@@ -13857,21 +13981,21 @@
         <v>15</v>
       </c>
       <c r="E250" s="19">
-        <v>12420</v>
+        <v>13044</v>
       </c>
       <c r="F250" s="20">
         <v>0</v>
       </c>
       <c r="G250" s="21">
         <f t="shared" si="34"/>
-        <v>1035</v>
+        <v>1087</v>
       </c>
       <c r="H250" s="22">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="I250" s="23">
         <f t="shared" si="32"/>
-        <v>1501</v>
+        <v>1413</v>
       </c>
       <c r="J250" t="str">
         <f t="shared" si="28"/>
@@ -13883,7 +14007,7 @@
       </c>
       <c r="L250">
         <f t="shared" si="30"/>
-        <v>1501</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="251" spans="1:12">
@@ -15321,21 +15445,21 @@
         <v>227</v>
       </c>
       <c r="E286" s="19">
-        <v>18802</v>
+        <v>19074</v>
       </c>
       <c r="F286" s="20">
         <v>0</v>
       </c>
       <c r="G286" s="21">
         <f>E286*(1-F286)</f>
-        <v>18802</v>
+        <v>19074</v>
       </c>
       <c r="H286" s="22">
         <v>0.3</v>
       </c>
       <c r="I286" s="23">
         <f>+ROUND((G286*H286)+G286,0)</f>
-        <v>24443</v>
+        <v>24796</v>
       </c>
       <c r="J286">
         <f t="shared" si="37"/>
@@ -15347,7 +15471,7 @@
       </c>
       <c r="L286">
         <f t="shared" si="39"/>
-        <v>24443</v>
+        <v>24796</v>
       </c>
     </row>
     <row r="287" spans="1:12">
@@ -15604,21 +15728,21 @@
         <v>227</v>
       </c>
       <c r="E293" s="19">
-        <v>61680</v>
+        <v>64690</v>
       </c>
       <c r="F293" s="20">
         <v>0</v>
       </c>
       <c r="G293" s="21">
         <f>E293*(1-F293)/6</f>
-        <v>10280</v>
+        <v>10781.666666666666</v>
       </c>
       <c r="H293" s="22">
-        <v>0.39979999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="I293" s="23">
         <f t="shared" si="42"/>
-        <v>14390</v>
+        <v>15094</v>
       </c>
       <c r="J293">
         <f t="shared" si="37"/>
@@ -15630,7 +15754,7 @@
       </c>
       <c r="L293">
         <f t="shared" si="39"/>
-        <v>14390</v>
+        <v>15094</v>
       </c>
     </row>
     <row r="294" spans="1:12">
@@ -15948,21 +16072,21 @@
         <v>227</v>
       </c>
       <c r="E301" s="19">
-        <v>55020</v>
+        <v>55300</v>
       </c>
       <c r="F301" s="20">
         <v>0</v>
       </c>
       <c r="G301" s="21">
         <f>E301*(1-F301)/6</f>
-        <v>9170</v>
+        <v>9216.6666666666661</v>
       </c>
       <c r="H301" s="22">
-        <v>0.39910000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="I301" s="23">
         <f t="shared" si="42"/>
-        <v>12830</v>
+        <v>12903</v>
       </c>
       <c r="J301">
         <f t="shared" si="37"/>
@@ -15974,7 +16098,7 @@
       </c>
       <c r="L301">
         <f t="shared" si="39"/>
-        <v>12830</v>
+        <v>12903</v>
       </c>
     </row>
     <row r="302" spans="1:12">
@@ -15991,21 +16115,21 @@
         <v>227</v>
       </c>
       <c r="E302" s="19">
-        <v>40872</v>
+        <v>45680</v>
       </c>
       <c r="F302" s="20">
         <v>0</v>
       </c>
       <c r="G302" s="21">
         <f>E302*(1-F302)/6</f>
-        <v>6812</v>
+        <v>7613.333333333333</v>
       </c>
       <c r="H302" s="22">
-        <v>0.47089999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="I302" s="23">
         <f>+ROUND((G302*H302)+G302,0)</f>
-        <v>10020</v>
+        <v>10659</v>
       </c>
       <c r="J302">
         <f t="shared" si="37"/>
@@ -16017,7 +16141,7 @@
       </c>
       <c r="L302">
         <f t="shared" si="39"/>
-        <v>10020</v>
+        <v>10659</v>
       </c>
     </row>
     <row r="303" spans="1:12">
@@ -16077,21 +16201,21 @@
         <v>227</v>
       </c>
       <c r="E304" s="19">
-        <v>43290</v>
+        <v>43620</v>
       </c>
       <c r="F304" s="20">
         <v>0</v>
       </c>
       <c r="G304" s="21">
         <f>E304*(1-F304)/6</f>
-        <v>7215</v>
+        <v>7270</v>
       </c>
       <c r="H304" s="22">
-        <v>0.41370000000000001</v>
+        <v>0.4002</v>
       </c>
       <c r="I304" s="23">
         <f>+ROUND((G304*H304)+G304,0)</f>
-        <v>10200</v>
+        <v>10179</v>
       </c>
       <c r="J304">
         <f t="shared" si="37"/>
@@ -16103,7 +16227,7 @@
       </c>
       <c r="L304">
         <f t="shared" si="39"/>
-        <v>10200</v>
+        <v>10179</v>
       </c>
     </row>
     <row r="305" spans="1:12">
@@ -16274,17 +16398,17 @@
         <v>227</v>
       </c>
       <c r="E309" s="19">
-        <v>70400</v>
+        <v>66110</v>
       </c>
       <c r="F309" s="20">
         <v>0</v>
       </c>
       <c r="G309" s="21">
         <f>E309*(1-F309)/10</f>
-        <v>7040</v>
+        <v>6611</v>
       </c>
       <c r="H309" s="22">
-        <v>0.40050000000000002</v>
+        <v>0.4914</v>
       </c>
       <c r="I309" s="23">
         <f t="shared" si="43"/>
@@ -16317,17 +16441,17 @@
         <v>227</v>
       </c>
       <c r="E310" s="19">
-        <v>63360</v>
+        <v>59508</v>
       </c>
       <c r="F310" s="20">
         <v>0</v>
       </c>
       <c r="G310" s="21">
         <f>E310*(1-F310)/9</f>
-        <v>7040</v>
+        <v>6612</v>
       </c>
       <c r="H310" s="22">
-        <v>0.40050000000000002</v>
+        <v>0.49120000000000003</v>
       </c>
       <c r="I310" s="23">
         <f t="shared" si="43"/>
@@ -16360,21 +16484,21 @@
         <v>227</v>
       </c>
       <c r="E311" s="19">
-        <v>44790</v>
+        <v>55200</v>
       </c>
       <c r="F311" s="20">
         <v>0</v>
       </c>
       <c r="G311" s="21">
         <f>E311*(1-F311)/15</f>
-        <v>2986</v>
+        <v>3680</v>
       </c>
       <c r="H311" s="22">
         <v>0.58740000000000003</v>
       </c>
       <c r="I311" s="23">
         <f>+ROUND((G311*H311)+G311,0)</f>
-        <v>4740</v>
+        <v>5842</v>
       </c>
       <c r="J311">
         <f t="shared" si="37"/>
@@ -16386,7 +16510,7 @@
       </c>
       <c r="L311">
         <f t="shared" si="39"/>
-        <v>4740</v>
+        <v>5842</v>
       </c>
     </row>
     <row r="312" spans="1:12">
@@ -16403,21 +16527,21 @@
         <v>227</v>
       </c>
       <c r="E312" s="51">
-        <v>44790</v>
+        <v>57225</v>
       </c>
       <c r="F312" s="52">
         <v>0</v>
       </c>
       <c r="G312" s="21">
         <f>E312*(1-F312)/15</f>
-        <v>2986</v>
+        <v>3815</v>
       </c>
       <c r="H312" s="53">
-        <v>0.58740000000000003</v>
+        <v>0.53080000000000005</v>
       </c>
       <c r="I312" s="54">
         <f t="shared" si="43"/>
-        <v>4740</v>
+        <v>5840</v>
       </c>
       <c r="J312">
         <f t="shared" si="37"/>
@@ -16429,7 +16553,7 @@
       </c>
       <c r="L312">
         <f t="shared" si="39"/>
-        <v>4740</v>
+        <v>5840</v>
       </c>
     </row>
     <row r="313" spans="1:12">
@@ -17227,21 +17351,21 @@
         <v>15</v>
       </c>
       <c r="E332" s="19">
-        <v>38310</v>
+        <v>39900</v>
       </c>
       <c r="F332" s="20">
         <v>0</v>
       </c>
       <c r="G332" s="21">
         <f>E332*(1-F332)/30</f>
-        <v>1277</v>
+        <v>1330</v>
       </c>
       <c r="H332" s="22">
         <v>0.39379999999999998</v>
       </c>
       <c r="I332" s="23">
         <f>+ROUND((G332*H332)+G332,0)</f>
-        <v>1780</v>
+        <v>1854</v>
       </c>
       <c r="J332" t="str">
         <f t="shared" si="50"/>
@@ -17253,7 +17377,7 @@
       </c>
       <c r="L332">
         <f t="shared" si="52"/>
-        <v>1780</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="333" spans="1:12">
@@ -17270,21 +17394,21 @@
         <v>15</v>
       </c>
       <c r="E333" s="19">
-        <v>38310</v>
+        <v>39900</v>
       </c>
       <c r="F333" s="20">
         <v>0</v>
       </c>
       <c r="G333" s="21">
         <f>E333*(1-F333)/30</f>
-        <v>1277</v>
+        <v>1330</v>
       </c>
       <c r="H333" s="22">
         <v>0.39379999999999998</v>
       </c>
       <c r="I333" s="23">
         <f>+ROUND((G333*H333)+G333,0)</f>
-        <v>1780</v>
+        <v>1854</v>
       </c>
       <c r="J333" t="str">
         <f t="shared" si="50"/>
@@ -17296,7 +17420,7 @@
       </c>
       <c r="L333">
         <f t="shared" si="52"/>
-        <v>1780</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="334" spans="1:12">
@@ -18481,21 +18605,21 @@
         <v>15</v>
       </c>
       <c r="E362" s="19">
-        <v>28752</v>
+        <v>30660</v>
       </c>
       <c r="F362" s="20">
         <v>0</v>
       </c>
       <c r="G362" s="21">
         <f>E362*(1-F362)/12</f>
-        <v>2396</v>
+        <v>2555</v>
       </c>
       <c r="H362" s="22">
         <v>0.34</v>
       </c>
       <c r="I362" s="23">
         <f t="shared" si="55"/>
-        <v>3211</v>
+        <v>3424</v>
       </c>
       <c r="J362" t="str">
         <f t="shared" si="50"/>
@@ -18507,7 +18631,7 @@
       </c>
       <c r="L362">
         <f t="shared" si="52"/>
-        <v>3211</v>
+        <v>3424</v>
       </c>
     </row>
     <row r="363" spans="1:12">
@@ -18524,21 +18648,21 @@
         <v>15</v>
       </c>
       <c r="E363" s="19">
-        <v>11880</v>
+        <v>12630</v>
       </c>
       <c r="F363" s="20">
         <v>0</v>
       </c>
       <c r="G363" s="21">
         <f>E363*(1-F363)/6</f>
-        <v>1980</v>
+        <v>2105</v>
       </c>
       <c r="H363" s="22">
         <v>0.3</v>
       </c>
       <c r="I363" s="23">
         <f t="shared" si="55"/>
-        <v>2574</v>
+        <v>2737</v>
       </c>
       <c r="J363" t="str">
         <f t="shared" si="50"/>
@@ -18550,7 +18674,7 @@
       </c>
       <c r="L363">
         <f t="shared" si="52"/>
-        <v>2574</v>
+        <v>2737</v>
       </c>
     </row>
     <row r="364" spans="1:12">
@@ -20158,21 +20282,21 @@
         <v>15</v>
       </c>
       <c r="E401" s="19">
-        <v>7848</v>
+        <v>10020</v>
       </c>
       <c r="F401" s="20">
         <v>0</v>
       </c>
       <c r="G401" s="21">
         <f>E401*(1-F401)/12</f>
-        <v>654</v>
+        <v>835</v>
       </c>
       <c r="H401" s="22">
-        <v>0.65139999999999998</v>
+        <v>0.4</v>
       </c>
       <c r="I401" s="23">
         <f t="shared" si="57"/>
-        <v>1080</v>
+        <v>1169</v>
       </c>
       <c r="J401" t="str">
         <f t="shared" si="58"/>
@@ -20184,7 +20308,7 @@
       </c>
       <c r="L401">
         <f t="shared" si="60"/>
-        <v>1080</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="402" spans="1:12">
@@ -20201,21 +20325,21 @@
         <v>15</v>
       </c>
       <c r="E402" s="19">
-        <v>15432</v>
+        <v>19044</v>
       </c>
       <c r="F402" s="20">
         <v>0</v>
       </c>
       <c r="G402" s="21">
         <f>E402*(1-F402)/12</f>
-        <v>1286</v>
+        <v>1587</v>
       </c>
       <c r="H402" s="22">
-        <v>0.57079999999999997</v>
+        <v>0.4</v>
       </c>
       <c r="I402" s="23">
         <f t="shared" si="57"/>
-        <v>2020</v>
+        <v>2222</v>
       </c>
       <c r="J402" t="str">
         <f t="shared" si="58"/>
@@ -20227,7 +20351,7 @@
       </c>
       <c r="L402">
         <f t="shared" si="60"/>
-        <v>2020</v>
+        <v>2222</v>
       </c>
     </row>
     <row r="403" spans="1:12">
@@ -22159,11 +22283,11 @@
         <v>5445</v>
       </c>
       <c r="H450" s="62">
-        <v>0.24890000000000001</v>
+        <v>0.19375000000000001</v>
       </c>
       <c r="I450" s="37">
         <f t="shared" si="66"/>
-        <v>6800</v>
+        <v>6500</v>
       </c>
       <c r="J450" t="str">
         <f t="shared" si="58"/>
@@ -22175,7 +22299,7 @@
       </c>
       <c r="L450">
         <f t="shared" si="60"/>
-        <v>6800</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="451" spans="1:12">
@@ -24730,7 +24854,7 @@
     </row>
     <row r="522" spans="1:12">
       <c r="A522" s="93"/>
-      <c r="B522" s="94"/>
+      <c r="B522" s="125"/>
       <c r="C522" s="94"/>
       <c r="D522" s="95"/>
       <c r="E522" s="47"/>
@@ -25107,7 +25231,7 @@
         <v>11250</v>
       </c>
       <c r="H531" s="22">
-        <v>0.26577000000000001</v>
+        <v>0.26579999999999998</v>
       </c>
       <c r="I531" s="23">
         <f t="shared" si="78"/>
@@ -25322,11 +25446,11 @@
         <v>11880</v>
       </c>
       <c r="H536" s="22">
-        <v>0.1507</v>
+        <v>0.1187</v>
       </c>
       <c r="I536" s="23">
         <f t="shared" si="82"/>
-        <v>13670</v>
+        <v>13290</v>
       </c>
       <c r="J536">
         <f t="shared" si="76"/>
@@ -25338,7 +25462,7 @@
       </c>
       <c r="L536">
         <f t="shared" si="80"/>
-        <v>13670</v>
+        <v>13290</v>
       </c>
     </row>
     <row r="537" spans="1:12">
@@ -25451,11 +25575,11 @@
         <v>10890</v>
       </c>
       <c r="H539" s="22">
-        <v>0.2</v>
+        <v>0.1157</v>
       </c>
       <c r="I539" s="23">
         <f t="shared" si="82"/>
-        <v>13068</v>
+        <v>12150</v>
       </c>
       <c r="J539">
         <f t="shared" si="76"/>
@@ -25467,7 +25591,7 @@
       </c>
       <c r="L539">
         <f t="shared" si="80"/>
-        <v>13068</v>
+        <v>12150</v>
       </c>
     </row>
     <row r="540" spans="1:12">
@@ -25699,21 +25823,21 @@
         <v>227</v>
       </c>
       <c r="E545" s="19">
-        <v>20700</v>
+        <v>10528</v>
       </c>
       <c r="F545" s="20">
         <v>0</v>
       </c>
       <c r="G545" s="21">
         <f t="shared" si="81"/>
-        <v>20700</v>
+        <v>10528</v>
       </c>
       <c r="H545" s="22">
-        <v>0.2</v>
+        <v>0.14929999999999999</v>
       </c>
       <c r="I545" s="23">
         <f t="shared" si="82"/>
-        <v>24840</v>
+        <v>12100</v>
       </c>
       <c r="J545">
         <f t="shared" si="76"/>
@@ -25725,7 +25849,7 @@
       </c>
       <c r="L545">
         <f t="shared" si="80"/>
-        <v>24840</v>
+        <v>12100</v>
       </c>
     </row>
     <row r="546" spans="1:12">
@@ -26834,11 +26958,11 @@
         <v>11875</v>
       </c>
       <c r="H572" s="22">
-        <v>0.25</v>
+        <v>0.15110000000000001</v>
       </c>
       <c r="I572" s="23">
         <f>+ROUND((G572*H572)+G572,0)</f>
-        <v>14844</v>
+        <v>13669</v>
       </c>
       <c r="J572">
         <f t="shared" si="76"/>
@@ -26850,7 +26974,7 @@
       </c>
       <c r="L572">
         <f t="shared" si="80"/>
-        <v>14844</v>
+        <v>13669</v>
       </c>
     </row>
     <row r="573" spans="1:12">
@@ -26966,21 +27090,21 @@
         <v>227</v>
       </c>
       <c r="E576" s="19">
-        <v>5739</v>
+        <v>6086</v>
       </c>
       <c r="F576" s="20">
         <v>0</v>
       </c>
       <c r="G576" s="21">
         <f t="shared" ref="G576:G598" si="85">E576*(1-F576)</f>
-        <v>5739</v>
+        <v>6086</v>
       </c>
       <c r="H576" s="22">
-        <v>0.25109999999999999</v>
+        <v>0.252</v>
       </c>
       <c r="I576" s="23">
         <f t="shared" ref="I576:I598" si="86">+ROUND((G576*H576)+G576,0)</f>
-        <v>7180</v>
+        <v>7620</v>
       </c>
       <c r="J576">
         <f t="shared" si="76"/>
@@ -26992,7 +27116,7 @@
       </c>
       <c r="L576">
         <f t="shared" si="80"/>
-        <v>7180</v>
+        <v>7620</v>
       </c>
     </row>
     <row r="577" spans="1:12">
@@ -27052,21 +27176,20 @@
         <v>227</v>
       </c>
       <c r="E578" s="19">
-        <v>5900</v>
+        <v>6273</v>
       </c>
       <c r="F578" s="20">
         <v>0</v>
       </c>
       <c r="G578" s="21">
         <f t="shared" si="85"/>
-        <v>5900</v>
+        <v>6273</v>
       </c>
       <c r="H578" s="22">
-        <v>0.25409999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="I578" s="23">
-        <f t="shared" si="86"/>
-        <v>7399</v>
+        <v>7300</v>
       </c>
       <c r="J578">
         <f t="shared" si="76"/>
@@ -27078,7 +27201,7 @@
       </c>
       <c r="L578">
         <f t="shared" si="80"/>
-        <v>7399</v>
+        <v>7300</v>
       </c>
     </row>
     <row r="579" spans="1:12">
@@ -27095,21 +27218,21 @@
         <v>227</v>
       </c>
       <c r="E579" s="19">
-        <v>5900</v>
+        <v>6273</v>
       </c>
       <c r="F579" s="20">
         <v>0</v>
       </c>
       <c r="G579" s="21">
         <f t="shared" si="85"/>
-        <v>5900</v>
+        <v>6273</v>
       </c>
       <c r="H579" s="22">
-        <v>0.25409999999999999</v>
+        <v>0.16350000000000001</v>
       </c>
       <c r="I579" s="23">
         <f t="shared" si="86"/>
-        <v>7399</v>
+        <v>7299</v>
       </c>
       <c r="J579">
         <f t="shared" si="76"/>
@@ -27121,7 +27244,7 @@
       </c>
       <c r="L579">
         <f t="shared" si="80"/>
-        <v>7399</v>
+        <v>7299</v>
       </c>
     </row>
     <row r="580" spans="1:12">
@@ -27148,11 +27271,11 @@
         <v>6500</v>
       </c>
       <c r="H580" s="22">
-        <v>0.25409999999999999</v>
+        <v>0.3518</v>
       </c>
       <c r="I580" s="23">
         <f>+ROUND((G580*H580)+G580,0)</f>
-        <v>8152</v>
+        <v>8787</v>
       </c>
       <c r="J580">
         <f t="shared" si="76"/>
@@ -27164,7 +27287,7 @@
       </c>
       <c r="L580">
         <f t="shared" si="80"/>
-        <v>8152</v>
+        <v>8787</v>
       </c>
     </row>
     <row r="581" spans="1:12">
@@ -27181,21 +27304,21 @@
         <v>227</v>
       </c>
       <c r="E581" s="19">
-        <v>4587</v>
+        <v>5292</v>
       </c>
       <c r="F581" s="20">
         <v>0</v>
       </c>
       <c r="G581" s="21">
         <f t="shared" si="85"/>
-        <v>4587</v>
+        <v>5292</v>
       </c>
       <c r="H581" s="22">
-        <v>0.39500000000000002</v>
+        <v>0.25090000000000001</v>
       </c>
       <c r="I581" s="23">
         <f t="shared" si="86"/>
-        <v>6399</v>
+        <v>6620</v>
       </c>
       <c r="J581">
         <f t="shared" si="76"/>
@@ -27207,7 +27330,7 @@
       </c>
       <c r="L581">
         <f t="shared" si="80"/>
-        <v>6399</v>
+        <v>6620</v>
       </c>
     </row>
     <row r="582" spans="1:12">
@@ -27224,21 +27347,21 @@
         <v>227</v>
       </c>
       <c r="E582" s="19">
-        <v>4587</v>
+        <v>4805</v>
       </c>
       <c r="F582" s="20">
         <v>0</v>
       </c>
       <c r="G582" s="21">
         <f t="shared" si="85"/>
-        <v>4587</v>
+        <v>4805</v>
       </c>
       <c r="H582" s="22">
-        <v>0.39500000000000002</v>
+        <v>0.25</v>
       </c>
       <c r="I582" s="23">
         <f t="shared" si="86"/>
-        <v>6399</v>
+        <v>6006</v>
       </c>
       <c r="J582">
         <f t="shared" ref="J582:J645" si="87">IF(ISNUMBER(A582), IF(C582=1032, A582, "00" &amp; A582 &amp; "." &amp; C582), "")</f>
@@ -27250,7 +27373,7 @@
       </c>
       <c r="L582">
         <f t="shared" si="80"/>
-        <v>6399</v>
+        <v>6006</v>
       </c>
     </row>
     <row r="583" spans="1:12">
@@ -27267,21 +27390,20 @@
         <v>227</v>
       </c>
       <c r="E583" s="19">
-        <v>6450</v>
+        <v>6941</v>
       </c>
       <c r="F583" s="20">
         <v>0</v>
       </c>
       <c r="G583" s="21">
         <f t="shared" si="85"/>
-        <v>6450</v>
+        <v>6941</v>
       </c>
       <c r="H583" s="22">
-        <v>0.16259999999999999</v>
+        <v>0.13800000000000001</v>
       </c>
       <c r="I583" s="23">
-        <f t="shared" si="86"/>
-        <v>7499</v>
+        <v>7899</v>
       </c>
       <c r="J583">
         <f t="shared" si="87"/>
@@ -27293,7 +27415,7 @@
       </c>
       <c r="L583">
         <f t="shared" si="80"/>
-        <v>7499</v>
+        <v>7899</v>
       </c>
     </row>
     <row r="584" spans="1:12">
@@ -27310,21 +27432,21 @@
         <v>227</v>
       </c>
       <c r="E584" s="19">
-        <v>10304</v>
+        <v>11850</v>
       </c>
       <c r="F584" s="20">
         <v>0</v>
       </c>
       <c r="G584" s="21">
         <f t="shared" si="85"/>
-        <v>10304</v>
+        <v>11850</v>
       </c>
       <c r="H584" s="22">
-        <v>0.25</v>
+        <v>0.24890000000000001</v>
       </c>
       <c r="I584" s="23">
         <f t="shared" si="86"/>
-        <v>12880</v>
+        <v>14799</v>
       </c>
       <c r="J584">
         <f t="shared" si="87"/>
@@ -27336,7 +27458,7 @@
       </c>
       <c r="L584">
         <f t="shared" si="80"/>
-        <v>12880</v>
+        <v>14799</v>
       </c>
     </row>
     <row r="585" spans="1:12">
@@ -27353,21 +27475,21 @@
         <v>227</v>
       </c>
       <c r="E585" s="19">
-        <v>5800</v>
+        <v>6400</v>
       </c>
       <c r="F585" s="20">
         <v>0</v>
       </c>
       <c r="G585" s="21">
         <f t="shared" si="85"/>
-        <v>5800</v>
+        <v>6400</v>
       </c>
       <c r="H585" s="22">
-        <v>0.29310000000000003</v>
+        <v>0.29680000000000001</v>
       </c>
       <c r="I585" s="23">
         <f t="shared" si="86"/>
-        <v>7500</v>
+        <v>8300</v>
       </c>
       <c r="J585">
         <f t="shared" si="87"/>
@@ -27379,7 +27501,7 @@
       </c>
       <c r="L585">
         <f t="shared" si="80"/>
-        <v>7500</v>
+        <v>8300</v>
       </c>
     </row>
     <row r="586" spans="1:12">
@@ -27697,21 +27819,21 @@
         <v>227</v>
       </c>
       <c r="E593" s="19">
-        <v>6540</v>
+        <v>6914</v>
       </c>
       <c r="F593" s="20">
         <v>0</v>
       </c>
       <c r="G593" s="21">
         <f t="shared" si="85"/>
-        <v>6540</v>
+        <v>6914</v>
       </c>
       <c r="H593" s="22">
-        <v>0.20795</v>
+        <v>0.251</v>
       </c>
       <c r="I593" s="23">
         <f t="shared" si="86"/>
-        <v>7900</v>
+        <v>8649</v>
       </c>
       <c r="J593">
         <f t="shared" si="87"/>
@@ -27723,7 +27845,7 @@
       </c>
       <c r="L593">
         <f t="shared" si="89"/>
-        <v>7900</v>
+        <v>8649</v>
       </c>
     </row>
     <row r="594" spans="1:12">
@@ -27783,21 +27905,21 @@
         <v>227</v>
       </c>
       <c r="E595" s="19">
-        <v>8210</v>
+        <v>8749</v>
       </c>
       <c r="F595" s="20">
         <v>0</v>
       </c>
       <c r="G595" s="21">
         <f t="shared" si="85"/>
-        <v>8210</v>
+        <v>8749</v>
       </c>
       <c r="H595" s="22">
-        <v>0.3155</v>
+        <v>0.25040000000000001</v>
       </c>
       <c r="I595" s="23">
         <f t="shared" si="86"/>
-        <v>10800</v>
+        <v>10940</v>
       </c>
       <c r="J595">
         <f t="shared" si="87"/>
@@ -27809,7 +27931,7 @@
       </c>
       <c r="L595">
         <f t="shared" si="89"/>
-        <v>10800</v>
+        <v>10940</v>
       </c>
     </row>
     <row r="596" spans="1:12">
@@ -27826,21 +27948,21 @@
         <v>227</v>
       </c>
       <c r="E596" s="19">
-        <v>6887</v>
+        <v>6913</v>
       </c>
       <c r="F596" s="20">
         <v>0</v>
       </c>
       <c r="G596" s="21">
         <f t="shared" si="85"/>
-        <v>6887</v>
+        <v>6913</v>
       </c>
       <c r="H596" s="22">
-        <v>0.25590000000000002</v>
+        <v>0.25119999999999998</v>
       </c>
       <c r="I596" s="23">
         <f t="shared" si="86"/>
-        <v>8649</v>
+        <v>8650</v>
       </c>
       <c r="J596">
         <f t="shared" si="87"/>
@@ -27852,7 +27974,7 @@
       </c>
       <c r="L596">
         <f t="shared" si="89"/>
-        <v>8649</v>
+        <v>8650</v>
       </c>
     </row>
     <row r="597" spans="1:12">
@@ -27869,21 +27991,21 @@
         <v>227</v>
       </c>
       <c r="E597" s="19">
-        <v>6843</v>
+        <v>6913</v>
       </c>
       <c r="F597" s="20">
         <v>0</v>
       </c>
       <c r="G597" s="21">
         <f t="shared" si="85"/>
-        <v>6843</v>
+        <v>6913</v>
       </c>
       <c r="H597" s="22">
-        <v>0.25090000000000001</v>
+        <v>8.4699999999999998E-2</v>
       </c>
       <c r="I597" s="23">
         <f t="shared" si="86"/>
-        <v>8560</v>
+        <v>7499</v>
       </c>
       <c r="J597">
         <f t="shared" si="87"/>
@@ -27895,7 +28017,7 @@
       </c>
       <c r="L597">
         <f t="shared" si="89"/>
-        <v>8560</v>
+        <v>7499</v>
       </c>
     </row>
     <row r="598" spans="1:12">
@@ -27922,11 +28044,11 @@
         <v>6039</v>
       </c>
       <c r="H598" s="22">
-        <v>0.19220000000000001</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="I598" s="23">
         <f t="shared" si="86"/>
-        <v>7200</v>
+        <v>7700</v>
       </c>
       <c r="J598">
         <f t="shared" si="87"/>
@@ -27938,7 +28060,7 @@
       </c>
       <c r="L598">
         <f t="shared" si="89"/>
-        <v>7200</v>
+        <v>7700</v>
       </c>
     </row>
     <row r="599" spans="1:12">
@@ -27990,11 +28112,11 @@
         <v>6236</v>
       </c>
       <c r="H600" s="22">
-        <v>0.12230000000000001</v>
+        <v>0.20269999999999999</v>
       </c>
       <c r="I600" s="23">
         <f>+ROUND((G600*H600)+G600,0)</f>
-        <v>6999</v>
+        <v>7500</v>
       </c>
       <c r="J600">
         <f t="shared" si="87"/>
@@ -28006,7 +28128,7 @@
       </c>
       <c r="L600">
         <f t="shared" si="89"/>
-        <v>6999</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="601" spans="1:12">
@@ -28023,21 +28145,21 @@
         <v>227</v>
       </c>
       <c r="E601" s="56">
-        <v>8000</v>
+        <v>7436</v>
       </c>
       <c r="F601" s="20">
         <v>0</v>
       </c>
       <c r="G601" s="21">
         <f>E601*(1-F601)</f>
-        <v>8000</v>
+        <v>7436</v>
       </c>
       <c r="H601" s="22">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="I601" s="23">
         <f>+ROUND((G601*H601)+G601,0)</f>
-        <v>10800</v>
+        <v>9295</v>
       </c>
       <c r="J601">
         <f t="shared" si="87"/>
@@ -28049,7 +28171,7 @@
       </c>
       <c r="L601">
         <f t="shared" si="89"/>
-        <v>10800</v>
+        <v>9295</v>
       </c>
     </row>
     <row r="602" spans="1:12">
@@ -28066,21 +28188,21 @@
         <v>227</v>
       </c>
       <c r="E602" s="57">
-        <v>7203</v>
+        <v>7389</v>
       </c>
       <c r="F602" s="20">
         <v>0</v>
       </c>
       <c r="G602" s="21">
         <f>E602*(1-F602)</f>
-        <v>7203</v>
+        <v>7389</v>
       </c>
       <c r="H602" s="22">
-        <v>0.25</v>
+        <v>0.2505</v>
       </c>
       <c r="I602" s="23">
         <f>+ROUND((G602*H602)+G602,0)</f>
-        <v>9004</v>
+        <v>9240</v>
       </c>
       <c r="J602">
         <f t="shared" si="87"/>
@@ -28092,7 +28214,7 @@
       </c>
       <c r="L602">
         <f t="shared" si="89"/>
-        <v>9004</v>
+        <v>9240</v>
       </c>
     </row>
     <row r="603" spans="1:12" ht="16.5" customHeight="1">
@@ -28372,21 +28494,21 @@
         <v>15</v>
       </c>
       <c r="E610" s="57">
-        <v>1050</v>
+        <v>1100</v>
       </c>
       <c r="F610" s="20">
         <v>0</v>
       </c>
       <c r="G610" s="21">
         <f t="shared" si="90"/>
-        <v>1050</v>
+        <v>1100</v>
       </c>
       <c r="H610" s="22">
-        <v>0.33300000000000002</v>
+        <v>0.36399999999999999</v>
       </c>
       <c r="I610" s="23">
         <f t="shared" si="91"/>
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="J610">
         <f t="shared" si="87"/>
@@ -28398,7 +28520,7 @@
       </c>
       <c r="L610">
         <f t="shared" si="89"/>
-        <v>1400</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="611" spans="1:12">
@@ -28501,20 +28623,21 @@
         <v>15</v>
       </c>
       <c r="E613" s="57">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="F613" s="20">
         <v>0</v>
       </c>
       <c r="G613" s="21">
         <f t="shared" si="90"/>
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="H613" s="22">
-        <v>0.4</v>
+        <v>0.187</v>
       </c>
       <c r="I613" s="23">
-        <v>1800</v>
+        <f t="shared" si="91"/>
+        <v>1899</v>
       </c>
       <c r="J613">
         <f t="shared" si="87"/>
@@ -28526,7 +28649,7 @@
       </c>
       <c r="L613">
         <f t="shared" si="89"/>
-        <v>1800</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="614" spans="1:12">
@@ -28672,21 +28795,21 @@
         <v>15</v>
       </c>
       <c r="E617" s="57">
-        <v>2250</v>
+        <v>2500</v>
       </c>
       <c r="F617" s="20">
         <v>0</v>
       </c>
       <c r="G617" s="21">
         <f t="shared" si="90"/>
-        <v>2250</v>
+        <v>2500</v>
       </c>
       <c r="H617" s="22">
-        <v>0.24399999999999999</v>
+        <v>0.16</v>
       </c>
       <c r="I617" s="23">
         <f t="shared" si="91"/>
-        <v>2799</v>
+        <v>2900</v>
       </c>
       <c r="J617">
         <f t="shared" si="87"/>
@@ -28698,7 +28821,7 @@
       </c>
       <c r="L617">
         <f t="shared" si="89"/>
-        <v>2799</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="618" spans="1:12">
@@ -30047,21 +30170,21 @@
         <v>15</v>
       </c>
       <c r="E649" s="57">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="F649" s="20">
         <v>0</v>
       </c>
       <c r="G649" s="21">
         <f t="shared" si="92"/>
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="H649" s="22">
-        <v>0.26340000000000002</v>
+        <v>0.3</v>
       </c>
       <c r="I649" s="23">
         <f t="shared" si="93"/>
-        <v>2400</v>
+        <v>2600</v>
       </c>
       <c r="J649">
         <f t="shared" si="94"/>
@@ -30073,7 +30196,7 @@
       </c>
       <c r="L649">
         <f t="shared" si="89"/>
-        <v>2400</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="650" spans="1:12">
@@ -30950,21 +31073,21 @@
         <v>15</v>
       </c>
       <c r="E670" s="57">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="F670" s="20">
         <v>0</v>
       </c>
       <c r="G670" s="21">
         <f t="shared" si="92"/>
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="H670" s="22">
-        <v>0.4</v>
+        <v>0.1429</v>
       </c>
       <c r="I670" s="23">
         <f t="shared" si="93"/>
-        <v>4200</v>
+        <v>4000</v>
       </c>
       <c r="J670">
         <f t="shared" si="94"/>
@@ -30976,7 +31099,7 @@
       </c>
       <c r="L670">
         <f t="shared" si="96"/>
-        <v>4200</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="671" spans="1:12">
@@ -31131,11 +31254,11 @@
         <v>5000</v>
       </c>
       <c r="H674" s="22">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="I674" s="23">
         <f t="shared" si="98"/>
-        <v>6500</v>
+        <v>6000</v>
       </c>
       <c r="J674">
         <f t="shared" si="94"/>
@@ -31147,7 +31270,7 @@
       </c>
       <c r="L674">
         <f t="shared" si="96"/>
-        <v>6500</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="675" spans="1:12">
@@ -31164,21 +31287,21 @@
         <v>15</v>
       </c>
       <c r="E675" s="57">
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="F675" s="20">
         <v>0</v>
       </c>
       <c r="G675" s="21">
         <f t="shared" si="97"/>
-        <v>1900</v>
+        <v>2000</v>
       </c>
       <c r="H675" s="22">
-        <v>0.316</v>
+        <v>0.3</v>
       </c>
       <c r="I675" s="23">
         <f t="shared" si="98"/>
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="J675">
         <f t="shared" si="94"/>
@@ -31190,7 +31313,7 @@
       </c>
       <c r="L675">
         <f t="shared" si="96"/>
-        <v>2500</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="676" spans="1:12">
@@ -31647,11 +31770,11 @@
         <v>1359</v>
       </c>
       <c r="H686" s="22">
-        <v>0.36499999999999999</v>
+        <v>0.39700000000000002</v>
       </c>
       <c r="I686" s="23">
         <f t="shared" si="98"/>
-        <v>1855</v>
+        <v>1899</v>
       </c>
       <c r="J686">
         <f t="shared" si="94"/>
@@ -31663,7 +31786,7 @@
       </c>
       <c r="L686">
         <f t="shared" si="96"/>
-        <v>1855</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="687" spans="1:12">
@@ -31680,21 +31803,21 @@
         <v>15</v>
       </c>
       <c r="E687" s="57">
-        <v>8000</v>
+        <v>8500</v>
       </c>
       <c r="F687" s="20">
         <v>0</v>
       </c>
       <c r="G687" s="21">
         <f t="shared" si="97"/>
-        <v>8000</v>
+        <v>8500</v>
       </c>
       <c r="H687" s="22">
         <v>0.3</v>
       </c>
       <c r="I687" s="23">
         <f t="shared" si="98"/>
-        <v>10400</v>
+        <v>11050</v>
       </c>
       <c r="J687">
         <f t="shared" si="94"/>
@@ -31706,7 +31829,7 @@
       </c>
       <c r="L687">
         <f t="shared" si="96"/>
-        <v>10400</v>
+        <v>11050</v>
       </c>
     </row>
     <row r="688" spans="1:12">
@@ -31852,21 +31975,21 @@
         <v>15</v>
       </c>
       <c r="E691" s="57">
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="F691" s="20">
         <v>0</v>
       </c>
       <c r="G691" s="21">
         <f t="shared" si="97"/>
-        <v>2000</v>
+        <v>100</v>
       </c>
       <c r="H691" s="22">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I691" s="23">
         <f t="shared" si="98"/>
-        <v>2600</v>
+        <v>100</v>
       </c>
       <c r="J691">
         <f t="shared" si="94"/>
@@ -31878,7 +32001,7 @@
       </c>
       <c r="L691">
         <f t="shared" si="96"/>
-        <v>2600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="692" spans="1:12">
@@ -32110,21 +32233,21 @@
         <v>15</v>
       </c>
       <c r="E697" s="57">
-        <v>3700</v>
+        <v>4150</v>
       </c>
       <c r="F697" s="20">
         <v>0</v>
       </c>
       <c r="G697" s="21">
         <f t="shared" si="97"/>
-        <v>3700</v>
+        <v>4150</v>
       </c>
       <c r="H697" s="22">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I697" s="23">
         <f t="shared" si="98"/>
-        <v>3700</v>
+        <v>4980</v>
       </c>
       <c r="J697">
         <f t="shared" si="94"/>
@@ -32136,12 +32259,16 @@
       </c>
       <c r="L697">
         <f t="shared" si="96"/>
-        <v>3700</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="698" spans="1:12">
-      <c r="A698" s="15"/>
-      <c r="B698" s="16"/>
+      <c r="A698" s="15">
+        <v>999</v>
+      </c>
+      <c r="B698" s="16" t="s">
+        <v>645</v>
+      </c>
       <c r="C698" s="17">
         <v>1032</v>
       </c>
@@ -32149,38 +32276,42 @@
         <v>15</v>
       </c>
       <c r="E698" s="57">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="F698" s="20">
         <v>0</v>
       </c>
       <c r="G698" s="21">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="H698" s="22">
-        <v>0</v>
+        <v>0.55549999999999999</v>
       </c>
       <c r="I698" s="23">
         <f t="shared" si="98"/>
-        <v>0</v>
-      </c>
-      <c r="J698" t="str">
+        <v>7000</v>
+      </c>
+      <c r="J698">
         <f t="shared" si="94"/>
-        <v/>
+        <v>999</v>
       </c>
       <c r="K698" t="str">
         <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="L698" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L698">
         <f t="shared" si="96"/>
-        <v/>
+        <v>7000</v>
       </c>
     </row>
     <row r="699" spans="1:12">
-      <c r="A699" s="15"/>
-      <c r="B699" s="16"/>
+      <c r="A699" s="15">
+        <v>6091</v>
+      </c>
+      <c r="B699" s="16" t="s">
+        <v>647</v>
+      </c>
       <c r="C699" s="17">
         <v>1032</v>
       </c>
@@ -32188,38 +32319,42 @@
         <v>15</v>
       </c>
       <c r="E699" s="57">
-        <v>0</v>
+        <v>2390</v>
       </c>
       <c r="F699" s="20">
         <v>0</v>
       </c>
       <c r="G699" s="21">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>2390</v>
       </c>
       <c r="H699" s="22">
         <v>0</v>
       </c>
       <c r="I699" s="23">
         <f t="shared" si="98"/>
-        <v>0</v>
-      </c>
-      <c r="J699" t="str">
+        <v>2390</v>
+      </c>
+      <c r="J699">
         <f t="shared" si="94"/>
-        <v/>
+        <v>6091</v>
       </c>
       <c r="K699" t="str">
         <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="L699" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L699">
         <f t="shared" si="96"/>
-        <v/>
+        <v>2390</v>
       </c>
     </row>
     <row r="700" spans="1:12">
-      <c r="A700" s="15"/>
-      <c r="B700" s="16"/>
+      <c r="A700" s="15">
+        <v>6092</v>
+      </c>
+      <c r="B700" s="16" t="s">
+        <v>648</v>
+      </c>
       <c r="C700" s="17">
         <v>1032</v>
       </c>
@@ -32227,38 +32362,42 @@
         <v>15</v>
       </c>
       <c r="E700" s="57">
-        <v>0</v>
+        <v>2450</v>
       </c>
       <c r="F700" s="20">
         <v>0</v>
       </c>
       <c r="G700" s="21">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>2450</v>
       </c>
       <c r="H700" s="22">
-        <v>0</v>
+        <v>0.42399999999999999</v>
       </c>
       <c r="I700" s="23">
         <f t="shared" si="98"/>
-        <v>0</v>
-      </c>
-      <c r="J700" t="str">
+        <v>3489</v>
+      </c>
+      <c r="J700">
         <f t="shared" si="94"/>
-        <v/>
+        <v>6092</v>
       </c>
       <c r="K700" t="str">
         <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="L700" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L700">
         <f t="shared" si="96"/>
-        <v/>
+        <v>3489</v>
       </c>
     </row>
     <row r="701" spans="1:12">
-      <c r="A701" s="15"/>
-      <c r="B701" s="16"/>
+      <c r="A701" s="15">
+        <v>6093</v>
+      </c>
+      <c r="B701" s="16" t="s">
+        <v>649</v>
+      </c>
       <c r="C701" s="17">
         <v>1032</v>
       </c>
@@ -32266,38 +32405,42 @@
         <v>15</v>
       </c>
       <c r="E701" s="57">
-        <v>0</v>
+        <v>1910</v>
       </c>
       <c r="F701" s="20">
         <v>0</v>
       </c>
       <c r="G701" s="21">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>1910</v>
       </c>
       <c r="H701" s="22">
-        <v>0</v>
+        <v>0.36099999999999999</v>
       </c>
       <c r="I701" s="23">
         <f t="shared" si="98"/>
-        <v>0</v>
-      </c>
-      <c r="J701" t="str">
+        <v>2600</v>
+      </c>
+      <c r="J701">
         <f t="shared" si="94"/>
-        <v/>
+        <v>6093</v>
       </c>
       <c r="K701" t="str">
         <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="L701" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L701">
         <f t="shared" si="96"/>
-        <v/>
+        <v>2600</v>
       </c>
     </row>
     <row r="702" spans="1:12">
-      <c r="A702" s="15"/>
-      <c r="B702" s="16"/>
+      <c r="A702" s="15">
+        <v>6094</v>
+      </c>
+      <c r="B702" s="16" t="s">
+        <v>650</v>
+      </c>
       <c r="C702" s="17">
         <v>1032</v>
       </c>
@@ -32305,38 +32448,42 @@
         <v>15</v>
       </c>
       <c r="E702" s="57">
-        <v>0</v>
+        <v>2380</v>
       </c>
       <c r="F702" s="20">
         <v>0</v>
       </c>
       <c r="G702" s="21">
         <f t="shared" si="97"/>
-        <v>0</v>
+        <v>2380</v>
       </c>
       <c r="H702" s="22">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I702" s="23">
         <f t="shared" si="98"/>
-        <v>0</v>
-      </c>
-      <c r="J702" t="str">
+        <v>3094</v>
+      </c>
+      <c r="J702">
         <f t="shared" si="94"/>
-        <v/>
+        <v>6094</v>
       </c>
       <c r="K702" t="str">
         <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="L702" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L702">
         <f t="shared" si="96"/>
-        <v/>
+        <v>3094</v>
       </c>
     </row>
     <row r="703" spans="1:12">
-      <c r="A703" s="15"/>
-      <c r="B703" s="16"/>
+      <c r="A703" s="15">
+        <v>6095</v>
+      </c>
+      <c r="B703" s="16" t="s">
+        <v>651</v>
+      </c>
       <c r="C703" s="17">
         <v>1032</v>
       </c>
@@ -32344,38 +32491,42 @@
         <v>15</v>
       </c>
       <c r="E703" s="57">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="F703" s="20">
         <v>0</v>
       </c>
       <c r="G703" s="21">
         <f t="shared" ref="G703:G734" si="99">E703*(1-F703)</f>
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="H703" s="22">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="I703" s="23">
         <f t="shared" ref="I703:I734" si="100">+ROUND((G703*H703)+G703,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J703" t="str">
+        <v>1755</v>
+      </c>
+      <c r="J703">
         <f t="shared" si="94"/>
-        <v/>
+        <v>6095</v>
       </c>
       <c r="K703" t="str">
         <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="L703" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L703">
         <f t="shared" si="96"/>
-        <v/>
+        <v>1755</v>
       </c>
     </row>
     <row r="704" spans="1:12">
-      <c r="A704" s="15"/>
-      <c r="B704" s="16"/>
+      <c r="A704" s="15">
+        <v>6096</v>
+      </c>
+      <c r="B704" s="16" t="s">
+        <v>652</v>
+      </c>
       <c r="C704" s="17">
         <v>1032</v>
       </c>
@@ -32383,38 +32534,42 @@
         <v>15</v>
       </c>
       <c r="E704" s="57">
-        <v>0</v>
+        <v>6230</v>
       </c>
       <c r="F704" s="20">
         <v>0</v>
       </c>
       <c r="G704" s="21">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>6230</v>
       </c>
       <c r="H704" s="22">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I704" s="23">
         <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="J704" t="str">
+        <v>8099</v>
+      </c>
+      <c r="J704">
         <f t="shared" si="94"/>
-        <v/>
+        <v>6096</v>
       </c>
       <c r="K704" t="str">
         <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="L704" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L704">
         <f t="shared" si="96"/>
-        <v/>
+        <v>8099</v>
       </c>
     </row>
     <row r="705" spans="1:12">
-      <c r="A705" s="15"/>
-      <c r="B705" s="16"/>
+      <c r="A705" s="15">
+        <v>6097</v>
+      </c>
+      <c r="B705" s="16" t="s">
+        <v>653</v>
+      </c>
       <c r="C705" s="17">
         <v>1032</v>
       </c>
@@ -32422,38 +32577,42 @@
         <v>15</v>
       </c>
       <c r="E705" s="57">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="F705" s="20">
         <v>0</v>
       </c>
       <c r="G705" s="21">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="H705" s="22">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I705" s="23">
         <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="J705" t="str">
+        <v>7800</v>
+      </c>
+      <c r="J705">
         <f t="shared" si="94"/>
-        <v/>
+        <v>6097</v>
       </c>
       <c r="K705" t="str">
         <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="L705" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L705">
         <f t="shared" si="96"/>
-        <v/>
+        <v>7800</v>
       </c>
     </row>
     <row r="706" spans="1:12">
-      <c r="A706" s="15"/>
-      <c r="B706" s="16"/>
+      <c r="A706" s="15">
+        <v>6098</v>
+      </c>
+      <c r="B706" s="16" t="s">
+        <v>654</v>
+      </c>
       <c r="C706" s="17">
         <v>1032</v>
       </c>
@@ -32461,38 +32620,42 @@
         <v>15</v>
       </c>
       <c r="E706" s="57">
-        <v>0</v>
+        <v>850</v>
       </c>
       <c r="F706" s="20">
         <v>0</v>
       </c>
       <c r="G706" s="21">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>850</v>
       </c>
       <c r="H706" s="22">
         <v>0</v>
       </c>
       <c r="I706" s="23">
         <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="J706" t="str">
+        <v>850</v>
+      </c>
+      <c r="J706">
         <f t="shared" si="94"/>
-        <v/>
+        <v>6098</v>
       </c>
       <c r="K706" t="str">
         <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="L706" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L706">
         <f t="shared" si="96"/>
-        <v/>
+        <v>850</v>
       </c>
     </row>
     <row r="707" spans="1:12">
-      <c r="A707" s="15"/>
-      <c r="B707" s="16"/>
+      <c r="A707" s="15">
+        <v>6099</v>
+      </c>
+      <c r="B707" s="16" t="s">
+        <v>655</v>
+      </c>
       <c r="C707" s="17">
         <v>1032</v>
       </c>
@@ -32500,38 +32663,42 @@
         <v>15</v>
       </c>
       <c r="E707" s="57">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="F707" s="20">
         <v>0</v>
       </c>
       <c r="G707" s="21">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="H707" s="22">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="I707" s="23">
         <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="J707" t="str">
+        <v>4123</v>
+      </c>
+      <c r="J707">
         <f t="shared" si="94"/>
-        <v/>
+        <v>6099</v>
       </c>
       <c r="K707" t="str">
         <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="L707" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L707">
         <f t="shared" si="96"/>
-        <v/>
+        <v>4123</v>
       </c>
     </row>
     <row r="708" spans="1:12">
-      <c r="A708" s="15"/>
-      <c r="B708" s="16"/>
+      <c r="A708" s="15">
+        <v>6100</v>
+      </c>
+      <c r="B708" s="16" t="s">
+        <v>656</v>
+      </c>
       <c r="C708" s="17">
         <v>1032</v>
       </c>
@@ -32539,38 +32706,42 @@
         <v>15</v>
       </c>
       <c r="E708" s="57">
-        <v>0</v>
+        <v>1550</v>
       </c>
       <c r="F708" s="20">
         <v>0</v>
       </c>
       <c r="G708" s="21">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>1550</v>
       </c>
       <c r="H708" s="22">
         <v>0</v>
       </c>
       <c r="I708" s="23">
         <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="J708" t="str">
+        <v>1550</v>
+      </c>
+      <c r="J708">
         <f t="shared" si="94"/>
-        <v/>
+        <v>6100</v>
       </c>
       <c r="K708" t="str">
         <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="L708" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L708">
         <f t="shared" si="96"/>
-        <v/>
+        <v>1550</v>
       </c>
     </row>
     <row r="709" spans="1:12">
-      <c r="A709" s="15"/>
-      <c r="B709" s="16"/>
+      <c r="A709" s="15">
+        <v>6101</v>
+      </c>
+      <c r="B709" s="16" t="s">
+        <v>657</v>
+      </c>
       <c r="C709" s="17">
         <v>1032</v>
       </c>
@@ -32578,38 +32749,42 @@
         <v>15</v>
       </c>
       <c r="E709" s="57">
-        <v>0</v>
+        <v>4390</v>
       </c>
       <c r="F709" s="20">
         <v>0</v>
       </c>
       <c r="G709" s="21">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>4390</v>
       </c>
       <c r="H709" s="22">
-        <v>0</v>
+        <v>0.40300000000000002</v>
       </c>
       <c r="I709" s="23">
         <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="J709" t="str">
+        <v>6159</v>
+      </c>
+      <c r="J709">
         <f t="shared" si="94"/>
-        <v/>
+        <v>6101</v>
       </c>
       <c r="K709" t="str">
         <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="L709" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L709">
         <f t="shared" si="96"/>
-        <v/>
+        <v>6159</v>
       </c>
     </row>
     <row r="710" spans="1:12">
-      <c r="A710" s="15"/>
-      <c r="B710" s="16"/>
+      <c r="A710" s="15">
+        <v>6102</v>
+      </c>
+      <c r="B710" s="16" t="s">
+        <v>658</v>
+      </c>
       <c r="C710" s="17">
         <v>1032</v>
       </c>
@@ -32617,38 +32792,42 @@
         <v>15</v>
       </c>
       <c r="E710" s="57">
-        <v>0</v>
+        <v>2550</v>
       </c>
       <c r="F710" s="20">
         <v>0</v>
       </c>
       <c r="G710" s="21">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>2550</v>
       </c>
       <c r="H710" s="22">
-        <v>0</v>
+        <v>0.29399999999999998</v>
       </c>
       <c r="I710" s="23">
         <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="J710" t="str">
+        <v>3300</v>
+      </c>
+      <c r="J710">
         <f t="shared" ref="J710:J773" si="101">IF(ISNUMBER(A710), IF(C710=1032, A710, "00" &amp; A710 &amp; "." &amp; C710), "")</f>
-        <v/>
+        <v>6102</v>
       </c>
       <c r="K710" t="str">
         <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="L710" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L710">
         <f t="shared" si="96"/>
-        <v/>
+        <v>3300</v>
       </c>
     </row>
     <row r="711" spans="1:12">
-      <c r="A711" s="15"/>
-      <c r="B711" s="16"/>
+      <c r="A711" s="15">
+        <v>6103</v>
+      </c>
+      <c r="B711" s="16" t="s">
+        <v>646</v>
+      </c>
       <c r="C711" s="17">
         <v>1032</v>
       </c>
@@ -32656,38 +32835,42 @@
         <v>15</v>
       </c>
       <c r="E711" s="57">
-        <v>0</v>
+        <v>1850</v>
       </c>
       <c r="F711" s="20">
         <v>0</v>
       </c>
       <c r="G711" s="21">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>1850</v>
       </c>
       <c r="H711" s="22">
-        <v>0</v>
+        <v>0.35110000000000002</v>
       </c>
       <c r="I711" s="23">
         <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="J711" t="str">
+        <v>2500</v>
+      </c>
+      <c r="J711">
         <f t="shared" si="101"/>
-        <v/>
+        <v>6103</v>
       </c>
       <c r="K711" t="str">
         <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="L711" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L711">
         <f t="shared" si="96"/>
-        <v/>
+        <v>2500</v>
       </c>
     </row>
     <row r="712" spans="1:12">
-      <c r="A712" s="15"/>
-      <c r="B712" s="16"/>
+      <c r="A712" s="15">
+        <v>6104</v>
+      </c>
+      <c r="B712" s="16" t="s">
+        <v>659</v>
+      </c>
       <c r="C712" s="17">
         <v>1032</v>
       </c>
@@ -32695,38 +32878,42 @@
         <v>15</v>
       </c>
       <c r="E712" s="57">
-        <v>0</v>
+        <v>1060</v>
       </c>
       <c r="F712" s="20">
         <v>0</v>
       </c>
       <c r="G712" s="21">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>1060</v>
       </c>
       <c r="H712" s="22">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="I712" s="23">
         <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="J712" t="str">
+        <v>1325</v>
+      </c>
+      <c r="J712">
         <f t="shared" si="101"/>
-        <v/>
+        <v>6104</v>
       </c>
       <c r="K712" t="str">
         <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="L712" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L712">
         <f t="shared" si="96"/>
-        <v/>
+        <v>1325</v>
       </c>
     </row>
     <row r="713" spans="1:12">
-      <c r="A713" s="15"/>
-      <c r="B713" s="16"/>
+      <c r="A713" s="15">
+        <v>6105</v>
+      </c>
+      <c r="B713" s="16" t="s">
+        <v>660</v>
+      </c>
       <c r="C713" s="17">
         <v>1032</v>
       </c>
@@ -32734,38 +32921,42 @@
         <v>15</v>
       </c>
       <c r="E713" s="57">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="F713" s="20">
         <v>0</v>
       </c>
       <c r="G713" s="21">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="H713" s="22">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I713" s="23">
         <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="J713" t="str">
+        <v>2210</v>
+      </c>
+      <c r="J713">
         <f t="shared" si="101"/>
-        <v/>
+        <v>6105</v>
       </c>
       <c r="K713" t="str">
         <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="L713" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L713">
         <f t="shared" si="96"/>
-        <v/>
+        <v>2210</v>
       </c>
     </row>
     <row r="714" spans="1:12">
-      <c r="A714" s="15"/>
-      <c r="B714" s="16"/>
+      <c r="A714" s="15">
+        <v>6106</v>
+      </c>
+      <c r="B714" s="16" t="s">
+        <v>661</v>
+      </c>
       <c r="C714" s="17">
         <v>1032</v>
       </c>
@@ -32773,38 +32964,42 @@
         <v>15</v>
       </c>
       <c r="E714" s="57">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="F714" s="20">
         <v>0</v>
       </c>
       <c r="G714" s="21">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="H714" s="22">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I714" s="23">
         <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="J714" t="str">
+        <v>2730</v>
+      </c>
+      <c r="J714">
         <f t="shared" si="101"/>
-        <v/>
+        <v>6106</v>
       </c>
       <c r="K714" t="str">
         <f t="shared" si="95"/>
-        <v/>
-      </c>
-      <c r="L714" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L714">
         <f t="shared" si="96"/>
-        <v/>
+        <v>2730</v>
       </c>
     </row>
     <row r="715" spans="1:12">
-      <c r="A715" s="15"/>
-      <c r="B715" s="16"/>
+      <c r="A715" s="15">
+        <v>6107</v>
+      </c>
+      <c r="B715" s="16" t="s">
+        <v>662</v>
+      </c>
       <c r="C715" s="17">
         <v>1032</v>
       </c>
@@ -32812,38 +33007,42 @@
         <v>15</v>
       </c>
       <c r="E715" s="57">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="F715" s="20">
         <v>0</v>
       </c>
       <c r="G715" s="21">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="H715" s="22">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I715" s="23">
         <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="J715" t="str">
+        <v>2730</v>
+      </c>
+      <c r="J715">
         <f t="shared" si="101"/>
-        <v/>
+        <v>6107</v>
       </c>
       <c r="K715" t="str">
         <f t="shared" ref="K715:K778" si="102">IF(J715="","","LISTA1")</f>
-        <v/>
-      </c>
-      <c r="L715" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L715">
         <f t="shared" ref="L715:L778" si="103">IF(J715="","",I715)</f>
-        <v/>
+        <v>2730</v>
       </c>
     </row>
     <row r="716" spans="1:12">
-      <c r="A716" s="15"/>
-      <c r="B716" s="16"/>
+      <c r="A716" s="15">
+        <v>6108</v>
+      </c>
+      <c r="B716" s="16" t="s">
+        <v>663</v>
+      </c>
       <c r="C716" s="17">
         <v>1032</v>
       </c>
@@ -32851,38 +33050,42 @@
         <v>15</v>
       </c>
       <c r="E716" s="57">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="F716" s="20">
         <v>0</v>
       </c>
       <c r="G716" s="21">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="H716" s="22">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I716" s="23">
         <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="J716" t="str">
+        <v>2730</v>
+      </c>
+      <c r="J716">
         <f t="shared" si="101"/>
-        <v/>
+        <v>6108</v>
       </c>
       <c r="K716" t="str">
         <f t="shared" si="102"/>
-        <v/>
-      </c>
-      <c r="L716" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L716">
         <f t="shared" si="103"/>
-        <v/>
+        <v>2730</v>
       </c>
     </row>
     <row r="717" spans="1:12">
-      <c r="A717" s="15"/>
-      <c r="B717" s="16"/>
+      <c r="A717" s="15">
+        <v>6109</v>
+      </c>
+      <c r="B717" s="16" t="s">
+        <v>664</v>
+      </c>
       <c r="C717" s="17">
         <v>1032</v>
       </c>
@@ -32890,38 +33093,42 @@
         <v>15</v>
       </c>
       <c r="E717" s="57">
-        <v>0</v>
+        <v>6849</v>
       </c>
       <c r="F717" s="20">
         <v>0</v>
       </c>
       <c r="G717" s="21">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>6849</v>
       </c>
       <c r="H717" s="22">
-        <v>0</v>
+        <v>0.20019999999999999</v>
       </c>
       <c r="I717" s="23">
         <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="J717" t="str">
+        <v>8220</v>
+      </c>
+      <c r="J717">
         <f t="shared" si="101"/>
-        <v/>
+        <v>6109</v>
       </c>
       <c r="K717" t="str">
         <f t="shared" si="102"/>
-        <v/>
-      </c>
-      <c r="L717" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L717">
         <f t="shared" si="103"/>
-        <v/>
+        <v>8220</v>
       </c>
     </row>
     <row r="718" spans="1:12">
-      <c r="A718" s="15"/>
-      <c r="B718" s="16"/>
+      <c r="A718" s="15">
+        <v>6110</v>
+      </c>
+      <c r="B718" s="16" t="s">
+        <v>665</v>
+      </c>
       <c r="C718" s="17">
         <v>1032</v>
       </c>
@@ -32929,38 +33136,42 @@
         <v>15</v>
       </c>
       <c r="E718" s="57">
-        <v>0</v>
+        <v>1876</v>
       </c>
       <c r="F718" s="20">
         <v>0</v>
       </c>
       <c r="G718" s="21">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>1876</v>
       </c>
       <c r="H718" s="22">
-        <v>0</v>
+        <v>0.20419999999999999</v>
       </c>
       <c r="I718" s="23">
         <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="J718" t="str">
+        <v>2259</v>
+      </c>
+      <c r="J718">
         <f t="shared" si="101"/>
-        <v/>
+        <v>6110</v>
       </c>
       <c r="K718" t="str">
         <f t="shared" si="102"/>
-        <v/>
-      </c>
-      <c r="L718" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L718">
         <f t="shared" si="103"/>
-        <v/>
+        <v>2259</v>
       </c>
     </row>
     <row r="719" spans="1:12">
-      <c r="A719" s="15"/>
-      <c r="B719" s="16"/>
+      <c r="A719" s="15">
+        <v>6111</v>
+      </c>
+      <c r="B719" s="16" t="s">
+        <v>666</v>
+      </c>
       <c r="C719" s="17">
         <v>1032</v>
       </c>
@@ -32968,38 +33179,42 @@
         <v>15</v>
       </c>
       <c r="E719" s="57">
-        <v>0</v>
+        <v>2113</v>
       </c>
       <c r="F719" s="20">
         <v>0</v>
       </c>
       <c r="G719" s="21">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>2113</v>
       </c>
       <c r="H719" s="22">
-        <v>0</v>
+        <v>0.20680000000000001</v>
       </c>
       <c r="I719" s="23">
         <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="J719" t="str">
+        <v>2550</v>
+      </c>
+      <c r="J719">
         <f t="shared" si="101"/>
-        <v/>
+        <v>6111</v>
       </c>
       <c r="K719" t="str">
         <f t="shared" si="102"/>
-        <v/>
-      </c>
-      <c r="L719" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L719">
         <f t="shared" si="103"/>
-        <v/>
+        <v>2550</v>
       </c>
     </row>
     <row r="720" spans="1:12">
-      <c r="A720" s="15"/>
-      <c r="B720" s="16"/>
+      <c r="A720" s="15">
+        <v>6112</v>
+      </c>
+      <c r="B720" s="16" t="s">
+        <v>667</v>
+      </c>
       <c r="C720" s="17">
         <v>1032</v>
       </c>
@@ -33007,38 +33222,42 @@
         <v>15</v>
       </c>
       <c r="E720" s="57">
-        <v>0</v>
+        <v>860</v>
       </c>
       <c r="F720" s="20">
         <v>0</v>
       </c>
       <c r="G720" s="21">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>860</v>
       </c>
       <c r="H720" s="22">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I720" s="23">
         <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="J720" t="str">
+        <v>1204</v>
+      </c>
+      <c r="J720">
         <f t="shared" si="101"/>
-        <v/>
+        <v>6112</v>
       </c>
       <c r="K720" t="str">
         <f t="shared" si="102"/>
-        <v/>
-      </c>
-      <c r="L720" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L720">
         <f t="shared" si="103"/>
-        <v/>
+        <v>1204</v>
       </c>
     </row>
     <row r="721" spans="1:12">
-      <c r="A721" s="15"/>
-      <c r="B721" s="16"/>
+      <c r="A721" s="15">
+        <v>6113</v>
+      </c>
+      <c r="B721" s="16" t="s">
+        <v>668</v>
+      </c>
       <c r="C721" s="17">
         <v>1032</v>
       </c>
@@ -33046,38 +33265,42 @@
         <v>15</v>
       </c>
       <c r="E721" s="57">
-        <v>0</v>
+        <v>890</v>
       </c>
       <c r="F721" s="20">
         <v>0</v>
       </c>
       <c r="G721" s="21">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>890</v>
       </c>
       <c r="H721" s="22">
-        <v>0</v>
+        <v>0.29210000000000003</v>
       </c>
       <c r="I721" s="23">
         <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="J721" t="str">
+        <v>1150</v>
+      </c>
+      <c r="J721">
         <f t="shared" si="101"/>
-        <v/>
+        <v>6113</v>
       </c>
       <c r="K721" t="str">
         <f t="shared" si="102"/>
-        <v/>
-      </c>
-      <c r="L721" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L721">
         <f t="shared" si="103"/>
-        <v/>
+        <v>1150</v>
       </c>
     </row>
     <row r="722" spans="1:12">
-      <c r="A722" s="15"/>
-      <c r="B722" s="16"/>
+      <c r="A722" s="15">
+        <v>6114</v>
+      </c>
+      <c r="B722" s="16" t="s">
+        <v>669</v>
+      </c>
       <c r="C722" s="17">
         <v>1032</v>
       </c>
@@ -33085,38 +33308,42 @@
         <v>15</v>
       </c>
       <c r="E722" s="57">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="F722" s="20">
         <v>0</v>
       </c>
       <c r="G722" s="21">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="H722" s="22">
-        <v>0</v>
+        <v>0.39100000000000001</v>
       </c>
       <c r="I722" s="23">
         <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="J722" t="str">
+        <v>3199</v>
+      </c>
+      <c r="J722">
         <f t="shared" si="101"/>
-        <v/>
+        <v>6114</v>
       </c>
       <c r="K722" t="str">
         <f t="shared" si="102"/>
-        <v/>
-      </c>
-      <c r="L722" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L722">
         <f t="shared" si="103"/>
-        <v/>
+        <v>3199</v>
       </c>
     </row>
     <row r="723" spans="1:12">
-      <c r="A723" s="15"/>
-      <c r="B723" s="16"/>
+      <c r="A723" s="15">
+        <v>6115</v>
+      </c>
+      <c r="B723" s="16" t="s">
+        <v>670</v>
+      </c>
       <c r="C723" s="17">
         <v>1032</v>
       </c>
@@ -33124,38 +33351,42 @@
         <v>15</v>
       </c>
       <c r="E723" s="57">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="F723" s="20">
         <v>0</v>
       </c>
       <c r="G723" s="21">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="H723" s="22">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I723" s="23">
         <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="J723" t="str">
+        <v>2380</v>
+      </c>
+      <c r="J723">
         <f t="shared" si="101"/>
-        <v/>
+        <v>6115</v>
       </c>
       <c r="K723" t="str">
         <f t="shared" si="102"/>
-        <v/>
-      </c>
-      <c r="L723" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L723">
         <f t="shared" si="103"/>
-        <v/>
+        <v>2380</v>
       </c>
     </row>
     <row r="724" spans="1:12">
-      <c r="A724" s="15"/>
-      <c r="B724" s="16"/>
+      <c r="A724" s="15">
+        <v>6116</v>
+      </c>
+      <c r="B724" s="16" t="s">
+        <v>671</v>
+      </c>
       <c r="C724" s="17">
         <v>1032</v>
       </c>
@@ -33163,38 +33394,42 @@
         <v>15</v>
       </c>
       <c r="E724" s="57">
-        <v>0</v>
+        <v>3170</v>
       </c>
       <c r="F724" s="20">
         <v>0</v>
       </c>
       <c r="G724" s="21">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>3170</v>
       </c>
       <c r="H724" s="22">
-        <v>0</v>
+        <v>0.3876</v>
       </c>
       <c r="I724" s="23">
         <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="J724" t="str">
+        <v>4399</v>
+      </c>
+      <c r="J724">
         <f t="shared" si="101"/>
-        <v/>
+        <v>6116</v>
       </c>
       <c r="K724" t="str">
         <f t="shared" si="102"/>
-        <v/>
-      </c>
-      <c r="L724" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L724">
         <f t="shared" si="103"/>
-        <v/>
+        <v>4399</v>
       </c>
     </row>
     <row r="725" spans="1:12">
-      <c r="A725" s="15"/>
-      <c r="B725" s="16"/>
+      <c r="A725" s="15">
+        <v>6117</v>
+      </c>
+      <c r="B725" s="16" t="s">
+        <v>672</v>
+      </c>
       <c r="C725" s="17">
         <v>1032</v>
       </c>
@@ -33202,38 +33437,42 @@
         <v>15</v>
       </c>
       <c r="E725" s="57">
-        <v>0</v>
+        <v>2030</v>
       </c>
       <c r="F725" s="20">
         <v>0</v>
       </c>
       <c r="G725" s="21">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>2030</v>
       </c>
       <c r="H725" s="22">
-        <v>0</v>
+        <v>0.28070000000000001</v>
       </c>
       <c r="I725" s="23">
         <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="J725" t="str">
+        <v>2600</v>
+      </c>
+      <c r="J725">
         <f t="shared" si="101"/>
-        <v/>
+        <v>6117</v>
       </c>
       <c r="K725" t="str">
         <f t="shared" si="102"/>
-        <v/>
-      </c>
-      <c r="L725" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L725">
         <f t="shared" si="103"/>
-        <v/>
+        <v>2600</v>
       </c>
     </row>
     <row r="726" spans="1:12">
-      <c r="A726" s="15"/>
-      <c r="B726" s="16"/>
+      <c r="A726" s="15">
+        <v>6118</v>
+      </c>
+      <c r="B726" s="16" t="s">
+        <v>673</v>
+      </c>
       <c r="C726" s="17">
         <v>1032</v>
       </c>
@@ -33241,38 +33480,42 @@
         <v>15</v>
       </c>
       <c r="E726" s="57">
-        <v>0</v>
+        <v>7870</v>
       </c>
       <c r="F726" s="20">
         <v>0</v>
       </c>
       <c r="G726" s="21">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>7870</v>
       </c>
       <c r="H726" s="22">
-        <v>0</v>
+        <v>0.12959999999999999</v>
       </c>
       <c r="I726" s="23">
         <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="J726" t="str">
+        <v>8890</v>
+      </c>
+      <c r="J726">
         <f t="shared" si="101"/>
-        <v/>
+        <v>6118</v>
       </c>
       <c r="K726" t="str">
         <f t="shared" si="102"/>
-        <v/>
-      </c>
-      <c r="L726" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L726">
         <f t="shared" si="103"/>
-        <v/>
+        <v>8890</v>
       </c>
     </row>
     <row r="727" spans="1:12">
-      <c r="A727" s="15"/>
-      <c r="B727" s="16"/>
+      <c r="A727" s="15">
+        <v>6120</v>
+      </c>
+      <c r="B727" s="16" t="s">
+        <v>674</v>
+      </c>
       <c r="C727" s="17">
         <v>1032</v>
       </c>
@@ -33280,38 +33523,42 @@
         <v>15</v>
       </c>
       <c r="E727" s="57">
-        <v>0</v>
+        <v>1320</v>
       </c>
       <c r="F727" s="20">
         <v>0</v>
       </c>
       <c r="G727" s="21">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>1320</v>
       </c>
       <c r="H727" s="22">
-        <v>0</v>
+        <v>0.33300000000000002</v>
       </c>
       <c r="I727" s="23">
         <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="J727" t="str">
+        <v>1760</v>
+      </c>
+      <c r="J727">
         <f t="shared" si="101"/>
-        <v/>
+        <v>6120</v>
       </c>
       <c r="K727" t="str">
         <f t="shared" si="102"/>
-        <v/>
-      </c>
-      <c r="L727" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L727">
         <f t="shared" si="103"/>
-        <v/>
+        <v>1760</v>
       </c>
     </row>
     <row r="728" spans="1:12">
-      <c r="A728" s="15"/>
-      <c r="B728" s="16"/>
+      <c r="A728" s="15">
+        <v>6121</v>
+      </c>
+      <c r="B728" s="16" t="s">
+        <v>675</v>
+      </c>
       <c r="C728" s="17">
         <v>1032</v>
       </c>
@@ -33319,38 +33566,42 @@
         <v>15</v>
       </c>
       <c r="E728" s="57">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="F728" s="20">
         <v>0</v>
       </c>
       <c r="G728" s="21">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="H728" s="22">
-        <v>0</v>
+        <v>0.33600000000000002</v>
       </c>
       <c r="I728" s="23">
         <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="J728" t="str">
+        <v>1470</v>
+      </c>
+      <c r="J728">
         <f t="shared" si="101"/>
-        <v/>
+        <v>6121</v>
       </c>
       <c r="K728" t="str">
         <f t="shared" si="102"/>
-        <v/>
-      </c>
-      <c r="L728" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L728">
         <f t="shared" si="103"/>
-        <v/>
+        <v>1470</v>
       </c>
     </row>
     <row r="729" spans="1:12">
-      <c r="A729" s="15"/>
-      <c r="B729" s="16"/>
+      <c r="A729" s="15">
+        <v>6122</v>
+      </c>
+      <c r="B729" s="16" t="s">
+        <v>676</v>
+      </c>
       <c r="C729" s="17">
         <v>1032</v>
       </c>
@@ -33358,38 +33609,42 @@
         <v>15</v>
       </c>
       <c r="E729" s="57">
-        <v>0</v>
+        <v>1050</v>
       </c>
       <c r="F729" s="20">
         <v>0</v>
       </c>
       <c r="G729" s="21">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>1050</v>
       </c>
       <c r="H729" s="22">
-        <v>0</v>
+        <v>0.33300000000000002</v>
       </c>
       <c r="I729" s="23">
         <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="J729" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J729">
         <f t="shared" si="101"/>
-        <v/>
+        <v>6122</v>
       </c>
       <c r="K729" t="str">
         <f t="shared" si="102"/>
-        <v/>
-      </c>
-      <c r="L729" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L729">
         <f t="shared" si="103"/>
-        <v/>
+        <v>1400</v>
       </c>
     </row>
     <row r="730" spans="1:12">
-      <c r="A730" s="15"/>
-      <c r="B730" s="16"/>
+      <c r="A730" s="15">
+        <v>6123</v>
+      </c>
+      <c r="B730" s="16" t="s">
+        <v>677</v>
+      </c>
       <c r="C730" s="17">
         <v>1032</v>
       </c>
@@ -33397,38 +33652,42 @@
         <v>15</v>
       </c>
       <c r="E730" s="57">
-        <v>0</v>
+        <v>1050</v>
       </c>
       <c r="F730" s="20">
         <v>0</v>
       </c>
       <c r="G730" s="21">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>1050</v>
       </c>
       <c r="H730" s="22">
-        <v>0</v>
+        <v>0.33300000000000002</v>
       </c>
       <c r="I730" s="23">
         <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="J730" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J730">
         <f t="shared" si="101"/>
-        <v/>
+        <v>6123</v>
       </c>
       <c r="K730" t="str">
         <f t="shared" si="102"/>
-        <v/>
-      </c>
-      <c r="L730" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L730">
         <f t="shared" si="103"/>
-        <v/>
+        <v>1400</v>
       </c>
     </row>
     <row r="731" spans="1:12">
-      <c r="A731" s="15"/>
-      <c r="B731" s="16"/>
+      <c r="A731" s="15">
+        <v>6124</v>
+      </c>
+      <c r="B731" s="16" t="s">
+        <v>678</v>
+      </c>
       <c r="C731" s="17">
         <v>1032</v>
       </c>
@@ -33436,38 +33695,42 @@
         <v>15</v>
       </c>
       <c r="E731" s="57">
-        <v>0</v>
+        <v>1250</v>
       </c>
       <c r="F731" s="20">
         <v>0</v>
       </c>
       <c r="G731" s="21">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>1250</v>
       </c>
       <c r="H731" s="22">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="I731" s="23">
         <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="J731" t="str">
+        <v>1650</v>
+      </c>
+      <c r="J731">
         <f t="shared" si="101"/>
-        <v/>
+        <v>6124</v>
       </c>
       <c r="K731" t="str">
         <f t="shared" si="102"/>
-        <v/>
-      </c>
-      <c r="L731" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L731">
         <f t="shared" si="103"/>
-        <v/>
+        <v>1650</v>
       </c>
     </row>
     <row r="732" spans="1:12">
-      <c r="A732" s="15"/>
-      <c r="B732" s="16"/>
+      <c r="A732" s="15">
+        <v>6125</v>
+      </c>
+      <c r="B732" s="16" t="s">
+        <v>679</v>
+      </c>
       <c r="C732" s="17">
         <v>1032</v>
       </c>
@@ -33475,38 +33738,42 @@
         <v>15</v>
       </c>
       <c r="E732" s="57">
-        <v>0</v>
+        <v>1880</v>
       </c>
       <c r="F732" s="20">
         <v>0</v>
       </c>
       <c r="G732" s="21">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>1880</v>
       </c>
       <c r="H732" s="22">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I732" s="23">
         <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="J732" t="str">
+        <v>2256</v>
+      </c>
+      <c r="J732">
         <f t="shared" si="101"/>
-        <v/>
+        <v>6125</v>
       </c>
       <c r="K732" t="str">
         <f t="shared" si="102"/>
-        <v/>
-      </c>
-      <c r="L732" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L732">
         <f t="shared" si="103"/>
-        <v/>
+        <v>2256</v>
       </c>
     </row>
     <row r="733" spans="1:12">
-      <c r="A733" s="15"/>
-      <c r="B733" s="16"/>
+      <c r="A733" s="15">
+        <v>6126</v>
+      </c>
+      <c r="B733" s="16" t="s">
+        <v>680</v>
+      </c>
       <c r="C733" s="17">
         <v>1032</v>
       </c>
@@ -33514,38 +33781,42 @@
         <v>15</v>
       </c>
       <c r="E733" s="57">
-        <v>0</v>
+        <v>1880</v>
       </c>
       <c r="F733" s="20">
         <v>0</v>
       </c>
       <c r="G733" s="21">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>1880</v>
       </c>
       <c r="H733" s="22">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I733" s="23">
         <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="J733" t="str">
+        <v>2256</v>
+      </c>
+      <c r="J733">
         <f t="shared" si="101"/>
-        <v/>
+        <v>6126</v>
       </c>
       <c r="K733" t="str">
         <f t="shared" si="102"/>
-        <v/>
-      </c>
-      <c r="L733" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L733">
         <f t="shared" si="103"/>
-        <v/>
+        <v>2256</v>
       </c>
     </row>
     <row r="734" spans="1:12">
-      <c r="A734" s="15"/>
-      <c r="B734" s="16"/>
+      <c r="A734" s="15">
+        <v>6126</v>
+      </c>
+      <c r="B734" s="16" t="s">
+        <v>681</v>
+      </c>
       <c r="C734" s="17">
         <v>1032</v>
       </c>
@@ -33553,38 +33824,42 @@
         <v>15</v>
       </c>
       <c r="E734" s="57">
-        <v>0</v>
+        <v>1880</v>
       </c>
       <c r="F734" s="20">
         <v>0</v>
       </c>
       <c r="G734" s="21">
         <f t="shared" si="99"/>
-        <v>0</v>
+        <v>1880</v>
       </c>
       <c r="H734" s="22">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I734" s="23">
         <f t="shared" si="100"/>
-        <v>0</v>
-      </c>
-      <c r="J734" t="str">
+        <v>2256</v>
+      </c>
+      <c r="J734">
         <f t="shared" si="101"/>
-        <v/>
+        <v>6126</v>
       </c>
       <c r="K734" t="str">
         <f t="shared" si="102"/>
-        <v/>
-      </c>
-      <c r="L734" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L734">
         <f t="shared" si="103"/>
-        <v/>
+        <v>2256</v>
       </c>
     </row>
     <row r="735" spans="1:12">
-      <c r="A735" s="15"/>
-      <c r="B735" s="16"/>
+      <c r="A735" s="15">
+        <v>6127</v>
+      </c>
+      <c r="B735" s="16" t="s">
+        <v>682</v>
+      </c>
       <c r="C735" s="17">
         <v>1032</v>
       </c>
@@ -33592,38 +33867,42 @@
         <v>15</v>
       </c>
       <c r="E735" s="57">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="F735" s="20">
         <v>0</v>
       </c>
       <c r="G735" s="21">
         <f t="shared" ref="G735:G766" si="104">E735*(1-F735)</f>
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="H735" s="22">
         <v>0</v>
       </c>
       <c r="I735" s="23">
         <f t="shared" ref="I735:I766" si="105">+ROUND((G735*H735)+G735,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J735" t="str">
+        <v>3000</v>
+      </c>
+      <c r="J735">
         <f t="shared" si="101"/>
-        <v/>
+        <v>6127</v>
       </c>
       <c r="K735" t="str">
         <f t="shared" si="102"/>
-        <v/>
-      </c>
-      <c r="L735" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L735">
         <f t="shared" si="103"/>
-        <v/>
+        <v>3000</v>
       </c>
     </row>
     <row r="736" spans="1:12">
-      <c r="A736" s="15"/>
-      <c r="B736" s="16"/>
+      <c r="A736" s="15">
+        <v>6130</v>
+      </c>
+      <c r="B736" s="16" t="s">
+        <v>683</v>
+      </c>
       <c r="C736" s="17">
         <v>1032</v>
       </c>
@@ -33631,33 +33910,33 @@
         <v>15</v>
       </c>
       <c r="E736" s="57">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="F736" s="20">
         <v>0</v>
       </c>
       <c r="G736" s="21">
         <f t="shared" si="104"/>
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="H736" s="22">
-        <v>0</v>
+        <v>0.33329999999999999</v>
       </c>
       <c r="I736" s="23">
         <f t="shared" si="105"/>
-        <v>0</v>
-      </c>
-      <c r="J736" t="str">
+        <v>4000</v>
+      </c>
+      <c r="J736">
         <f t="shared" si="101"/>
-        <v/>
+        <v>6130</v>
       </c>
       <c r="K736" t="str">
         <f t="shared" si="102"/>
-        <v/>
-      </c>
-      <c r="L736" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="L736">
         <f t="shared" si="103"/>
-        <v/>
+        <v>4000</v>
       </c>
     </row>
     <row r="737" spans="1:12">
@@ -43971,7 +44250,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C999"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
@@ -44621,7 +44900,7 @@
       </c>
       <c r="C46">
         <f>IF(PRECIOS_DE_VENTA!L49="","",PRECIOS_DE_VENTA!L49)</f>
-        <v>5999</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -44859,7 +45138,7 @@
       </c>
       <c r="C63">
         <f>IF(PRECIOS_DE_VENTA!L66="","",PRECIOS_DE_VENTA!L66)</f>
-        <v>9999</v>
+        <v>9290</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -45083,7 +45362,7 @@
       </c>
       <c r="C79">
         <f>IF(PRECIOS_DE_VENTA!L82="","",PRECIOS_DE_VENTA!L82)</f>
-        <v>2640</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="80" spans="1:3">
@@ -45097,7 +45376,7 @@
       </c>
       <c r="C80">
         <f>IF(PRECIOS_DE_VENTA!L83="","",PRECIOS_DE_VENTA!L83)</f>
-        <v>5109</v>
+        <v>4490</v>
       </c>
     </row>
     <row r="81" spans="1:3">
@@ -45139,7 +45418,7 @@
       </c>
       <c r="C83">
         <f>IF(PRECIOS_DE_VENTA!L86="","",PRECIOS_DE_VENTA!L86)</f>
-        <v>1643</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="84" spans="1:3">
@@ -45153,7 +45432,7 @@
       </c>
       <c r="C84">
         <f>IF(PRECIOS_DE_VENTA!L87="","",PRECIOS_DE_VENTA!L87)</f>
-        <v>5031</v>
+        <v>4711</v>
       </c>
     </row>
     <row r="85" spans="1:3">
@@ -45251,7 +45530,7 @@
       </c>
       <c r="C91">
         <f>IF(PRECIOS_DE_VENTA!L94="","",PRECIOS_DE_VENTA!L94)</f>
-        <v>3670</v>
+        <v>3661</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -45265,7 +45544,7 @@
       </c>
       <c r="C92">
         <f>IF(PRECIOS_DE_VENTA!L95="","",PRECIOS_DE_VENTA!L95)</f>
-        <v>3670</v>
+        <v>3661</v>
       </c>
     </row>
     <row r="93" spans="1:3">
@@ -45377,7 +45656,7 @@
       </c>
       <c r="C100">
         <f>IF(PRECIOS_DE_VENTA!L103="","",PRECIOS_DE_VENTA!L103)</f>
-        <v>3562</v>
+        <v>3634</v>
       </c>
     </row>
     <row r="101" spans="1:3">
@@ -45391,7 +45670,7 @@
       </c>
       <c r="C101">
         <f>IF(PRECIOS_DE_VENTA!L104="","",PRECIOS_DE_VENTA!L104)</f>
-        <v>3562</v>
+        <v>3634</v>
       </c>
     </row>
     <row r="102" spans="1:3">
@@ -46581,7 +46860,7 @@
       </c>
       <c r="C186">
         <f>IF(PRECIOS_DE_VENTA!L189="","",PRECIOS_DE_VENTA!L189)</f>
-        <v>1753</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="187" spans="1:3">
@@ -46609,7 +46888,7 @@
       </c>
       <c r="C188">
         <f>IF(PRECIOS_DE_VENTA!L191="","",PRECIOS_DE_VENTA!L191)</f>
-        <v>841</v>
+        <v>866</v>
       </c>
     </row>
     <row r="189" spans="1:3">
@@ -46623,7 +46902,7 @@
       </c>
       <c r="C189">
         <f>IF(PRECIOS_DE_VENTA!L192="","",PRECIOS_DE_VENTA!L192)</f>
-        <v>1327</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="190" spans="1:3">
@@ -46637,7 +46916,7 @@
       </c>
       <c r="C190">
         <f>IF(PRECIOS_DE_VENTA!L193="","",PRECIOS_DE_VENTA!L193)</f>
-        <v>2469</v>
+        <v>2723</v>
       </c>
     </row>
     <row r="191" spans="1:3">
@@ -46651,7 +46930,7 @@
       </c>
       <c r="C191">
         <f>IF(PRECIOS_DE_VENTA!L194="","",PRECIOS_DE_VENTA!L194)</f>
-        <v>1717</v>
+        <v>2195</v>
       </c>
     </row>
     <row r="192" spans="1:3">
@@ -46665,7 +46944,7 @@
       </c>
       <c r="C192">
         <f>IF(PRECIOS_DE_VENTA!L195="","",PRECIOS_DE_VENTA!L195)</f>
-        <v>1188</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="193" spans="1:3">
@@ -46679,7 +46958,7 @@
       </c>
       <c r="C193">
         <f>IF(PRECIOS_DE_VENTA!L196="","",PRECIOS_DE_VENTA!L196)</f>
-        <v>1328</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="194" spans="1:3">
@@ -46693,7 +46972,7 @@
       </c>
       <c r="C194">
         <f>IF(PRECIOS_DE_VENTA!L197="","",PRECIOS_DE_VENTA!L197)</f>
-        <v>1093</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="195" spans="1:3">
@@ -46707,7 +46986,7 @@
       </c>
       <c r="C195">
         <f>IF(PRECIOS_DE_VENTA!L198="","",PRECIOS_DE_VENTA!L198)</f>
-        <v>1008</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="196" spans="1:3">
@@ -46721,7 +47000,7 @@
       </c>
       <c r="C196">
         <f>IF(PRECIOS_DE_VENTA!L199="","",PRECIOS_DE_VENTA!L199)</f>
-        <v>1415</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="197" spans="1:3">
@@ -46735,7 +47014,7 @@
       </c>
       <c r="C197">
         <f>IF(PRECIOS_DE_VENTA!L200="","",PRECIOS_DE_VENTA!L200)</f>
-        <v>1233</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="198" spans="1:3">
@@ -46749,7 +47028,7 @@
       </c>
       <c r="C198">
         <f>IF(PRECIOS_DE_VENTA!L201="","",PRECIOS_DE_VENTA!L201)</f>
-        <v>1231</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="199" spans="1:3">
@@ -46763,7 +47042,7 @@
       </c>
       <c r="C199">
         <f>IF(PRECIOS_DE_VENTA!L202="","",PRECIOS_DE_VENTA!L202)</f>
-        <v>1328</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="200" spans="1:3">
@@ -46777,7 +47056,7 @@
       </c>
       <c r="C200">
         <f>IF(PRECIOS_DE_VENTA!L203="","",PRECIOS_DE_VENTA!L203)</f>
-        <v>1405</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="201" spans="1:3">
@@ -46791,7 +47070,7 @@
       </c>
       <c r="C201">
         <f>IF(PRECIOS_DE_VENTA!L204="","",PRECIOS_DE_VENTA!L204)</f>
-        <v>1943</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="202" spans="1:3">
@@ -46805,7 +47084,7 @@
       </c>
       <c r="C202">
         <f>IF(PRECIOS_DE_VENTA!L205="","",PRECIOS_DE_VENTA!L205)</f>
-        <v>1582</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="203" spans="1:3">
@@ -46819,7 +47098,7 @@
       </c>
       <c r="C203">
         <f>IF(PRECIOS_DE_VENTA!L206="","",PRECIOS_DE_VENTA!L206)</f>
-        <v>7692</v>
+        <v>7458</v>
       </c>
     </row>
     <row r="204" spans="1:3">
@@ -46833,7 +47112,7 @@
       </c>
       <c r="C204">
         <f>IF(PRECIOS_DE_VENTA!L207="","",PRECIOS_DE_VENTA!L207)</f>
-        <v>7267</v>
+        <v>7253</v>
       </c>
     </row>
     <row r="205" spans="1:3">
@@ -46847,7 +47126,7 @@
       </c>
       <c r="C205">
         <f>IF(PRECIOS_DE_VENTA!L208="","",PRECIOS_DE_VENTA!L208)</f>
-        <v>944</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="206" spans="1:3">
@@ -46861,7 +47140,7 @@
       </c>
       <c r="C206">
         <f>IF(PRECIOS_DE_VENTA!L209="","",PRECIOS_DE_VENTA!L209)</f>
-        <v>883</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="207" spans="1:3">
@@ -46875,7 +47154,7 @@
       </c>
       <c r="C207">
         <f>IF(PRECIOS_DE_VENTA!L210="","",PRECIOS_DE_VENTA!L210)</f>
-        <v>1695</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="208" spans="1:3">
@@ -46889,7 +47168,7 @@
       </c>
       <c r="C208">
         <f>IF(PRECIOS_DE_VENTA!L211="","",PRECIOS_DE_VENTA!L211)</f>
-        <v>2438</v>
+        <v>3712</v>
       </c>
     </row>
     <row r="209" spans="1:3">
@@ -46903,7 +47182,7 @@
       </c>
       <c r="C209">
         <f>IF(PRECIOS_DE_VENTA!L212="","",PRECIOS_DE_VENTA!L212)</f>
-        <v>2189</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -46917,7 +47196,7 @@
       </c>
       <c r="C210">
         <f>IF(PRECIOS_DE_VENTA!L213="","",PRECIOS_DE_VENTA!L213)</f>
-        <v>468</v>
+        <v>384</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -46931,7 +47210,7 @@
       </c>
       <c r="C211">
         <f>IF(PRECIOS_DE_VENTA!L214="","",PRECIOS_DE_VENTA!L214)</f>
-        <v>468</v>
+        <v>384</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -46945,7 +47224,7 @@
       </c>
       <c r="C212">
         <f>IF(PRECIOS_DE_VENTA!L215="","",PRECIOS_DE_VENTA!L215)</f>
-        <v>468</v>
+        <v>384</v>
       </c>
     </row>
     <row r="213" spans="1:3">
@@ -46959,7 +47238,7 @@
       </c>
       <c r="C213">
         <f>IF(PRECIOS_DE_VENTA!L216="","",PRECIOS_DE_VENTA!L216)</f>
-        <v>937</v>
+        <v>384</v>
       </c>
     </row>
     <row r="214" spans="1:3">
@@ -46973,7 +47252,7 @@
       </c>
       <c r="C214">
         <f>IF(PRECIOS_DE_VENTA!L217="","",PRECIOS_DE_VENTA!L217)</f>
-        <v>387</v>
+        <v>439</v>
       </c>
     </row>
     <row r="215" spans="1:3">
@@ -46987,7 +47266,7 @@
       </c>
       <c r="C215">
         <f>IF(PRECIOS_DE_VENTA!L218="","",PRECIOS_DE_VENTA!L218)</f>
-        <v>387</v>
+        <v>439</v>
       </c>
     </row>
     <row r="216" spans="1:3">
@@ -47001,7 +47280,7 @@
       </c>
       <c r="C216">
         <f>IF(PRECIOS_DE_VENTA!L219="","",PRECIOS_DE_VENTA!L219)</f>
-        <v>387</v>
+        <v>439</v>
       </c>
     </row>
     <row r="217" spans="1:3">
@@ -47015,7 +47294,7 @@
       </c>
       <c r="C217">
         <f>IF(PRECIOS_DE_VENTA!L220="","",PRECIOS_DE_VENTA!L220)</f>
-        <v>387</v>
+        <v>439</v>
       </c>
     </row>
     <row r="218" spans="1:3">
@@ -47029,7 +47308,7 @@
       </c>
       <c r="C218">
         <f>IF(PRECIOS_DE_VENTA!L221="","",PRECIOS_DE_VENTA!L221)</f>
-        <v>387</v>
+        <v>439</v>
       </c>
     </row>
     <row r="219" spans="1:3">
@@ -47043,7 +47322,7 @@
       </c>
       <c r="C219">
         <f>IF(PRECIOS_DE_VENTA!L222="","",PRECIOS_DE_VENTA!L222)</f>
-        <v>387</v>
+        <v>439</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -47057,7 +47336,7 @@
       </c>
       <c r="C220">
         <f>IF(PRECIOS_DE_VENTA!L223="","",PRECIOS_DE_VENTA!L223)</f>
-        <v>387</v>
+        <v>439</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -47071,7 +47350,7 @@
       </c>
       <c r="C221">
         <f>IF(PRECIOS_DE_VENTA!L224="","",PRECIOS_DE_VENTA!L224)</f>
-        <v>37150</v>
+        <v>44215</v>
       </c>
     </row>
     <row r="222" spans="1:3">
@@ -47085,7 +47364,7 @@
       </c>
       <c r="C222">
         <f>IF(PRECIOS_DE_VENTA!L225="","",PRECIOS_DE_VENTA!L225)</f>
-        <v>2581</v>
+        <v>2819</v>
       </c>
     </row>
     <row r="223" spans="1:3">
@@ -47099,7 +47378,7 @@
       </c>
       <c r="C223">
         <f>IF(PRECIOS_DE_VENTA!L226="","",PRECIOS_DE_VENTA!L226)</f>
-        <v>2581</v>
+        <v>2819</v>
       </c>
     </row>
     <row r="224" spans="1:3">
@@ -47113,7 +47392,7 @@
       </c>
       <c r="C224">
         <f>IF(PRECIOS_DE_VENTA!L227="","",PRECIOS_DE_VENTA!L227)</f>
-        <v>2581</v>
+        <v>2819</v>
       </c>
     </row>
     <row r="225" spans="1:3">
@@ -47127,7 +47406,7 @@
       </c>
       <c r="C225">
         <f>IF(PRECIOS_DE_VENTA!L228="","",PRECIOS_DE_VENTA!L228)</f>
-        <v>2710</v>
+        <v>2819</v>
       </c>
     </row>
     <row r="226" spans="1:3">
@@ -47141,7 +47420,7 @@
       </c>
       <c r="C226">
         <f>IF(PRECIOS_DE_VENTA!L229="","",PRECIOS_DE_VENTA!L229)</f>
-        <v>2710</v>
+        <v>2819</v>
       </c>
     </row>
     <row r="227" spans="1:3">
@@ -47155,7 +47434,7 @@
       </c>
       <c r="C227">
         <f>IF(PRECIOS_DE_VENTA!L230="","",PRECIOS_DE_VENTA!L230)</f>
-        <v>2710</v>
+        <v>2819</v>
       </c>
     </row>
     <row r="228" spans="1:3">
@@ -47169,7 +47448,7 @@
       </c>
       <c r="C228">
         <f>IF(PRECIOS_DE_VENTA!L231="","",PRECIOS_DE_VENTA!L231)</f>
-        <v>2710</v>
+        <v>2819</v>
       </c>
     </row>
     <row r="229" spans="1:3">
@@ -47183,7 +47462,7 @@
       </c>
       <c r="C229">
         <f>IF(PRECIOS_DE_VENTA!L232="","",PRECIOS_DE_VENTA!L232)</f>
-        <v>2258</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="230" spans="1:3">
@@ -47197,7 +47476,7 @@
       </c>
       <c r="C230">
         <f>IF(PRECIOS_DE_VENTA!L233="","",PRECIOS_DE_VENTA!L233)</f>
-        <v>1343</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="231" spans="1:3">
@@ -47211,7 +47490,7 @@
       </c>
       <c r="C231">
         <f>IF(PRECIOS_DE_VENTA!L234="","",PRECIOS_DE_VENTA!L234)</f>
-        <v>5752</v>
+        <v>5465</v>
       </c>
     </row>
     <row r="232" spans="1:3">
@@ -47225,7 +47504,7 @@
       </c>
       <c r="C232">
         <f>IF(PRECIOS_DE_VENTA!L235="","",PRECIOS_DE_VENTA!L235)</f>
-        <v>5290</v>
+        <v>5727</v>
       </c>
     </row>
     <row r="233" spans="1:3">
@@ -47239,7 +47518,7 @@
       </c>
       <c r="C233">
         <f>IF(PRECIOS_DE_VENTA!L236="","",PRECIOS_DE_VENTA!L236)</f>
-        <v>5402</v>
+        <v>5727</v>
       </c>
     </row>
     <row r="234" spans="1:3">
@@ -47253,7 +47532,7 @@
       </c>
       <c r="C234">
         <f>IF(PRECIOS_DE_VENTA!L237="","",PRECIOS_DE_VENTA!L237)</f>
-        <v>4100</v>
+        <v>4250</v>
       </c>
     </row>
     <row r="235" spans="1:3">
@@ -47267,7 +47546,7 @@
       </c>
       <c r="C235">
         <f>IF(PRECIOS_DE_VENTA!L238="","",PRECIOS_DE_VENTA!L238)</f>
-        <v>1140</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="236" spans="1:3">
@@ -47281,7 +47560,7 @@
       </c>
       <c r="C236">
         <f>IF(PRECIOS_DE_VENTA!L239="","",PRECIOS_DE_VENTA!L239)</f>
-        <v>2079</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="237" spans="1:3">
@@ -47323,7 +47602,7 @@
       </c>
       <c r="C239">
         <f>IF(PRECIOS_DE_VENTA!L242="","",PRECIOS_DE_VENTA!L242)</f>
-        <v>1565</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="240" spans="1:3">
@@ -47351,7 +47630,7 @@
       </c>
       <c r="C241">
         <f>IF(PRECIOS_DE_VENTA!L244="","",PRECIOS_DE_VENTA!L244)</f>
-        <v>1931</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="242" spans="1:3">
@@ -47365,7 +47644,7 @@
       </c>
       <c r="C242">
         <f>IF(PRECIOS_DE_VENTA!L245="","",PRECIOS_DE_VENTA!L245)</f>
-        <v>3187</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="243" spans="1:3">
@@ -47379,7 +47658,7 @@
       </c>
       <c r="C243">
         <f>IF(PRECIOS_DE_VENTA!L246="","",PRECIOS_DE_VENTA!L246)</f>
-        <v>3187</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="244" spans="1:3">
@@ -47393,7 +47672,7 @@
       </c>
       <c r="C244">
         <f>IF(PRECIOS_DE_VENTA!L247="","",PRECIOS_DE_VENTA!L247)</f>
-        <v>3187</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="245" spans="1:3">
@@ -47407,7 +47686,7 @@
       </c>
       <c r="C245">
         <f>IF(PRECIOS_DE_VENTA!L248="","",PRECIOS_DE_VENTA!L248)</f>
-        <v>1318</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="246" spans="1:3">
@@ -47421,7 +47700,7 @@
       </c>
       <c r="C246">
         <f>IF(PRECIOS_DE_VENTA!L249="","",PRECIOS_DE_VENTA!L249)</f>
-        <v>1557</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="247" spans="1:3">
@@ -47435,7 +47714,7 @@
       </c>
       <c r="C247">
         <f>IF(PRECIOS_DE_VENTA!L250="","",PRECIOS_DE_VENTA!L250)</f>
-        <v>1501</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="248" spans="1:3">
@@ -47939,7 +48218,7 @@
       </c>
       <c r="C283">
         <f>IF(PRECIOS_DE_VENTA!L286="","",PRECIOS_DE_VENTA!L286)</f>
-        <v>24443</v>
+        <v>24796</v>
       </c>
     </row>
     <row r="284" spans="1:3">
@@ -48037,7 +48316,7 @@
       </c>
       <c r="C290">
         <f>IF(PRECIOS_DE_VENTA!L293="","",PRECIOS_DE_VENTA!L293)</f>
-        <v>14390</v>
+        <v>15094</v>
       </c>
     </row>
     <row r="291" spans="1:3">
@@ -48149,7 +48428,7 @@
       </c>
       <c r="C298">
         <f>IF(PRECIOS_DE_VENTA!L301="","",PRECIOS_DE_VENTA!L301)</f>
-        <v>12830</v>
+        <v>12903</v>
       </c>
     </row>
     <row r="299" spans="1:3">
@@ -48163,7 +48442,7 @@
       </c>
       <c r="C299">
         <f>IF(PRECIOS_DE_VENTA!L302="","",PRECIOS_DE_VENTA!L302)</f>
-        <v>10020</v>
+        <v>10659</v>
       </c>
     </row>
     <row r="300" spans="1:3">
@@ -48191,7 +48470,7 @@
       </c>
       <c r="C301">
         <f>IF(PRECIOS_DE_VENTA!L304="","",PRECIOS_DE_VENTA!L304)</f>
-        <v>10200</v>
+        <v>10179</v>
       </c>
     </row>
     <row r="302" spans="1:3">
@@ -48289,7 +48568,7 @@
       </c>
       <c r="C308">
         <f>IF(PRECIOS_DE_VENTA!L311="","",PRECIOS_DE_VENTA!L311)</f>
-        <v>4740</v>
+        <v>5842</v>
       </c>
     </row>
     <row r="309" spans="1:3">
@@ -48303,7 +48582,7 @@
       </c>
       <c r="C309">
         <f>IF(PRECIOS_DE_VENTA!L312="","",PRECIOS_DE_VENTA!L312)</f>
-        <v>4740</v>
+        <v>5840</v>
       </c>
     </row>
     <row r="310" spans="1:3">
@@ -48583,7 +48862,7 @@
       </c>
       <c r="C329">
         <f>IF(PRECIOS_DE_VENTA!L332="","",PRECIOS_DE_VENTA!L332)</f>
-        <v>1780</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="330" spans="1:3">
@@ -48597,7 +48876,7 @@
       </c>
       <c r="C330">
         <f>IF(PRECIOS_DE_VENTA!L333="","",PRECIOS_DE_VENTA!L333)</f>
-        <v>1780</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="331" spans="1:3">
@@ -49003,7 +49282,7 @@
       </c>
       <c r="C359">
         <f>IF(PRECIOS_DE_VENTA!L362="","",PRECIOS_DE_VENTA!L362)</f>
-        <v>3211</v>
+        <v>3424</v>
       </c>
     </row>
     <row r="360" spans="1:3">
@@ -49017,7 +49296,7 @@
       </c>
       <c r="C360">
         <f>IF(PRECIOS_DE_VENTA!L363="","",PRECIOS_DE_VENTA!L363)</f>
-        <v>2574</v>
+        <v>2737</v>
       </c>
     </row>
     <row r="361" spans="1:3">
@@ -49549,7 +49828,7 @@
       </c>
       <c r="C398">
         <f>IF(PRECIOS_DE_VENTA!L401="","",PRECIOS_DE_VENTA!L401)</f>
-        <v>1080</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="399" spans="1:3">
@@ -49563,7 +49842,7 @@
       </c>
       <c r="C399">
         <f>IF(PRECIOS_DE_VENTA!L402="","",PRECIOS_DE_VENTA!L402)</f>
-        <v>2020</v>
+        <v>2222</v>
       </c>
     </row>
     <row r="400" spans="1:3">
@@ -50235,7 +50514,7 @@
       </c>
       <c r="C447">
         <f>IF(PRECIOS_DE_VENTA!L450="","",PRECIOS_DE_VENTA!L450)</f>
-        <v>6800</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="448" spans="1:3">
@@ -51439,7 +51718,7 @@
       </c>
       <c r="C533">
         <f>IF(PRECIOS_DE_VENTA!L536="","",PRECIOS_DE_VENTA!L536)</f>
-        <v>13670</v>
+        <v>13290</v>
       </c>
     </row>
     <row r="534" spans="1:3">
@@ -51481,7 +51760,7 @@
       </c>
       <c r="C536">
         <f>IF(PRECIOS_DE_VENTA!L539="","",PRECIOS_DE_VENTA!L539)</f>
-        <v>13068</v>
+        <v>12150</v>
       </c>
     </row>
     <row r="537" spans="1:3">
@@ -51565,7 +51844,7 @@
       </c>
       <c r="C542">
         <f>IF(PRECIOS_DE_VENTA!L545="","",PRECIOS_DE_VENTA!L545)</f>
-        <v>24840</v>
+        <v>12100</v>
       </c>
     </row>
     <row r="543" spans="1:3">
@@ -51943,7 +52222,7 @@
       </c>
       <c r="C569">
         <f>IF(PRECIOS_DE_VENTA!L572="","",PRECIOS_DE_VENTA!L572)</f>
-        <v>14844</v>
+        <v>13669</v>
       </c>
     </row>
     <row r="570" spans="1:3">
@@ -51999,7 +52278,7 @@
       </c>
       <c r="C573">
         <f>IF(PRECIOS_DE_VENTA!L576="","",PRECIOS_DE_VENTA!L576)</f>
-        <v>7180</v>
+        <v>7620</v>
       </c>
     </row>
     <row r="574" spans="1:3">
@@ -52027,7 +52306,7 @@
       </c>
       <c r="C575">
         <f>IF(PRECIOS_DE_VENTA!L578="","",PRECIOS_DE_VENTA!L578)</f>
-        <v>7399</v>
+        <v>7300</v>
       </c>
     </row>
     <row r="576" spans="1:3">
@@ -52041,7 +52320,7 @@
       </c>
       <c r="C576">
         <f>IF(PRECIOS_DE_VENTA!L579="","",PRECIOS_DE_VENTA!L579)</f>
-        <v>7399</v>
+        <v>7299</v>
       </c>
     </row>
     <row r="577" spans="1:3">
@@ -52055,7 +52334,7 @@
       </c>
       <c r="C577">
         <f>IF(PRECIOS_DE_VENTA!L580="","",PRECIOS_DE_VENTA!L580)</f>
-        <v>8152</v>
+        <v>8787</v>
       </c>
     </row>
     <row r="578" spans="1:3">
@@ -52069,7 +52348,7 @@
       </c>
       <c r="C578">
         <f>IF(PRECIOS_DE_VENTA!L581="","",PRECIOS_DE_VENTA!L581)</f>
-        <v>6399</v>
+        <v>6620</v>
       </c>
     </row>
     <row r="579" spans="1:3">
@@ -52083,7 +52362,7 @@
       </c>
       <c r="C579">
         <f>IF(PRECIOS_DE_VENTA!L582="","",PRECIOS_DE_VENTA!L582)</f>
-        <v>6399</v>
+        <v>6006</v>
       </c>
     </row>
     <row r="580" spans="1:3">
@@ -52097,7 +52376,7 @@
       </c>
       <c r="C580">
         <f>IF(PRECIOS_DE_VENTA!L583="","",PRECIOS_DE_VENTA!L583)</f>
-        <v>7499</v>
+        <v>7899</v>
       </c>
     </row>
     <row r="581" spans="1:3">
@@ -52111,7 +52390,7 @@
       </c>
       <c r="C581">
         <f>IF(PRECIOS_DE_VENTA!L584="","",PRECIOS_DE_VENTA!L584)</f>
-        <v>12880</v>
+        <v>14799</v>
       </c>
     </row>
     <row r="582" spans="1:3">
@@ -52125,7 +52404,7 @@
       </c>
       <c r="C582">
         <f>IF(PRECIOS_DE_VENTA!L585="","",PRECIOS_DE_VENTA!L585)</f>
-        <v>7500</v>
+        <v>8300</v>
       </c>
     </row>
     <row r="583" spans="1:3">
@@ -52237,7 +52516,7 @@
       </c>
       <c r="C590">
         <f>IF(PRECIOS_DE_VENTA!L593="","",PRECIOS_DE_VENTA!L593)</f>
-        <v>7900</v>
+        <v>8649</v>
       </c>
     </row>
     <row r="591" spans="1:3">
@@ -52265,7 +52544,7 @@
       </c>
       <c r="C592">
         <f>IF(PRECIOS_DE_VENTA!L595="","",PRECIOS_DE_VENTA!L595)</f>
-        <v>10800</v>
+        <v>10940</v>
       </c>
     </row>
     <row r="593" spans="1:3">
@@ -52279,7 +52558,7 @@
       </c>
       <c r="C593">
         <f>IF(PRECIOS_DE_VENTA!L596="","",PRECIOS_DE_VENTA!L596)</f>
-        <v>8649</v>
+        <v>8650</v>
       </c>
     </row>
     <row r="594" spans="1:3">
@@ -52293,7 +52572,7 @@
       </c>
       <c r="C594">
         <f>IF(PRECIOS_DE_VENTA!L597="","",PRECIOS_DE_VENTA!L597)</f>
-        <v>8560</v>
+        <v>7499</v>
       </c>
     </row>
     <row r="595" spans="1:3">
@@ -52307,7 +52586,7 @@
       </c>
       <c r="C595">
         <f>IF(PRECIOS_DE_VENTA!L598="","",PRECIOS_DE_VENTA!L598)</f>
-        <v>7200</v>
+        <v>7700</v>
       </c>
     </row>
     <row r="596" spans="1:3">
@@ -52335,7 +52614,7 @@
       </c>
       <c r="C597">
         <f>IF(PRECIOS_DE_VENTA!L600="","",PRECIOS_DE_VENTA!L600)</f>
-        <v>6999</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="598" spans="1:3">
@@ -52349,7 +52628,7 @@
       </c>
       <c r="C598">
         <f>IF(PRECIOS_DE_VENTA!L601="","",PRECIOS_DE_VENTA!L601)</f>
-        <v>10800</v>
+        <v>9295</v>
       </c>
     </row>
     <row r="599" spans="1:3">
@@ -52363,7 +52642,7 @@
       </c>
       <c r="C599">
         <f>IF(PRECIOS_DE_VENTA!L602="","",PRECIOS_DE_VENTA!L602)</f>
-        <v>9004</v>
+        <v>9240</v>
       </c>
     </row>
     <row r="600" spans="1:3">
@@ -52475,7 +52754,7 @@
       </c>
       <c r="C607">
         <f>IF(PRECIOS_DE_VENTA!L610="","",PRECIOS_DE_VENTA!L610)</f>
-        <v>1400</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="608" spans="1:3">
@@ -52517,7 +52796,7 @@
       </c>
       <c r="C610">
         <f>IF(PRECIOS_DE_VENTA!L613="","",PRECIOS_DE_VENTA!L613)</f>
-        <v>1800</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="611" spans="1:3">
@@ -52573,7 +52852,7 @@
       </c>
       <c r="C614">
         <f>IF(PRECIOS_DE_VENTA!L617="","",PRECIOS_DE_VENTA!L617)</f>
-        <v>2799</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="615" spans="1:3">
@@ -53021,7 +53300,7 @@
       </c>
       <c r="C646">
         <f>IF(PRECIOS_DE_VENTA!L649="","",PRECIOS_DE_VENTA!L649)</f>
-        <v>2400</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="647" spans="1:3">
@@ -53315,7 +53594,7 @@
       </c>
       <c r="C667">
         <f>IF(PRECIOS_DE_VENTA!L670="","",PRECIOS_DE_VENTA!L670)</f>
-        <v>4200</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="668" spans="1:3">
@@ -53371,7 +53650,7 @@
       </c>
       <c r="C671">
         <f>IF(PRECIOS_DE_VENTA!L674="","",PRECIOS_DE_VENTA!L674)</f>
-        <v>6500</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="672" spans="1:3">
@@ -53385,7 +53664,7 @@
       </c>
       <c r="C672">
         <f>IF(PRECIOS_DE_VENTA!L675="","",PRECIOS_DE_VENTA!L675)</f>
-        <v>2500</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="673" spans="1:3">
@@ -53539,7 +53818,7 @@
       </c>
       <c r="C683">
         <f>IF(PRECIOS_DE_VENTA!L686="","",PRECIOS_DE_VENTA!L686)</f>
-        <v>1855</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="684" spans="1:3">
@@ -53553,7 +53832,7 @@
       </c>
       <c r="C684">
         <f>IF(PRECIOS_DE_VENTA!L687="","",PRECIOS_DE_VENTA!L687)</f>
-        <v>10400</v>
+        <v>11050</v>
       </c>
     </row>
     <row r="685" spans="1:3">
@@ -53609,7 +53888,7 @@
       </c>
       <c r="C688">
         <f>IF(PRECIOS_DE_VENTA!L691="","",PRECIOS_DE_VENTA!L691)</f>
-        <v>2600</v>
+        <v>100</v>
       </c>
     </row>
     <row r="689" spans="1:3">
@@ -53693,553 +53972,553 @@
       </c>
       <c r="C694">
         <f>IF(PRECIOS_DE_VENTA!L697="","",PRECIOS_DE_VENTA!L697)</f>
-        <v>3700</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="695" spans="1:3">
-      <c r="A695" t="str">
+      <c r="A695">
         <f>IF(PRECIOS_DE_VENTA!J698="","",PRECIOS_DE_VENTA!J698)</f>
-        <v/>
+        <v>999</v>
       </c>
       <c r="B695" t="str">
         <f>IF(PRECIOS_DE_VENTA!K698="","",PRECIOS_DE_VENTA!K698)</f>
-        <v/>
-      </c>
-      <c r="C695" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C695">
         <f>IF(PRECIOS_DE_VENTA!L698="","",PRECIOS_DE_VENTA!L698)</f>
-        <v/>
+        <v>7000</v>
       </c>
     </row>
     <row r="696" spans="1:3">
-      <c r="A696" t="str">
+      <c r="A696">
         <f>IF(PRECIOS_DE_VENTA!J699="","",PRECIOS_DE_VENTA!J699)</f>
-        <v/>
+        <v>6091</v>
       </c>
       <c r="B696" t="str">
         <f>IF(PRECIOS_DE_VENTA!K699="","",PRECIOS_DE_VENTA!K699)</f>
-        <v/>
-      </c>
-      <c r="C696" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C696">
         <f>IF(PRECIOS_DE_VENTA!L699="","",PRECIOS_DE_VENTA!L699)</f>
-        <v/>
+        <v>2390</v>
       </c>
     </row>
     <row r="697" spans="1:3">
-      <c r="A697" t="str">
+      <c r="A697">
         <f>IF(PRECIOS_DE_VENTA!J700="","",PRECIOS_DE_VENTA!J700)</f>
-        <v/>
+        <v>6092</v>
       </c>
       <c r="B697" t="str">
         <f>IF(PRECIOS_DE_VENTA!K700="","",PRECIOS_DE_VENTA!K700)</f>
-        <v/>
-      </c>
-      <c r="C697" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C697">
         <f>IF(PRECIOS_DE_VENTA!L700="","",PRECIOS_DE_VENTA!L700)</f>
-        <v/>
+        <v>3489</v>
       </c>
     </row>
     <row r="698" spans="1:3">
-      <c r="A698" t="str">
+      <c r="A698">
         <f>IF(PRECIOS_DE_VENTA!J701="","",PRECIOS_DE_VENTA!J701)</f>
-        <v/>
+        <v>6093</v>
       </c>
       <c r="B698" t="str">
         <f>IF(PRECIOS_DE_VENTA!K701="","",PRECIOS_DE_VENTA!K701)</f>
-        <v/>
-      </c>
-      <c r="C698" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C698">
         <f>IF(PRECIOS_DE_VENTA!L701="","",PRECIOS_DE_VENTA!L701)</f>
-        <v/>
+        <v>2600</v>
       </c>
     </row>
     <row r="699" spans="1:3">
-      <c r="A699" t="str">
+      <c r="A699">
         <f>IF(PRECIOS_DE_VENTA!J702="","",PRECIOS_DE_VENTA!J702)</f>
-        <v/>
+        <v>6094</v>
       </c>
       <c r="B699" t="str">
         <f>IF(PRECIOS_DE_VENTA!K702="","",PRECIOS_DE_VENTA!K702)</f>
-        <v/>
-      </c>
-      <c r="C699" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C699">
         <f>IF(PRECIOS_DE_VENTA!L702="","",PRECIOS_DE_VENTA!L702)</f>
-        <v/>
+        <v>3094</v>
       </c>
     </row>
     <row r="700" spans="1:3">
-      <c r="A700" t="str">
+      <c r="A700">
         <f>IF(PRECIOS_DE_VENTA!J703="","",PRECIOS_DE_VENTA!J703)</f>
-        <v/>
+        <v>6095</v>
       </c>
       <c r="B700" t="str">
         <f>IF(PRECIOS_DE_VENTA!K703="","",PRECIOS_DE_VENTA!K703)</f>
-        <v/>
-      </c>
-      <c r="C700" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C700">
         <f>IF(PRECIOS_DE_VENTA!L703="","",PRECIOS_DE_VENTA!L703)</f>
-        <v/>
+        <v>1755</v>
       </c>
     </row>
     <row r="701" spans="1:3">
-      <c r="A701" t="str">
+      <c r="A701">
         <f>IF(PRECIOS_DE_VENTA!J704="","",PRECIOS_DE_VENTA!J704)</f>
-        <v/>
+        <v>6096</v>
       </c>
       <c r="B701" t="str">
         <f>IF(PRECIOS_DE_VENTA!K704="","",PRECIOS_DE_VENTA!K704)</f>
-        <v/>
-      </c>
-      <c r="C701" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C701">
         <f>IF(PRECIOS_DE_VENTA!L704="","",PRECIOS_DE_VENTA!L704)</f>
-        <v/>
+        <v>8099</v>
       </c>
     </row>
     <row r="702" spans="1:3">
-      <c r="A702" t="str">
+      <c r="A702">
         <f>IF(PRECIOS_DE_VENTA!J705="","",PRECIOS_DE_VENTA!J705)</f>
-        <v/>
+        <v>6097</v>
       </c>
       <c r="B702" t="str">
         <f>IF(PRECIOS_DE_VENTA!K705="","",PRECIOS_DE_VENTA!K705)</f>
-        <v/>
-      </c>
-      <c r="C702" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C702">
         <f>IF(PRECIOS_DE_VENTA!L705="","",PRECIOS_DE_VENTA!L705)</f>
-        <v/>
+        <v>7800</v>
       </c>
     </row>
     <row r="703" spans="1:3">
-      <c r="A703" t="str">
+      <c r="A703">
         <f>IF(PRECIOS_DE_VENTA!J706="","",PRECIOS_DE_VENTA!J706)</f>
-        <v/>
+        <v>6098</v>
       </c>
       <c r="B703" t="str">
         <f>IF(PRECIOS_DE_VENTA!K706="","",PRECIOS_DE_VENTA!K706)</f>
-        <v/>
-      </c>
-      <c r="C703" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C703">
         <f>IF(PRECIOS_DE_VENTA!L706="","",PRECIOS_DE_VENTA!L706)</f>
-        <v/>
+        <v>850</v>
       </c>
     </row>
     <row r="704" spans="1:3">
-      <c r="A704" t="str">
+      <c r="A704">
         <f>IF(PRECIOS_DE_VENTA!J707="","",PRECIOS_DE_VENTA!J707)</f>
-        <v/>
+        <v>6099</v>
       </c>
       <c r="B704" t="str">
         <f>IF(PRECIOS_DE_VENTA!K707="","",PRECIOS_DE_VENTA!K707)</f>
-        <v/>
-      </c>
-      <c r="C704" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C704">
         <f>IF(PRECIOS_DE_VENTA!L707="","",PRECIOS_DE_VENTA!L707)</f>
-        <v/>
+        <v>4123</v>
       </c>
     </row>
     <row r="705" spans="1:3">
-      <c r="A705" t="str">
+      <c r="A705">
         <f>IF(PRECIOS_DE_VENTA!J708="","",PRECIOS_DE_VENTA!J708)</f>
-        <v/>
+        <v>6100</v>
       </c>
       <c r="B705" t="str">
         <f>IF(PRECIOS_DE_VENTA!K708="","",PRECIOS_DE_VENTA!K708)</f>
-        <v/>
-      </c>
-      <c r="C705" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C705">
         <f>IF(PRECIOS_DE_VENTA!L708="","",PRECIOS_DE_VENTA!L708)</f>
-        <v/>
+        <v>1550</v>
       </c>
     </row>
     <row r="706" spans="1:3">
-      <c r="A706" t="str">
+      <c r="A706">
         <f>IF(PRECIOS_DE_VENTA!J709="","",PRECIOS_DE_VENTA!J709)</f>
-        <v/>
+        <v>6101</v>
       </c>
       <c r="B706" t="str">
         <f>IF(PRECIOS_DE_VENTA!K709="","",PRECIOS_DE_VENTA!K709)</f>
-        <v/>
-      </c>
-      <c r="C706" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C706">
         <f>IF(PRECIOS_DE_VENTA!L709="","",PRECIOS_DE_VENTA!L709)</f>
-        <v/>
+        <v>6159</v>
       </c>
     </row>
     <row r="707" spans="1:3">
-      <c r="A707" t="str">
+      <c r="A707">
         <f>IF(PRECIOS_DE_VENTA!J710="","",PRECIOS_DE_VENTA!J710)</f>
-        <v/>
+        <v>6102</v>
       </c>
       <c r="B707" t="str">
         <f>IF(PRECIOS_DE_VENTA!K710="","",PRECIOS_DE_VENTA!K710)</f>
-        <v/>
-      </c>
-      <c r="C707" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C707">
         <f>IF(PRECIOS_DE_VENTA!L710="","",PRECIOS_DE_VENTA!L710)</f>
-        <v/>
+        <v>3300</v>
       </c>
     </row>
     <row r="708" spans="1:3">
-      <c r="A708" t="str">
+      <c r="A708">
         <f>IF(PRECIOS_DE_VENTA!J711="","",PRECIOS_DE_VENTA!J711)</f>
-        <v/>
+        <v>6103</v>
       </c>
       <c r="B708" t="str">
         <f>IF(PRECIOS_DE_VENTA!K711="","",PRECIOS_DE_VENTA!K711)</f>
-        <v/>
-      </c>
-      <c r="C708" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C708">
         <f>IF(PRECIOS_DE_VENTA!L711="","",PRECIOS_DE_VENTA!L711)</f>
-        <v/>
+        <v>2500</v>
       </c>
     </row>
     <row r="709" spans="1:3">
-      <c r="A709" t="str">
+      <c r="A709">
         <f>IF(PRECIOS_DE_VENTA!J712="","",PRECIOS_DE_VENTA!J712)</f>
-        <v/>
+        <v>6104</v>
       </c>
       <c r="B709" t="str">
         <f>IF(PRECIOS_DE_VENTA!K712="","",PRECIOS_DE_VENTA!K712)</f>
-        <v/>
-      </c>
-      <c r="C709" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C709">
         <f>IF(PRECIOS_DE_VENTA!L712="","",PRECIOS_DE_VENTA!L712)</f>
-        <v/>
+        <v>1325</v>
       </c>
     </row>
     <row r="710" spans="1:3">
-      <c r="A710" t="str">
+      <c r="A710">
         <f>IF(PRECIOS_DE_VENTA!J713="","",PRECIOS_DE_VENTA!J713)</f>
-        <v/>
+        <v>6105</v>
       </c>
       <c r="B710" t="str">
         <f>IF(PRECIOS_DE_VENTA!K713="","",PRECIOS_DE_VENTA!K713)</f>
-        <v/>
-      </c>
-      <c r="C710" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C710">
         <f>IF(PRECIOS_DE_VENTA!L713="","",PRECIOS_DE_VENTA!L713)</f>
-        <v/>
+        <v>2210</v>
       </c>
     </row>
     <row r="711" spans="1:3">
-      <c r="A711" t="str">
+      <c r="A711">
         <f>IF(PRECIOS_DE_VENTA!J714="","",PRECIOS_DE_VENTA!J714)</f>
-        <v/>
+        <v>6106</v>
       </c>
       <c r="B711" t="str">
         <f>IF(PRECIOS_DE_VENTA!K714="","",PRECIOS_DE_VENTA!K714)</f>
-        <v/>
-      </c>
-      <c r="C711" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C711">
         <f>IF(PRECIOS_DE_VENTA!L714="","",PRECIOS_DE_VENTA!L714)</f>
-        <v/>
+        <v>2730</v>
       </c>
     </row>
     <row r="712" spans="1:3">
-      <c r="A712" t="str">
+      <c r="A712">
         <f>IF(PRECIOS_DE_VENTA!J715="","",PRECIOS_DE_VENTA!J715)</f>
-        <v/>
+        <v>6107</v>
       </c>
       <c r="B712" t="str">
         <f>IF(PRECIOS_DE_VENTA!K715="","",PRECIOS_DE_VENTA!K715)</f>
-        <v/>
-      </c>
-      <c r="C712" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C712">
         <f>IF(PRECIOS_DE_VENTA!L715="","",PRECIOS_DE_VENTA!L715)</f>
-        <v/>
+        <v>2730</v>
       </c>
     </row>
     <row r="713" spans="1:3">
-      <c r="A713" t="str">
+      <c r="A713">
         <f>IF(PRECIOS_DE_VENTA!J716="","",PRECIOS_DE_VENTA!J716)</f>
-        <v/>
+        <v>6108</v>
       </c>
       <c r="B713" t="str">
         <f>IF(PRECIOS_DE_VENTA!K716="","",PRECIOS_DE_VENTA!K716)</f>
-        <v/>
-      </c>
-      <c r="C713" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C713">
         <f>IF(PRECIOS_DE_VENTA!L716="","",PRECIOS_DE_VENTA!L716)</f>
-        <v/>
+        <v>2730</v>
       </c>
     </row>
     <row r="714" spans="1:3">
-      <c r="A714" t="str">
+      <c r="A714">
         <f>IF(PRECIOS_DE_VENTA!J717="","",PRECIOS_DE_VENTA!J717)</f>
-        <v/>
+        <v>6109</v>
       </c>
       <c r="B714" t="str">
         <f>IF(PRECIOS_DE_VENTA!K717="","",PRECIOS_DE_VENTA!K717)</f>
-        <v/>
-      </c>
-      <c r="C714" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C714">
         <f>IF(PRECIOS_DE_VENTA!L717="","",PRECIOS_DE_VENTA!L717)</f>
-        <v/>
+        <v>8220</v>
       </c>
     </row>
     <row r="715" spans="1:3">
-      <c r="A715" t="str">
+      <c r="A715">
         <f>IF(PRECIOS_DE_VENTA!J718="","",PRECIOS_DE_VENTA!J718)</f>
-        <v/>
+        <v>6110</v>
       </c>
       <c r="B715" t="str">
         <f>IF(PRECIOS_DE_VENTA!K718="","",PRECIOS_DE_VENTA!K718)</f>
-        <v/>
-      </c>
-      <c r="C715" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C715">
         <f>IF(PRECIOS_DE_VENTA!L718="","",PRECIOS_DE_VENTA!L718)</f>
-        <v/>
+        <v>2259</v>
       </c>
     </row>
     <row r="716" spans="1:3">
-      <c r="A716" t="str">
+      <c r="A716">
         <f>IF(PRECIOS_DE_VENTA!J719="","",PRECIOS_DE_VENTA!J719)</f>
-        <v/>
+        <v>6111</v>
       </c>
       <c r="B716" t="str">
         <f>IF(PRECIOS_DE_VENTA!K719="","",PRECIOS_DE_VENTA!K719)</f>
-        <v/>
-      </c>
-      <c r="C716" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C716">
         <f>IF(PRECIOS_DE_VENTA!L719="","",PRECIOS_DE_VENTA!L719)</f>
-        <v/>
+        <v>2550</v>
       </c>
     </row>
     <row r="717" spans="1:3">
-      <c r="A717" t="str">
+      <c r="A717">
         <f>IF(PRECIOS_DE_VENTA!J720="","",PRECIOS_DE_VENTA!J720)</f>
-        <v/>
+        <v>6112</v>
       </c>
       <c r="B717" t="str">
         <f>IF(PRECIOS_DE_VENTA!K720="","",PRECIOS_DE_VENTA!K720)</f>
-        <v/>
-      </c>
-      <c r="C717" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C717">
         <f>IF(PRECIOS_DE_VENTA!L720="","",PRECIOS_DE_VENTA!L720)</f>
-        <v/>
+        <v>1204</v>
       </c>
     </row>
     <row r="718" spans="1:3">
-      <c r="A718" t="str">
+      <c r="A718">
         <f>IF(PRECIOS_DE_VENTA!J721="","",PRECIOS_DE_VENTA!J721)</f>
-        <v/>
+        <v>6113</v>
       </c>
       <c r="B718" t="str">
         <f>IF(PRECIOS_DE_VENTA!K721="","",PRECIOS_DE_VENTA!K721)</f>
-        <v/>
-      </c>
-      <c r="C718" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C718">
         <f>IF(PRECIOS_DE_VENTA!L721="","",PRECIOS_DE_VENTA!L721)</f>
-        <v/>
+        <v>1150</v>
       </c>
     </row>
     <row r="719" spans="1:3">
-      <c r="A719" t="str">
+      <c r="A719">
         <f>IF(PRECIOS_DE_VENTA!J722="","",PRECIOS_DE_VENTA!J722)</f>
-        <v/>
+        <v>6114</v>
       </c>
       <c r="B719" t="str">
         <f>IF(PRECIOS_DE_VENTA!K722="","",PRECIOS_DE_VENTA!K722)</f>
-        <v/>
-      </c>
-      <c r="C719" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C719">
         <f>IF(PRECIOS_DE_VENTA!L722="","",PRECIOS_DE_VENTA!L722)</f>
-        <v/>
+        <v>3199</v>
       </c>
     </row>
     <row r="720" spans="1:3">
-      <c r="A720" t="str">
+      <c r="A720">
         <f>IF(PRECIOS_DE_VENTA!J723="","",PRECIOS_DE_VENTA!J723)</f>
-        <v/>
+        <v>6115</v>
       </c>
       <c r="B720" t="str">
         <f>IF(PRECIOS_DE_VENTA!K723="","",PRECIOS_DE_VENTA!K723)</f>
-        <v/>
-      </c>
-      <c r="C720" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C720">
         <f>IF(PRECIOS_DE_VENTA!L723="","",PRECIOS_DE_VENTA!L723)</f>
-        <v/>
+        <v>2380</v>
       </c>
     </row>
     <row r="721" spans="1:3">
-      <c r="A721" t="str">
+      <c r="A721">
         <f>IF(PRECIOS_DE_VENTA!J724="","",PRECIOS_DE_VENTA!J724)</f>
-        <v/>
+        <v>6116</v>
       </c>
       <c r="B721" t="str">
         <f>IF(PRECIOS_DE_VENTA!K724="","",PRECIOS_DE_VENTA!K724)</f>
-        <v/>
-      </c>
-      <c r="C721" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C721">
         <f>IF(PRECIOS_DE_VENTA!L724="","",PRECIOS_DE_VENTA!L724)</f>
-        <v/>
+        <v>4399</v>
       </c>
     </row>
     <row r="722" spans="1:3">
-      <c r="A722" t="str">
+      <c r="A722">
         <f>IF(PRECIOS_DE_VENTA!J725="","",PRECIOS_DE_VENTA!J725)</f>
-        <v/>
+        <v>6117</v>
       </c>
       <c r="B722" t="str">
         <f>IF(PRECIOS_DE_VENTA!K725="","",PRECIOS_DE_VENTA!K725)</f>
-        <v/>
-      </c>
-      <c r="C722" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C722">
         <f>IF(PRECIOS_DE_VENTA!L725="","",PRECIOS_DE_VENTA!L725)</f>
-        <v/>
+        <v>2600</v>
       </c>
     </row>
     <row r="723" spans="1:3">
-      <c r="A723" t="str">
+      <c r="A723">
         <f>IF(PRECIOS_DE_VENTA!J726="","",PRECIOS_DE_VENTA!J726)</f>
-        <v/>
+        <v>6118</v>
       </c>
       <c r="B723" t="str">
         <f>IF(PRECIOS_DE_VENTA!K726="","",PRECIOS_DE_VENTA!K726)</f>
-        <v/>
-      </c>
-      <c r="C723" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C723">
         <f>IF(PRECIOS_DE_VENTA!L726="","",PRECIOS_DE_VENTA!L726)</f>
-        <v/>
+        <v>8890</v>
       </c>
     </row>
     <row r="724" spans="1:3">
-      <c r="A724" t="str">
+      <c r="A724">
         <f>IF(PRECIOS_DE_VENTA!J727="","",PRECIOS_DE_VENTA!J727)</f>
-        <v/>
+        <v>6120</v>
       </c>
       <c r="B724" t="str">
         <f>IF(PRECIOS_DE_VENTA!K727="","",PRECIOS_DE_VENTA!K727)</f>
-        <v/>
-      </c>
-      <c r="C724" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C724">
         <f>IF(PRECIOS_DE_VENTA!L727="","",PRECIOS_DE_VENTA!L727)</f>
-        <v/>
+        <v>1760</v>
       </c>
     </row>
     <row r="725" spans="1:3">
-      <c r="A725" t="str">
+      <c r="A725">
         <f>IF(PRECIOS_DE_VENTA!J728="","",PRECIOS_DE_VENTA!J728)</f>
-        <v/>
+        <v>6121</v>
       </c>
       <c r="B725" t="str">
         <f>IF(PRECIOS_DE_VENTA!K728="","",PRECIOS_DE_VENTA!K728)</f>
-        <v/>
-      </c>
-      <c r="C725" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C725">
         <f>IF(PRECIOS_DE_VENTA!L728="","",PRECIOS_DE_VENTA!L728)</f>
-        <v/>
+        <v>1470</v>
       </c>
     </row>
     <row r="726" spans="1:3">
-      <c r="A726" t="str">
+      <c r="A726">
         <f>IF(PRECIOS_DE_VENTA!J729="","",PRECIOS_DE_VENTA!J729)</f>
-        <v/>
+        <v>6122</v>
       </c>
       <c r="B726" t="str">
         <f>IF(PRECIOS_DE_VENTA!K729="","",PRECIOS_DE_VENTA!K729)</f>
-        <v/>
-      </c>
-      <c r="C726" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C726">
         <f>IF(PRECIOS_DE_VENTA!L729="","",PRECIOS_DE_VENTA!L729)</f>
-        <v/>
+        <v>1400</v>
       </c>
     </row>
     <row r="727" spans="1:3">
-      <c r="A727" t="str">
+      <c r="A727">
         <f>IF(PRECIOS_DE_VENTA!J730="","",PRECIOS_DE_VENTA!J730)</f>
-        <v/>
+        <v>6123</v>
       </c>
       <c r="B727" t="str">
         <f>IF(PRECIOS_DE_VENTA!K730="","",PRECIOS_DE_VENTA!K730)</f>
-        <v/>
-      </c>
-      <c r="C727" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C727">
         <f>IF(PRECIOS_DE_VENTA!L730="","",PRECIOS_DE_VENTA!L730)</f>
-        <v/>
+        <v>1400</v>
       </c>
     </row>
     <row r="728" spans="1:3">
-      <c r="A728" t="str">
+      <c r="A728">
         <f>IF(PRECIOS_DE_VENTA!J731="","",PRECIOS_DE_VENTA!J731)</f>
-        <v/>
+        <v>6124</v>
       </c>
       <c r="B728" t="str">
         <f>IF(PRECIOS_DE_VENTA!K731="","",PRECIOS_DE_VENTA!K731)</f>
-        <v/>
-      </c>
-      <c r="C728" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C728">
         <f>IF(PRECIOS_DE_VENTA!L731="","",PRECIOS_DE_VENTA!L731)</f>
-        <v/>
+        <v>1650</v>
       </c>
     </row>
     <row r="729" spans="1:3">
-      <c r="A729" t="str">
+      <c r="A729">
         <f>IF(PRECIOS_DE_VENTA!J732="","",PRECIOS_DE_VENTA!J732)</f>
-        <v/>
+        <v>6125</v>
       </c>
       <c r="B729" t="str">
         <f>IF(PRECIOS_DE_VENTA!K732="","",PRECIOS_DE_VENTA!K732)</f>
-        <v/>
-      </c>
-      <c r="C729" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C729">
         <f>IF(PRECIOS_DE_VENTA!L732="","",PRECIOS_DE_VENTA!L732)</f>
-        <v/>
+        <v>2256</v>
       </c>
     </row>
     <row r="730" spans="1:3">
-      <c r="A730" t="str">
+      <c r="A730">
         <f>IF(PRECIOS_DE_VENTA!J733="","",PRECIOS_DE_VENTA!J733)</f>
-        <v/>
+        <v>6126</v>
       </c>
       <c r="B730" t="str">
         <f>IF(PRECIOS_DE_VENTA!K733="","",PRECIOS_DE_VENTA!K733)</f>
-        <v/>
-      </c>
-      <c r="C730" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C730">
         <f>IF(PRECIOS_DE_VENTA!L733="","",PRECIOS_DE_VENTA!L733)</f>
-        <v/>
+        <v>2256</v>
       </c>
     </row>
     <row r="731" spans="1:3">
-      <c r="A731" t="str">
+      <c r="A731">
         <f>IF(PRECIOS_DE_VENTA!J734="","",PRECIOS_DE_VENTA!J734)</f>
-        <v/>
+        <v>6126</v>
       </c>
       <c r="B731" t="str">
         <f>IF(PRECIOS_DE_VENTA!K734="","",PRECIOS_DE_VENTA!K734)</f>
-        <v/>
-      </c>
-      <c r="C731" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C731">
         <f>IF(PRECIOS_DE_VENTA!L734="","",PRECIOS_DE_VENTA!L734)</f>
-        <v/>
+        <v>2256</v>
       </c>
     </row>
     <row r="732" spans="1:3">
-      <c r="A732" t="str">
+      <c r="A732">
         <f>IF(PRECIOS_DE_VENTA!J735="","",PRECIOS_DE_VENTA!J735)</f>
-        <v/>
+        <v>6127</v>
       </c>
       <c r="B732" t="str">
         <f>IF(PRECIOS_DE_VENTA!K735="","",PRECIOS_DE_VENTA!K735)</f>
-        <v/>
-      </c>
-      <c r="C732" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C732">
         <f>IF(PRECIOS_DE_VENTA!L735="","",PRECIOS_DE_VENTA!L735)</f>
-        <v/>
+        <v>3000</v>
       </c>
     </row>
     <row r="733" spans="1:3">
-      <c r="A733" t="str">
+      <c r="A733">
         <f>IF(PRECIOS_DE_VENTA!J736="","",PRECIOS_DE_VENTA!J736)</f>
-        <v/>
+        <v>6130</v>
       </c>
       <c r="B733" t="str">
         <f>IF(PRECIOS_DE_VENTA!K736="","",PRECIOS_DE_VENTA!K736)</f>
-        <v/>
-      </c>
-      <c r="C733" t="str">
+        <v>LISTA1</v>
+      </c>
+      <c r="C733">
         <f>IF(PRECIOS_DE_VENTA!L736="","",PRECIOS_DE_VENTA!L736)</f>
-        <v/>
+        <v>4000</v>
       </c>
     </row>
     <row r="734" spans="1:3">
